--- a/data/BULGS (TRY).xlsx
+++ b/data/BULGS (TRY).xlsx
@@ -12,6 +12,28 @@
     <sheet name="Nakit Akış (Yıllıklan.)" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -381,9 +403,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I108"/>
+  <dimension ref="A1:J108"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -392,6 +414,7 @@
     <col min="7" max="7" customWidth="1" width="20"/>
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -399,27 +422,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -433,28 +459,31 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>41194978</v>
+        <v>9243325</v>
       </c>
       <c r="C3">
-        <v>126258779.38707031</v>
+        <v>42989111.89196429</v>
       </c>
       <c r="D3">
-        <v>521498793.80548894</v>
+        <v>131757633.0399691</v>
       </c>
       <c r="E3">
-        <v>73255829</v>
+        <v>544211238.5259334</v>
       </c>
       <c r="F3">
-        <v>80707039.3411027</v>
+        <v>76446285</v>
       </c>
       <c r="G3">
-        <v>58741790.395880125</v>
+        <v>84222012.32159483</v>
       </c>
       <c r="H3">
-        <v>111498478.50182097</v>
+        <v>61300127.410258695</v>
       </c>
       <c r="I3">
-        <v>31387226.069639303</v>
+        <v>116354487.87224881</v>
+      </c>
+      <c r="J3">
+        <v>32754210.318697162</v>
       </c>
     </row>
     <row r="4">
@@ -467,22 +496,25 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
-        <v>1103130832</v>
+        <v>1182143764</v>
       </c>
       <c r="C5">
-        <v>838802881.0067462</v>
+        <v>1151174659.4044464</v>
       </c>
       <c r="D5">
-        <v>387470360.68081594</v>
-      </c>
-      <c r="G5">
-        <v>82530.16019817101</v>
+        <v>875334631.9762816</v>
+      </c>
+      <c r="E5">
+        <v>404345565.86308545</v>
       </c>
       <c r="H5">
-        <v>21332141.663125064</v>
+        <v>86124.53419008772</v>
       </c>
       <c r="I5">
-        <v>20716336.659562342</v>
+        <v>22261204.3839741</v>
+      </c>
+      <c r="J5">
+        <v>21618579.688269947</v>
       </c>
     </row>
     <row r="6">
@@ -494,6 +526,9 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
+      <c r="B7">
+        <v>25197</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -510,25 +545,28 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>2422854</v>
+        <v>2217080</v>
       </c>
       <c r="C10">
-        <v>3042010.644262604</v>
+        <v>2528374.737908423</v>
       </c>
       <c r="D10">
-        <v>3214537.3043737244</v>
+        <v>3174497.045798919</v>
       </c>
       <c r="E10">
-        <v>775061</v>
+        <v>3354537.6297716512</v>
       </c>
       <c r="F10">
-        <v>823655.6873990564</v>
+        <v>808816</v>
       </c>
       <c r="G10">
-        <v>109743.36357303831</v>
+        <v>859527.7440383824</v>
       </c>
       <c r="H10">
-        <v>259107.56300471866</v>
+        <v>114522.93374308544</v>
+      </c>
+      <c r="I10">
+        <v>270392.2798080882</v>
       </c>
     </row>
     <row r="11">
@@ -566,28 +604,31 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>193104</v>
+        <v>94661</v>
       </c>
       <c r="C17">
-        <v>166484.51101313147</v>
+        <v>201514.1132685123</v>
       </c>
       <c r="D17">
-        <v>158752.3048644697</v>
+        <v>173735.28569969063</v>
       </c>
       <c r="E17">
-        <v>61779</v>
+        <v>165666.32459242764</v>
       </c>
       <c r="F17">
-        <v>123992.75534407957</v>
+        <v>64470</v>
       </c>
       <c r="G17">
-        <v>60182.37053509899</v>
+        <v>129392.91855622765</v>
       </c>
       <c r="H17">
-        <v>13460.02927763879</v>
+        <v>62803.448052746266</v>
       </c>
       <c r="I17">
-        <v>1137311.158715204</v>
+        <v>14046.243808784877</v>
+      </c>
+      <c r="J17">
+        <v>1186843.6161802895</v>
       </c>
     </row>
     <row r="18">
@@ -600,28 +641,31 @@
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
-        <v>16388082</v>
+        <v>17058319</v>
       </c>
       <c r="C19">
-        <v>12882837.062522149</v>
+        <v>17101819.809023466</v>
       </c>
       <c r="D19">
-        <v>4389390.743468858</v>
+        <v>13443913.575259324</v>
       </c>
       <c r="E19">
-        <v>2762950</v>
+        <v>4580558.57703177</v>
       </c>
       <c r="F19">
-        <v>2028242.999580391</v>
+        <v>2883283</v>
       </c>
       <c r="G19">
-        <v>964005.4030880408</v>
+        <v>2116577.5413948447</v>
       </c>
       <c r="H19">
-        <v>164163.5715789974</v>
+        <v>1005990.0053305023</v>
       </c>
       <c r="I19">
-        <v>425643.76798777597</v>
+        <v>171313.26413608008</v>
+      </c>
+      <c r="J19">
+        <v>444181.51086629514</v>
       </c>
     </row>
     <row r="20">
@@ -634,13 +678,16 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>101367</v>
+        <v>133648</v>
       </c>
       <c r="C21">
-        <v>108256.91261968539</v>
+        <v>105781.76070764607</v>
       </c>
       <c r="D21">
-        <v>24843.68783188761</v>
+        <v>112971.74450939763</v>
+      </c>
+      <c r="E21">
+        <v>25925.686281809598</v>
       </c>
     </row>
     <row r="22">
@@ -658,28 +705,31 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>1163431217</v>
+        <v>1210915994</v>
       </c>
       <c r="C24">
-        <v>981261249.524234</v>
+        <v>1214101261.7173188</v>
       </c>
       <c r="D24">
-        <v>916756678.5268437</v>
+        <v>1023997382.6675181</v>
       </c>
       <c r="E24">
-        <v>76855619</v>
+        <v>956683492.6066964</v>
       </c>
       <c r="F24">
-        <v>83682930.78342624</v>
+        <v>80202854</v>
       </c>
       <c r="G24">
-        <v>59958251.69327448</v>
+        <v>87327510.5255843</v>
       </c>
       <c r="H24">
-        <v>133267351.32880738</v>
+        <v>62569568.331575125</v>
       </c>
       <c r="I24">
-        <v>53666517.65590462</v>
+        <v>139071444.04397586</v>
+      </c>
+      <c r="J24">
+        <v>56003815.13401369</v>
       </c>
     </row>
     <row r="25">
@@ -692,28 +742,31 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>5331917655</v>
+        <v>6263971198</v>
       </c>
       <c r="C26">
-        <v>4915573376.905174</v>
+        <v>5564134654.217678</v>
       </c>
       <c r="D26">
-        <v>4295254523.040589</v>
+        <v>5129657646.933014</v>
       </c>
       <c r="E26">
-        <v>4589148190</v>
+        <v>4482322512.5999</v>
       </c>
       <c r="F26">
-        <v>4249729521.4579997</v>
+        <v>4789015910</v>
       </c>
       <c r="G26">
-        <v>2864852367.4492483</v>
+        <v>4434814794.8650875</v>
       </c>
       <c r="H26">
-        <v>212628199.79759002</v>
+        <v>2989623127.8053975</v>
       </c>
       <c r="I26">
-        <v>194682563.1120436</v>
+        <v>221888635.85472813</v>
+      </c>
+      <c r="J26">
+        <v>203161426.3524559</v>
       </c>
     </row>
     <row r="27">
@@ -735,23 +788,23 @@
       <c r="A30" t="str">
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
-      <c r="D30">
-        <v>10199.587435568537</v>
-      </c>
       <c r="E30">
-        <v>11226</v>
+        <v>10643.802395513574</v>
       </c>
       <c r="F30">
-        <v>11929.814026031605</v>
+        <v>11715</v>
       </c>
       <c r="G30">
-        <v>61486.83824849603</v>
+        <v>12449.384243278335</v>
       </c>
       <c r="H30">
-        <v>2231.341751908035</v>
+        <v>64164.72826730738</v>
       </c>
       <c r="I30">
-        <v>3666.9182553757487</v>
+        <v>2328.5217009215576</v>
+      </c>
+      <c r="J30">
+        <v>3826.6207880735983</v>
       </c>
     </row>
     <row r="31">
@@ -799,28 +852,31 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>6051226</v>
+        <v>6284121</v>
       </c>
       <c r="C39">
-        <v>6334366.742763004</v>
+        <v>6314770.494538521</v>
       </c>
       <c r="D39">
-        <v>6503258.088537207</v>
+        <v>6610242.653106312</v>
       </c>
       <c r="E39">
-        <v>6676825</v>
+        <v>6786489.596631118</v>
       </c>
       <c r="F39">
-        <v>6954047.215647466</v>
+        <v>6967616</v>
       </c>
       <c r="G39">
-        <v>1749121.873721853</v>
+        <v>7256911.603532635</v>
       </c>
       <c r="H39">
-        <v>1052541.499184533</v>
+        <v>1825300.0630831984</v>
       </c>
       <c r="I39">
-        <v>700609.3195363715</v>
+        <v>1098382.0474277164</v>
+      </c>
+      <c r="J39">
+        <v>731122.4302656999</v>
       </c>
     </row>
     <row r="40">
@@ -828,28 +884,31 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>6729726</v>
+        <v>5287643</v>
       </c>
       <c r="C40">
-        <v>8785054.909350386</v>
+        <v>7022820.694703642</v>
       </c>
       <c r="D40">
-        <v>10956174.597639685</v>
+        <v>9167663.798123984</v>
       </c>
       <c r="E40">
-        <v>17030829</v>
+        <v>11433340.629186142</v>
       </c>
       <c r="F40">
-        <v>19949529.535112582</v>
+        <v>17772560</v>
       </c>
       <c r="G40">
-        <v>17149908.522895828</v>
+        <v>20818376.389884252</v>
       </c>
       <c r="H40">
-        <v>7780976.603968079</v>
+        <v>17896825.58946192</v>
       </c>
       <c r="I40">
-        <v>11732768.154764546</v>
+        <v>8119855.625526492</v>
+      </c>
+      <c r="J40">
+        <v>12243756.581388354</v>
       </c>
     </row>
     <row r="41">
@@ -857,48 +916,51 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>7847781</v>
+        <v>8127278</v>
       </c>
       <c r="C41">
-        <v>4955730.548686693</v>
+        <v>8189569.503171756</v>
       </c>
       <c r="D41">
-        <v>133015.15596560045</v>
+        <v>5171563.753812852</v>
       </c>
       <c r="E41">
-        <v>134296</v>
+        <v>138808.26500580434</v>
       </c>
       <c r="F41">
-        <v>140259.95650315104</v>
+        <v>140145</v>
       </c>
       <c r="G41">
-        <v>36640.49119591738</v>
+        <v>146368.59289197836</v>
       </c>
       <c r="H41">
-        <v>36370.60396807804</v>
+        <v>38236.26694976811</v>
       </c>
       <c r="I41">
-        <v>20058.082845108787</v>
+        <v>37954.6255264908</v>
+      </c>
+      <c r="J41">
+        <v>20931.65744054217</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="D42">
-        <v>276.9273460159949</v>
-      </c>
       <c r="E42">
-        <v>32880</v>
-      </c>
-      <c r="G42">
-        <v>865.4641560037995</v>
+        <v>288.98815442567576</v>
+      </c>
+      <c r="F42">
+        <v>34312</v>
       </c>
       <c r="H42">
-        <v>4138.779055958451</v>
+        <v>903.1570654299603</v>
       </c>
       <c r="I42">
-        <v>12043.11393577604</v>
+        <v>4319.03218719321</v>
+      </c>
+      <c r="J42">
+        <v>12567.618618773158</v>
       </c>
     </row>
     <row r="43">
@@ -926,28 +988,31 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>5352546388</v>
+        <v>6283670240</v>
       </c>
       <c r="C47">
-        <v>4935648529.105974</v>
+        <v>5585661814.910092</v>
       </c>
       <c r="D47">
-        <v>4312857447.397514</v>
+        <v>5150607117.138058</v>
       </c>
       <c r="E47">
-        <v>4613034246</v>
+        <v>4500692083.881274</v>
       </c>
       <c r="F47">
-        <v>4276785287.979289</v>
+        <v>4813942258</v>
       </c>
       <c r="G47">
-        <v>2883850390.639467</v>
+        <v>4463048900.83564</v>
       </c>
       <c r="H47">
-        <v>221504458.62551862</v>
+        <v>3009448557.610225</v>
       </c>
       <c r="I47">
-        <v>207151708.70138076</v>
+        <v>231151475.707097</v>
+      </c>
+      <c r="J47">
+        <v>216173631.26095736</v>
       </c>
     </row>
     <row r="48">
@@ -955,28 +1020,31 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>6515977605</v>
+        <v>7494586234</v>
       </c>
       <c r="C48">
-        <v>5916909778.630209</v>
+        <v>6799763076.627411</v>
       </c>
       <c r="D48">
-        <v>5229614125.924358</v>
+        <v>6174604499.805576</v>
       </c>
       <c r="E48">
-        <v>4689889865</v>
+        <v>5457375576.48797</v>
       </c>
       <c r="F48">
-        <v>4360468218.762715</v>
+        <v>4894145112</v>
       </c>
       <c r="G48">
-        <v>2943808642.3327413</v>
+        <v>4550376411.361224</v>
       </c>
       <c r="H48">
-        <v>354771809.954326</v>
+        <v>3072018125.9418006</v>
       </c>
       <c r="I48">
-        <v>260818226.35728538</v>
+        <v>370222919.7510728</v>
+      </c>
+      <c r="J48">
+        <v>272177446.394971</v>
       </c>
     </row>
     <row r="49">
@@ -989,28 +1057,31 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>7088691</v>
+        <v>7427565</v>
       </c>
       <c r="C50">
-        <v>6277062.607010475</v>
+        <v>7397419.427352534</v>
       </c>
       <c r="D50">
-        <v>5454530.810318511</v>
+        <v>6550442.793430752</v>
       </c>
       <c r="E50">
-        <v>10202074</v>
+        <v>5692087.888066092</v>
       </c>
       <c r="F50">
-        <v>8169528.647385757</v>
+        <v>10646397</v>
       </c>
       <c r="G50">
-        <v>6568383.7686763145</v>
+        <v>8525329.98384109</v>
       </c>
       <c r="H50">
-        <v>2368663.9083985183</v>
+        <v>6854451.646532939</v>
       </c>
       <c r="I50">
-        <v>4260024.621726257</v>
+        <v>2471824.5460065873</v>
+      </c>
+      <c r="J50">
+        <v>4445558.269891852</v>
       </c>
     </row>
     <row r="51">
@@ -1023,28 +1094,31 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>178593</v>
+        <v>77984</v>
       </c>
       <c r="C52">
-        <v>121215.49081946383</v>
+        <v>186371.12659998456</v>
       </c>
       <c r="D52">
-        <v>35085.44115964788</v>
+        <v>126494.69791869535</v>
       </c>
       <c r="E52">
-        <v>50667</v>
+        <v>36613.49098890239</v>
       </c>
       <c r="F52">
-        <v>466910.2609969282</v>
+        <v>52874</v>
       </c>
       <c r="G52">
-        <v>518621.24256206816</v>
+        <v>487245.2524068151</v>
       </c>
       <c r="H52">
-        <v>65342.05735978719</v>
+        <v>541208.3634575628</v>
       </c>
       <c r="I52">
-        <v>49100.18206289389</v>
+        <v>68187.85083684328</v>
+      </c>
+      <c r="J52">
+        <v>51238.6053614973</v>
       </c>
     </row>
     <row r="53">
@@ -1057,28 +1131,31 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>311949</v>
+        <v>427118</v>
       </c>
       <c r="C54">
-        <v>271960.28527187224</v>
+        <v>325535.08016405225</v>
       </c>
       <c r="D54">
-        <v>366242.68300904665</v>
+        <v>283804.7670209472</v>
       </c>
       <c r="E54">
-        <v>328895</v>
+        <v>382193.37511210993</v>
       </c>
       <c r="F54">
-        <v>409435.2161937487</v>
+        <v>343219</v>
       </c>
       <c r="G54">
-        <v>449825.62223091396</v>
+        <v>427267.0402072712</v>
       </c>
       <c r="H54">
-        <v>199165.24604933974</v>
+        <v>469416.53921886353</v>
       </c>
       <c r="I54">
-        <v>161926.89806663082</v>
+        <v>207839.34020806284</v>
+      </c>
+      <c r="J54">
+        <v>168979.17846454703</v>
       </c>
     </row>
     <row r="55">
@@ -1086,19 +1163,22 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>448718</v>
+        <v>860394</v>
       </c>
       <c r="C55">
-        <v>390107.6010305954</v>
+        <v>468260.67755002645</v>
       </c>
       <c r="D55">
-        <v>1092284.6448527595</v>
+        <v>407097.6639582143</v>
       </c>
       <c r="E55">
-        <v>694027</v>
-      </c>
-      <c r="I55">
-        <v>417932.7094245812</v>
+        <v>1139856.0964263594</v>
+      </c>
+      <c r="F55">
+        <v>724253</v>
+      </c>
+      <c r="J55">
+        <v>436134.6183693828</v>
       </c>
     </row>
     <row r="56">
@@ -1135,22 +1215,25 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
+      <c r="B62">
+        <v>976495</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
-      <c r="F63">
-        <v>59982.30515881814</v>
-      </c>
       <c r="G63">
-        <v>35131.57325436293</v>
+        <v>62594.669379611754</v>
       </c>
       <c r="H63">
-        <v>13958.5488805143</v>
+        <v>36661.63224004023</v>
       </c>
       <c r="I63">
-        <v>3581.6100880387626</v>
+        <v>14566.475060962093</v>
+      </c>
+      <c r="J63">
+        <v>3737.5972582892614</v>
       </c>
     </row>
     <row r="64">
@@ -1168,28 +1251,31 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>8027951</v>
+        <v>9769556</v>
       </c>
       <c r="C66">
-        <v>7060345.984132406</v>
+        <v>8377586.311666598</v>
       </c>
       <c r="D66">
-        <v>6948143.579339964</v>
+        <v>7367839.922328609</v>
       </c>
       <c r="E66">
-        <v>11275663</v>
+        <v>7250750.850593463</v>
       </c>
       <c r="F66">
-        <v>9105856.42973525</v>
+        <v>11766743</v>
       </c>
       <c r="G66">
-        <v>7571962.206723659</v>
+        <v>9502436.945834786</v>
       </c>
       <c r="H66">
-        <v>2647129.760688159</v>
+        <v>7901738.181449405</v>
       </c>
       <c r="I66">
-        <v>4892566.021368401</v>
+        <v>2762418.212112455</v>
+      </c>
+      <c r="J66">
+        <v>5105648.269345568</v>
       </c>
     </row>
     <row r="67">
@@ -1201,29 +1287,29 @@
       <c r="A68" t="str">
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
-      <c r="B68">
-        <v>1423708</v>
-      </c>
       <c r="C68">
-        <v>3740909.531819793</v>
+        <v>1485713.683679712</v>
       </c>
       <c r="D68">
-        <v>6204342.9391712835</v>
+        <v>3903834.550927951</v>
       </c>
       <c r="E68">
-        <v>15062231</v>
+        <v>6474556.020594377</v>
       </c>
       <c r="F68">
-        <v>18470519.17800931</v>
+        <v>15718225</v>
       </c>
       <c r="G68">
-        <v>8721302.36878434</v>
+        <v>19274951.807138104</v>
       </c>
       <c r="H68">
-        <v>4842894.007996327</v>
+        <v>9101134.691110242</v>
       </c>
       <c r="I68">
-        <v>9004994.184200527</v>
+        <v>5053812.9281359855</v>
+      </c>
+      <c r="J68">
+        <v>9397181.92278399</v>
       </c>
     </row>
     <row r="69">
@@ -1246,16 +1332,19 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B72">
-        <v>419603</v>
+        <v>702955</v>
       </c>
       <c r="C72">
-        <v>428874.75620416517</v>
+        <v>437877.65385392105</v>
       </c>
       <c r="D72">
-        <v>341371.64432816976</v>
+        <v>447553.2158822797</v>
       </c>
       <c r="E72">
-        <v>231344</v>
+        <v>356239.14679035696</v>
+      </c>
+      <c r="F72">
+        <v>241419</v>
       </c>
     </row>
     <row r="73">
@@ -1297,17 +1386,17 @@
       <c r="A80" t="str">
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
-      <c r="F80">
-        <v>253609.185031827</v>
-      </c>
       <c r="G80">
-        <v>394369.43856512266</v>
+        <v>264654.4351149571</v>
       </c>
       <c r="H80">
-        <v>152284.40927732212</v>
+        <v>411545.11409733474</v>
       </c>
       <c r="I80">
-        <v>40140.158612281106</v>
+        <v>158916.73761361119</v>
+      </c>
+      <c r="J80">
+        <v>41888.352748836194</v>
       </c>
     </row>
     <row r="81">
@@ -1330,28 +1419,31 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>1843311</v>
+        <v>702955</v>
       </c>
       <c r="C84">
-        <v>4169784.288023958</v>
+        <v>1923591.337533633</v>
       </c>
       <c r="D84">
-        <v>6545714.583499454</v>
+        <v>4351387.766810231</v>
       </c>
       <c r="E84">
-        <v>15293575</v>
+        <v>6830795.167384734</v>
       </c>
       <c r="F84">
-        <v>18724128.363041144</v>
+        <v>15959644</v>
       </c>
       <c r="G84">
-        <v>9115671.807349464</v>
+        <v>19539606.24225307</v>
       </c>
       <c r="H84">
-        <v>4995178.417273649</v>
+        <v>9512679.805207578</v>
       </c>
       <c r="I84">
-        <v>9045134.342812806</v>
+        <v>5212729.665749596</v>
+      </c>
+      <c r="J84">
+        <v>9439070.275532823</v>
       </c>
     </row>
     <row r="85">
@@ -1364,28 +1456,31 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>6506106343</v>
+        <v>7484113723</v>
       </c>
       <c r="C86">
-        <v>5905679648.358052</v>
+        <v>6789461898.97821</v>
       </c>
       <c r="D86">
-        <v>5216120267.7615185</v>
+        <v>6162885272.116437</v>
       </c>
       <c r="E86">
-        <v>4663320627</v>
+        <v>5443294030.469992</v>
       </c>
       <c r="F86">
-        <v>4332638233.969939</v>
+        <v>4866418725</v>
       </c>
       <c r="G86">
-        <v>2927121008.318668</v>
+        <v>4521334368.173137</v>
       </c>
       <c r="H86">
-        <v>347129501.7763642</v>
+        <v>3054603707.9551435</v>
       </c>
       <c r="I86">
-        <v>246880525.9931042</v>
+        <v>362247771.8732108</v>
+      </c>
+      <c r="J86">
+        <v>257632727.85009265</v>
       </c>
     </row>
     <row r="87">
@@ -1402,18 +1497,21 @@
         <v>268000000</v>
       </c>
       <c r="E87">
-        <v>200000000</v>
+        <v>268000000</v>
       </c>
       <c r="F87">
         <v>200000000</v>
       </c>
       <c r="G87">
+        <v>200000000</v>
+      </c>
+      <c r="H87">
         <v>40000000</v>
       </c>
-      <c r="H87">
+      <c r="I87">
         <v>30000000</v>
       </c>
-      <c r="I87">
+      <c r="J87">
         <v>30000000</v>
       </c>
     </row>
@@ -1422,28 +1520,31 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>337308349</v>
+        <v>363670888</v>
       </c>
       <c r="C88">
-        <v>337308348.3980882</v>
+        <v>363670888.2403377</v>
       </c>
       <c r="D88">
-        <v>337308386.66310847</v>
+        <v>363670887.61221135</v>
       </c>
       <c r="E88">
-        <v>327814315</v>
+        <v>363670927.5437592</v>
       </c>
       <c r="F88">
-        <v>327814275.58385855</v>
+        <v>350801815</v>
       </c>
       <c r="G88">
-        <v>169220237.6161219</v>
+        <v>350801773.7319964</v>
       </c>
       <c r="H88">
-        <v>151241249.64655444</v>
+        <v>178332249.25967482</v>
       </c>
       <c r="I88">
-        <v>151241249.64655444</v>
+        <v>159134713.4715101</v>
+      </c>
+      <c r="J88">
+        <v>159134713.4715101</v>
       </c>
     </row>
     <row r="89">
@@ -1455,8 +1556,8 @@
       <c r="A90" t="str">
         <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
       </c>
-      <c r="G90">
-        <v>318593999.0770073</v>
+      <c r="H90">
+        <v>332469483.88781357</v>
       </c>
     </row>
     <row r="91">
@@ -1479,22 +1580,25 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>939224301</v>
+        <v>980129631</v>
       </c>
       <c r="C94">
-        <v>939224301.2718467</v>
+        <v>980129630.5423672</v>
       </c>
       <c r="D94">
-        <v>940896486.5618999</v>
+        <v>980129630.8260535</v>
       </c>
       <c r="E94">
-        <v>75320491</v>
+        <v>981874643.5443075</v>
       </c>
       <c r="F94">
-        <v>75320491.04500905</v>
+        <v>78600868</v>
       </c>
       <c r="G94">
-        <v>75320491.32151757</v>
+        <v>78600867.73906247</v>
+      </c>
+      <c r="H94">
+        <v>78600868.02761357</v>
       </c>
     </row>
     <row r="95">
@@ -1512,25 +1616,28 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>27023</v>
+        <v>-91723</v>
       </c>
       <c r="C97">
-        <v>77446.15675394375</v>
+        <v>28199.912393606595</v>
       </c>
       <c r="D97">
-        <v>146056.95245863358</v>
+        <v>80819.1109677955</v>
       </c>
       <c r="E97">
-        <v>73369</v>
+        <v>152418.06105209008</v>
       </c>
       <c r="F97">
-        <v>293442.76741774083</v>
+        <v>76564</v>
       </c>
       <c r="G97">
-        <v>-60278.95131772551</v>
+        <v>306222.8595536309</v>
       </c>
       <c r="H97">
-        <v>42338.176861323125</v>
+        <v>-62904.235145555125</v>
+      </c>
+      <c r="I97">
+        <v>44182.09963343574</v>
       </c>
     </row>
     <row r="98">
@@ -1543,33 +1650,36 @@
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>56708250</v>
+        <v>59178021</v>
       </c>
       <c r="C99">
-        <v>764156.1974860879</v>
+        <v>59178021.75904752</v>
       </c>
       <c r="D99">
-        <v>764155.3699102106</v>
+        <v>797436.9175938726</v>
       </c>
       <c r="E99">
-        <v>764156</v>
+        <v>797436.0539752055</v>
       </c>
       <c r="F99">
-        <v>764155.9065617381</v>
+        <v>797437</v>
       </c>
       <c r="G99">
-        <v>764155.9322121026</v>
+        <v>797436.6139991134</v>
       </c>
       <c r="H99">
-        <v>764155.9065617381</v>
+        <v>797436.6407666089</v>
+      </c>
+      <c r="I99">
+        <v>797436.6139991134</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="H100">
-        <v>103299518.53670394</v>
+      <c r="I100">
+        <v>107798444.77063212</v>
       </c>
     </row>
     <row r="101">
@@ -1587,25 +1697,28 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>4006237942</v>
+        <v>4177761457</v>
       </c>
       <c r="C103">
-        <v>4059348297.058672</v>
+        <v>4180718609.7895412</v>
       </c>
       <c r="D103">
-        <v>4059348298.292268</v>
+        <v>4236142040.1950436</v>
       </c>
       <c r="E103">
-        <v>2323282401</v>
+        <v>4236142041.4823656</v>
       </c>
       <c r="F103">
-        <v>2323282401.3227115</v>
+        <v>2424466574</v>
       </c>
       <c r="G103">
-        <v>61782241.23367418</v>
+        <v>2424466572.2868824</v>
       </c>
       <c r="H103">
-        <v>64875125.77174843</v>
+        <v>64472996.71651116</v>
+      </c>
+      <c r="I103">
+        <v>67700583.32855402</v>
       </c>
     </row>
     <row r="104">
@@ -1613,28 +1726,31 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>898600478</v>
+        <v>1635465449</v>
       </c>
       <c r="C104">
-        <v>300957099.2752054</v>
+        <v>937736548.7345228</v>
       </c>
       <c r="D104">
-        <v>-390343116.0781266</v>
+        <v>314064457.45456666</v>
       </c>
       <c r="E104">
-        <v>1736065895</v>
+        <v>-407343436.2154676</v>
       </c>
       <c r="F104">
-        <v>1405163467.3443804</v>
+        <v>1811675467</v>
       </c>
       <c r="G104">
-        <v>2261500162.0894527</v>
+        <v>1466361494.9416425</v>
       </c>
       <c r="H104">
-        <v>-3092886.2620657445</v>
+        <v>2359993577.6579094</v>
       </c>
       <c r="I104">
-        <v>65639276.346549705</v>
+        <v>-3227588.411118061</v>
+      </c>
+      <c r="J104">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="105">
@@ -1647,28 +1763,31 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>6506106343</v>
+        <v>7484113723</v>
       </c>
       <c r="C106">
-        <v>5905679648.358052</v>
+        <v>6789461898.97821</v>
       </c>
       <c r="D106">
-        <v>5216120267.7615185</v>
+        <v>6162885272.116437</v>
       </c>
       <c r="E106">
-        <v>4663320627</v>
+        <v>5443294030.469992</v>
       </c>
       <c r="F106">
-        <v>4332638233.969939</v>
+        <v>4866418725</v>
       </c>
       <c r="G106">
-        <v>2927121008.318668</v>
+        <v>4521334368.173137</v>
       </c>
       <c r="H106">
-        <v>347129501.7763642</v>
+        <v>3054603707.9551435</v>
       </c>
       <c r="I106">
-        <v>246880525.9931042</v>
+        <v>362247771.8732108</v>
+      </c>
+      <c r="J106">
+        <v>257632727.85009265</v>
       </c>
     </row>
     <row r="107">
@@ -1676,28 +1795,31 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>6515977605</v>
+        <v>7494586234</v>
       </c>
       <c r="C107">
-        <v>5916909778.630209</v>
+        <v>6799763076.627411</v>
       </c>
       <c r="D107">
-        <v>5229614125.924358</v>
+        <v>6174604499.805576</v>
       </c>
       <c r="E107">
-        <v>4689889865</v>
+        <v>5457375576.48797</v>
       </c>
       <c r="F107">
-        <v>4360468218.762715</v>
+        <v>4894145112</v>
       </c>
       <c r="G107">
-        <v>2943808642.3327413</v>
+        <v>4550376411.361224</v>
       </c>
       <c r="H107">
-        <v>354771809.954326</v>
+        <v>3072018125.9418006</v>
       </c>
       <c r="I107">
-        <v>260818226.35728538</v>
+        <v>370222919.7510728</v>
+      </c>
+      <c r="J107">
+        <v>272177446.394971</v>
       </c>
     </row>
     <row r="108">
@@ -1707,16 +1829,16 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:M50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -1728,6 +1850,7 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1735,36 +1858,39 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -1778,37 +1904,40 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1113729174</v>
+        <v>1982114356</v>
       </c>
       <c r="C3">
-        <v>192957218.88231483</v>
+        <v>1162234583.0220122</v>
       </c>
       <c r="D3">
-        <v>92454775.78967297</v>
+        <v>201360939.50321025</v>
       </c>
       <c r="E3">
-        <v>4114980857.694452</v>
+        <v>96481389.09963061</v>
       </c>
       <c r="F3">
-        <v>3065064307</v>
+        <v>4294197524</v>
       </c>
       <c r="G3">
-        <v>1352831775.3720136</v>
+        <v>3198554747.369667</v>
       </c>
       <c r="H3">
-        <v>1210726961.890651</v>
+        <v>1411750640.1501706</v>
       </c>
       <c r="I3">
-        <v>803333357.234218</v>
+        <v>1263456842.6116207</v>
       </c>
       <c r="J3">
-        <v>577033498.5295706</v>
+        <v>838320330.7133485</v>
       </c>
       <c r="K3">
-        <v>466483373.59581345</v>
+        <v>602164604.4743445</v>
       </c>
       <c r="L3">
-        <v>110558569.10938342</v>
+        <v>486799773.0998037</v>
+      </c>
+      <c r="M3">
+        <v>115373643.3129968</v>
       </c>
     </row>
     <row r="4">
@@ -1831,34 +1960,37 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-629144319</v>
+        <v>-1379706610</v>
       </c>
       <c r="C7">
-        <v>-57388552.493408725</v>
-      </c>
-      <c r="E7">
-        <v>-1251414788.2285078</v>
+        <v>-656544968.3134841</v>
+      </c>
+      <c r="D7">
+        <v>-59887952.95526105</v>
       </c>
       <c r="F7">
-        <v>-379661373</v>
+        <v>-1305916715</v>
       </c>
       <c r="G7">
-        <v>-318652329.14387786</v>
+        <v>-396196479.21534973</v>
       </c>
       <c r="H7">
-        <v>-251299467.4739749</v>
+        <v>-332530354.3602135</v>
       </c>
       <c r="I7">
-        <v>-456924642.1423703</v>
+        <v>-262244124.16556573</v>
       </c>
       <c r="J7">
-        <v>-278887722.50416446</v>
+        <v>-476824737.4049841</v>
       </c>
       <c r="K7">
-        <v>-422798939.21516454</v>
+        <v>-291033909.7165342</v>
       </c>
       <c r="L7">
-        <v>-95629062.66234127</v>
+        <v>-441212783.4058927</v>
+      </c>
+      <c r="M7">
+        <v>-99793923.30091919</v>
       </c>
     </row>
     <row r="8">
@@ -1866,37 +1998,40 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>484584855</v>
+        <v>602407746</v>
       </c>
       <c r="C8">
-        <v>135568666.3889061</v>
+        <v>505689614.7085281</v>
       </c>
       <c r="D8">
-        <v>35066223.29626425</v>
+        <v>141472986.5479492</v>
       </c>
       <c r="E8">
-        <v>2863566069.4659443</v>
+        <v>36593436.14436956</v>
       </c>
       <c r="F8">
-        <v>2685402934</v>
+        <v>2988280809</v>
       </c>
       <c r="G8">
-        <v>1034179446.2281358</v>
+        <v>2802358268.1543174</v>
       </c>
       <c r="H8">
-        <v>959427494.416676</v>
+        <v>1079220285.789957</v>
       </c>
       <c r="I8">
-        <v>346408715.09184784</v>
+        <v>1001212718.446055</v>
       </c>
       <c r="J8">
-        <v>298145776.0254062</v>
+        <v>361495593.30836457</v>
       </c>
       <c r="K8">
-        <v>43684434.380648896</v>
+        <v>311130694.7578103</v>
       </c>
       <c r="L8">
-        <v>14929506.447042152</v>
+        <v>45586989.69391092</v>
+      </c>
+      <c r="M8">
+        <v>15579720.01207762</v>
       </c>
     </row>
     <row r="9">
@@ -1924,37 +2059,40 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>484584855</v>
+        <v>602407746</v>
       </c>
       <c r="C13">
-        <v>135568666.3889061</v>
+        <v>505689614.7085281</v>
       </c>
       <c r="D13">
-        <v>35066223.29626425</v>
+        <v>141472986.5479492</v>
       </c>
       <c r="E13">
-        <v>2863566069.4659443</v>
+        <v>36593436.14436956</v>
       </c>
       <c r="F13">
-        <v>2685402934</v>
+        <v>2988280809</v>
       </c>
       <c r="G13">
-        <v>1034179446.2281358</v>
+        <v>2802358268.1543174</v>
       </c>
       <c r="H13">
-        <v>959427494.416676</v>
+        <v>1079220285.789957</v>
       </c>
       <c r="I13">
-        <v>346408715.09184784</v>
+        <v>1001212718.446055</v>
       </c>
       <c r="J13">
-        <v>298145776.0254062</v>
+        <v>361495593.30836457</v>
       </c>
       <c r="K13">
-        <v>43684434.380648896</v>
+        <v>311130694.7578103</v>
       </c>
       <c r="L13">
-        <v>14929506.447042152</v>
+        <v>45586989.69391092</v>
+      </c>
+      <c r="M13">
+        <v>15579720.01207762</v>
       </c>
     </row>
     <row r="14"/>
@@ -1963,37 +2101,40 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-40527075</v>
+        <v>-57425649</v>
       </c>
       <c r="C15">
-        <v>-29189565.059987165</v>
+        <v>-42292120.21496962</v>
       </c>
       <c r="D15">
-        <v>-17739591.55188256</v>
+        <v>-30460836.232065946</v>
       </c>
       <c r="E15">
-        <v>-47759940.80626548</v>
+        <v>-18512190.639879063</v>
       </c>
       <c r="F15">
-        <v>-35193625</v>
+        <v>-49839994</v>
       </c>
       <c r="G15">
-        <v>-24443446.555218905</v>
+        <v>-36726386.47868271</v>
       </c>
       <c r="H15">
-        <v>-9176664.346596768</v>
+        <v>-25508013.59786027</v>
       </c>
       <c r="I15">
-        <v>-24074748.12862491</v>
+        <v>-9576328.706641082</v>
       </c>
       <c r="J15">
-        <v>-18887849.398502078</v>
+        <v>-25123257.526009943</v>
       </c>
       <c r="K15">
-        <v>-15474000.487411726</v>
+        <v>-19710457.69682839</v>
       </c>
       <c r="L15">
-        <v>-5928684.365400449</v>
+        <v>-16147927.991845332</v>
+      </c>
+      <c r="M15">
+        <v>-6186891.896297147</v>
       </c>
     </row>
     <row r="16">
@@ -2011,37 +2152,40 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>1106081024</v>
+        <v>1691186990</v>
       </c>
       <c r="C18">
-        <v>625784506.9941607</v>
+        <v>1154253338.8976307</v>
       </c>
       <c r="D18">
-        <v>206475959.4146614</v>
+        <v>653038828.9424425</v>
       </c>
       <c r="E18">
-        <v>662504048.9099029</v>
+        <v>215468451.57381943</v>
       </c>
       <c r="F18">
-        <v>604554097</v>
+        <v>691357589</v>
       </c>
       <c r="G18">
-        <v>1711279686.3837786</v>
+        <v>630883786.8702936</v>
       </c>
       <c r="H18">
-        <v>2081498239.2742922</v>
+        <v>1785809763.4230516</v>
       </c>
       <c r="I18">
-        <v>2017183342.3110838</v>
+        <v>2172152166.487119</v>
       </c>
       <c r="J18">
-        <v>2505190095.700724</v>
+        <v>2105036211.1910264</v>
       </c>
       <c r="K18">
-        <v>59319700.627830386</v>
+        <v>2614296755.6559725</v>
       </c>
       <c r="L18">
-        <v>86493105.77893722</v>
+        <v>61903206.93186497</v>
+      </c>
+      <c r="M18">
+        <v>90260074.95899707</v>
       </c>
     </row>
     <row r="19">
@@ -2049,37 +2193,40 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-312737480</v>
+        <v>-280589419</v>
       </c>
       <c r="C19">
-        <v>-358014035.1517127</v>
+        <v>-326357900.2404357</v>
       </c>
       <c r="D19">
-        <v>-593777939.0363678</v>
+        <v>-373606351.1438364</v>
       </c>
       <c r="E19">
-        <v>-505818811.35395503</v>
+        <v>-619638303.004176</v>
       </c>
       <c r="F19">
-        <v>-770957857</v>
+        <v>-527848358</v>
       </c>
       <c r="G19">
-        <v>-410654354.5291603</v>
+        <v>-804534804.6687149</v>
       </c>
       <c r="H19">
-        <v>-234247871.71523258</v>
+        <v>-428539274.75762814</v>
       </c>
       <c r="I19">
-        <v>-34189854.18043993</v>
+        <v>-244449893.08212838</v>
       </c>
       <c r="J19">
-        <v>-2994270.020624189</v>
+        <v>-35678899.18360619</v>
       </c>
       <c r="K19">
-        <v>-60182911.3131314</v>
+        <v>-3124677.210687368</v>
       </c>
       <c r="L19">
-        <v>-1899069.1060107043</v>
+        <v>-62804012.38287757</v>
+      </c>
+      <c r="M19">
+        <v>-1981777.8343968715</v>
       </c>
     </row>
     <row r="20">
@@ -2092,37 +2239,40 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>1237401324</v>
+        <v>1955579668</v>
       </c>
       <c r="C21">
-        <v>374149573.1713668</v>
+        <v>1291292933.1507535</v>
       </c>
       <c r="D21">
-        <v>-369975347.8773247</v>
+        <v>390444628.1144893</v>
       </c>
       <c r="E21">
-        <v>2972491366.2156267</v>
+        <v>-386088605.9258661</v>
       </c>
       <c r="F21">
-        <v>2483805549</v>
+        <v>3101950046</v>
       </c>
       <c r="G21">
-        <v>2310361331.5275354</v>
+        <v>2591980863.877213</v>
       </c>
       <c r="H21">
-        <v>2797501197.629139</v>
+        <v>2410982760.8575206</v>
       </c>
       <c r="I21">
-        <v>2305327455.093867</v>
+        <v>2919338663.144405</v>
       </c>
       <c r="J21">
-        <v>2781453752.307004</v>
+        <v>2405729647.789775</v>
       </c>
       <c r="K21">
-        <v>27347223.207936157</v>
+        <v>2902592315.506267</v>
       </c>
       <c r="L21">
-        <v>93594858.75456822</v>
+        <v>28538256.251052983</v>
+      </c>
+      <c r="M21">
+        <v>97671125.24038067</v>
       </c>
     </row>
     <row r="22"/>
@@ -2181,37 +2331,40 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>1237401324</v>
+        <v>1955579668</v>
       </c>
       <c r="C33">
-        <v>374149573.1713668</v>
+        <v>1291292933.1507535</v>
       </c>
       <c r="D33">
-        <v>-369975347.8773247</v>
+        <v>390444628.1144893</v>
       </c>
       <c r="E33">
-        <v>2972491366.2156267</v>
+        <v>-386088605.9258661</v>
       </c>
       <c r="F33">
-        <v>2483805549</v>
+        <v>3101950046</v>
       </c>
       <c r="G33">
-        <v>2310361331.5275354</v>
+        <v>2591980863.877213</v>
       </c>
       <c r="H33">
-        <v>2797501197.629139</v>
+        <v>2410982760.8575206</v>
       </c>
       <c r="I33">
-        <v>2305327455.093867</v>
+        <v>2919338663.144405</v>
       </c>
       <c r="J33">
-        <v>2781453752.307004</v>
+        <v>2405729647.789775</v>
       </c>
       <c r="K33">
-        <v>27347223.207936157</v>
+        <v>2902592315.506267</v>
       </c>
       <c r="L33">
-        <v>93594858.75456822</v>
+        <v>28538256.251052983</v>
+      </c>
+      <c r="M33">
+        <v>97671125.24038067</v>
       </c>
     </row>
     <row r="34"/>
@@ -2219,14 +2372,14 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
-      <c r="J35">
-        <v>-2743361.372264623</v>
-      </c>
       <c r="K35">
-        <v>-1836101.0149950914</v>
+        <v>-2862840.926687146</v>
       </c>
       <c r="L35">
-        <v>-1724024.7442758973</v>
+        <v>-1916067.3414748076</v>
+      </c>
+      <c r="M35">
+        <v>-1799109.8972353297</v>
       </c>
     </row>
     <row r="36">
@@ -2234,37 +2387,40 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-1375927</v>
+        <v>-1753642</v>
       </c>
       <c r="C36">
-        <v>-1037110.8982909613</v>
+        <v>-1435851.7137252688</v>
       </c>
       <c r="D36">
-        <v>-576577.1766475</v>
+        <v>-1082279.4091795785</v>
       </c>
       <c r="E36">
-        <v>-6854044.63776797</v>
+        <v>-601688.4087485673</v>
       </c>
       <c r="F36">
-        <v>-5643158</v>
+        <v>-7152554</v>
       </c>
       <c r="G36">
-        <v>-3303851.5420618933</v>
+        <v>-5888930.215863531</v>
       </c>
       <c r="H36">
-        <v>-2454072.404531044</v>
+        <v>-3447741.7032760037</v>
       </c>
       <c r="I36">
-        <v>-1711281.0213704344</v>
+        <v>-2560952.7741310336</v>
       </c>
       <c r="J36">
-        <v>-128132991.30358331</v>
+        <v>-1785811.1565513771</v>
       </c>
       <c r="K36">
-        <v>-28604009.787946925</v>
+        <v>-133713471.09839045</v>
       </c>
       <c r="L36">
-        <v>-26231557.663742594</v>
+        <v>-29849778.711688887</v>
+      </c>
+      <c r="M36">
+        <v>-27374000.96456281</v>
       </c>
     </row>
     <row r="37">
@@ -2272,28 +2428,31 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-337424919</v>
+        <v>-318360577</v>
       </c>
       <c r="C37">
-        <v>-72155362.99787049</v>
+        <v>-352120532.70250535</v>
       </c>
       <c r="D37">
-        <v>-19791190.126327753</v>
+        <v>-75297891.25074309</v>
       </c>
       <c r="E37">
-        <v>-1229571427.450135</v>
+        <v>-20653140.94392386</v>
       </c>
       <c r="F37">
-        <v>-1072998924</v>
+        <v>-1283122027</v>
       </c>
       <c r="G37">
-        <v>-864478605.1403724</v>
+        <v>-1119730439.079086</v>
       </c>
       <c r="H37">
-        <v>-860705753.9065888</v>
+        <v>-902128591.611062</v>
       </c>
       <c r="I37">
-        <v>-42116011.98304371</v>
+        <v>-898191424.2252496</v>
+      </c>
+      <c r="J37">
+        <v>-43950258.97531429</v>
       </c>
     </row>
     <row r="38">
@@ -2301,37 +2460,40 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>898600478</v>
+        <v>1635465449</v>
       </c>
       <c r="C38">
-        <v>300957099.2752054</v>
+        <v>937736548.7345228</v>
       </c>
       <c r="D38">
-        <v>-390343115.18029994</v>
+        <v>314064457.45456666</v>
       </c>
       <c r="E38">
-        <v>1736065894.1277235</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F38">
-        <v>1405163467</v>
+        <v>1811675465</v>
       </c>
       <c r="G38">
-        <v>1442578874.845101</v>
+        <v>1466361494.5822637</v>
       </c>
       <c r="H38">
-        <v>1934341371.3180192</v>
+        <v>1505406427.5431826</v>
       </c>
       <c r="I38">
-        <v>2261500162.0894527</v>
+        <v>2018586286.145024</v>
       </c>
       <c r="J38">
-        <v>2650577399.6311555</v>
+        <v>2359993577.6579094</v>
       </c>
       <c r="K38">
-        <v>-3092887.595005859</v>
+        <v>2766016003.481189</v>
       </c>
       <c r="L38">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M38">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="39"/>
@@ -2355,37 +2517,40 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>898600478</v>
+        <v>1635465449</v>
       </c>
       <c r="C43">
-        <v>300957099.2752054</v>
+        <v>937736548.7345228</v>
       </c>
       <c r="D43">
-        <v>-390343115.18029994</v>
+        <v>314064457.45456666</v>
       </c>
       <c r="E43">
-        <v>1736065894.1277235</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F43">
-        <v>1405163467</v>
+        <v>1811675465</v>
       </c>
       <c r="G43">
-        <v>1442578874.845101</v>
+        <v>1466361494.5822637</v>
       </c>
       <c r="H43">
-        <v>1934341371.3180192</v>
+        <v>1505406427.5431826</v>
       </c>
       <c r="I43">
-        <v>2261500162.0894527</v>
+        <v>2018586286.145024</v>
       </c>
       <c r="J43">
-        <v>2650577399.6311555</v>
+        <v>2359993577.6579094</v>
       </c>
       <c r="K43">
-        <v>-3092887.595005859</v>
+        <v>2766016003.481189</v>
       </c>
       <c r="L43">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M43">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="44">
@@ -2399,37 +2564,40 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>898600478</v>
+        <v>1635465449</v>
       </c>
       <c r="C46">
-        <v>300957099.2752054</v>
+        <v>937736548.7345228</v>
       </c>
       <c r="D46">
-        <v>-390343115.18029994</v>
+        <v>314064457.45456666</v>
       </c>
       <c r="E46">
-        <v>1736065894.1277235</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F46">
-        <v>1405163467</v>
+        <v>1811675465</v>
       </c>
       <c r="G46">
-        <v>1442578874.845101</v>
+        <v>1466361494.5822637</v>
       </c>
       <c r="H46">
-        <v>1934341371.3180192</v>
+        <v>1505406427.5431826</v>
       </c>
       <c r="I46">
-        <v>2261500162.0894527</v>
+        <v>2018586286.145024</v>
       </c>
       <c r="J46">
-        <v>2650577399.6311555</v>
+        <v>2359993577.6579094</v>
       </c>
       <c r="K46">
-        <v>-3092887.595005859</v>
+        <v>2766016003.481189</v>
       </c>
       <c r="L46">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M46">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="47">
@@ -2460,43 +2628,49 @@
       <c r="I47">
         <v>0</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>898600478</v>
+        <v>1635465449</v>
       </c>
       <c r="C48">
-        <v>300957099.2752054</v>
+        <v>937736548.7345228</v>
       </c>
       <c r="D48">
-        <v>-390343115.18029994</v>
+        <v>314064457.45456666</v>
       </c>
       <c r="E48">
-        <v>1736065894.1277235</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F48">
-        <v>1405163467</v>
+        <v>1811675465</v>
       </c>
       <c r="G48">
-        <v>1442578874.845101</v>
+        <v>1466361494.5822637</v>
       </c>
       <c r="H48">
-        <v>1934341371.3180192</v>
+        <v>1505406427.5431826</v>
       </c>
       <c r="I48">
-        <v>2261500162.0894527</v>
+        <v>2018586286.145024</v>
       </c>
       <c r="J48">
-        <v>2650577399.6311555</v>
+        <v>2359993577.6579094</v>
       </c>
       <c r="K48">
-        <v>-3092887.595005859</v>
+        <v>2766016003.481189</v>
       </c>
       <c r="L48">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M48">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="49"/>
@@ -2505,51 +2679,54 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>5334151</v>
+        <v>7224205</v>
       </c>
       <c r="C50">
-        <v>3735989.0562581215</v>
+        <v>5566465.266412649</v>
       </c>
       <c r="D50">
-        <v>1953673.422538405</v>
+        <v>3898699.777595086</v>
       </c>
       <c r="E50">
-        <v>10680043.423977949</v>
+        <v>2038760.2916515777</v>
       </c>
       <c r="F50">
-        <v>10975684</v>
+        <v>11145184</v>
       </c>
       <c r="G50">
-        <v>12228519.167114174</v>
+        <v>11453699.709873427</v>
       </c>
       <c r="H50">
-        <v>2142700.837996541</v>
+        <v>12761098.664698916</v>
       </c>
       <c r="I50">
-        <v>5964638.482039821</v>
+        <v>2236020.275957884</v>
       </c>
       <c r="J50">
-        <v>1963868.6567438329</v>
+        <v>6224411.895535565</v>
       </c>
       <c r="K50">
-        <v>1646486.2848671505</v>
+        <v>2049399.5512239924</v>
       </c>
       <c r="L50">
-        <v>130292.23032587011</v>
+        <v>1718194.4636246322</v>
+      </c>
+      <c r="M50">
+        <v>135966.74983373977</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:M50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -2561,6 +2738,7 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2568,36 +2746,39 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -2611,28 +2792,31 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>920771955.1176852</v>
+        <v>819879772.9779878</v>
       </c>
       <c r="C3">
-        <v>100502443.09264186</v>
+        <v>960873643.5188019</v>
       </c>
       <c r="D3">
-        <v>92454775.78967297</v>
+        <v>104879550.40357964</v>
       </c>
       <c r="E3">
-        <v>1049916550.6944518</v>
+        <v>96481389.09963061</v>
       </c>
       <c r="F3">
-        <v>1712232531.6279864</v>
+        <v>1095642776.630333</v>
       </c>
       <c r="G3">
-        <v>142104813.48136258</v>
+        <v>1786804107.2194965</v>
       </c>
       <c r="H3">
-        <v>1210726961.890651</v>
+        <v>148293797.5385499</v>
       </c>
       <c r="I3">
-        <v>226299858.70464742</v>
+        <v>1263456842.6116207</v>
+      </c>
+      <c r="J3">
+        <v>236155726.23900402</v>
       </c>
     </row>
     <row r="4">
@@ -2655,22 +2839,25 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-571755766.5065913</v>
-      </c>
-      <c r="E7">
-        <v>-871753415.2285078</v>
+        <v>-723161641.6865159</v>
+      </c>
+      <c r="C7">
+        <v>-596657015.358223</v>
       </c>
       <c r="F7">
-        <v>-61009043.856122136</v>
+        <v>-909720235.7846503</v>
       </c>
       <c r="G7">
-        <v>-67352861.66990295</v>
+        <v>-63666124.855136216</v>
       </c>
       <c r="H7">
-        <v>-251299467.4739749</v>
+        <v>-70286230.19464779</v>
       </c>
       <c r="I7">
-        <v>-178036919.63820583</v>
+        <v>-262244124.16556573</v>
+      </c>
+      <c r="J7">
+        <v>-185790827.68844992</v>
       </c>
     </row>
     <row r="8">
@@ -2678,28 +2865,31 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>349016188.6110939</v>
+        <v>96718131.2914719</v>
       </c>
       <c r="C8">
-        <v>100502443.09264183</v>
+        <v>364216628.1605789</v>
       </c>
       <c r="D8">
-        <v>35066223.29626425</v>
+        <v>104879550.40357964</v>
       </c>
       <c r="E8">
-        <v>178163135.4659443</v>
+        <v>36593436.14436956</v>
       </c>
       <c r="F8">
-        <v>1651223487.7718642</v>
+        <v>185922540.84568262</v>
       </c>
       <c r="G8">
-        <v>74751951.81145978</v>
+        <v>1723137982.3643603</v>
       </c>
       <c r="H8">
-        <v>959427494.416676</v>
+        <v>78007567.34390199</v>
       </c>
       <c r="I8">
-        <v>48262939.066441655</v>
+        <v>1001212718.446055</v>
+      </c>
+      <c r="J8">
+        <v>50364898.550554276</v>
       </c>
     </row>
     <row r="9">
@@ -2727,28 +2917,31 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>349016188.6110939</v>
+        <v>96718131.2914719</v>
       </c>
       <c r="C13">
-        <v>100502443.09264183</v>
+        <v>364216628.1605789</v>
       </c>
       <c r="D13">
-        <v>35066223.29626425</v>
+        <v>104879550.40357964</v>
       </c>
       <c r="E13">
-        <v>178163135.4659443</v>
+        <v>36593436.14436956</v>
       </c>
       <c r="F13">
-        <v>1651223487.7718642</v>
+        <v>185922540.84568262</v>
       </c>
       <c r="G13">
-        <v>74751951.81145978</v>
+        <v>1723137982.3643603</v>
       </c>
       <c r="H13">
-        <v>959427494.416676</v>
+        <v>78007567.34390199</v>
       </c>
       <c r="I13">
-        <v>48262939.066441655</v>
+        <v>1001212718.446055</v>
+      </c>
+      <c r="J13">
+        <v>50364898.550554276</v>
       </c>
     </row>
     <row r="14"/>
@@ -2757,28 +2950,31 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-11337509.940012835</v>
+        <v>-15133528.78503038</v>
       </c>
       <c r="C15">
-        <v>-11449973.508104604</v>
+        <v>-11831283.982903674</v>
       </c>
       <c r="D15">
-        <v>-17739591.55188256</v>
+        <v>-11948645.592186883</v>
       </c>
       <c r="E15">
-        <v>-12566315.80626548</v>
+        <v>-18512190.639879063</v>
       </c>
       <c r="F15">
-        <v>-10750178.444781095</v>
+        <v>-13113607.521317288</v>
       </c>
       <c r="G15">
-        <v>-15266782.208622137</v>
+        <v>-11218372.880822442</v>
       </c>
       <c r="H15">
-        <v>-9176664.346596768</v>
+        <v>-15931684.891219188</v>
       </c>
       <c r="I15">
-        <v>-5186898.730122831</v>
+        <v>-9576328.706641082</v>
+      </c>
+      <c r="J15">
+        <v>-5412799.829181552</v>
       </c>
     </row>
     <row r="16">
@@ -2796,28 +2992,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>480296517.00583935</v>
+        <v>536933651.1023693</v>
       </c>
       <c r="C18">
-        <v>419308547.57949924</v>
+        <v>501214509.95518816</v>
       </c>
       <c r="D18">
-        <v>206475959.4146614</v>
+        <v>437570377.36862314</v>
       </c>
       <c r="E18">
-        <v>57949951.90990293</v>
+        <v>215468451.57381943</v>
       </c>
       <c r="F18">
-        <v>-1106725589.3837786</v>
+        <v>60473802.12970638</v>
       </c>
       <c r="G18">
-        <v>-370218552.89051366</v>
+        <v>-1154925976.552758</v>
       </c>
       <c r="H18">
-        <v>2081498239.2742922</v>
+        <v>-386342403.0640676</v>
       </c>
       <c r="I18">
-        <v>-488006753.38964033</v>
+        <v>2172152166.487119</v>
+      </c>
+      <c r="J18">
+        <v>-509260544.46494603</v>
       </c>
     </row>
     <row r="19">
@@ -2825,28 +3024,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>45276555.151712716</v>
+        <v>45768481.24043572</v>
       </c>
       <c r="C19">
-        <v>235763903.88465506</v>
+        <v>47248450.90340066</v>
       </c>
       <c r="D19">
-        <v>-593777939.0363678</v>
+        <v>246031951.86033964</v>
       </c>
       <c r="E19">
-        <v>265139045.64604497</v>
+        <v>-619638303.004176</v>
       </c>
       <c r="F19">
-        <v>-360303502.4708397</v>
+        <v>276686446.6687149</v>
       </c>
       <c r="G19">
-        <v>-176406482.81392774</v>
+        <v>-375995529.91108674</v>
       </c>
       <c r="H19">
-        <v>-234247871.71523258</v>
+        <v>-184089381.67549977</v>
       </c>
       <c r="I19">
-        <v>-31195584.159815736</v>
+        <v>-244449893.08212838</v>
+      </c>
+      <c r="J19">
+        <v>-32554221.972918823</v>
       </c>
     </row>
     <row r="20">
@@ -2859,28 +3061,31 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>863251750.8286332</v>
+        <v>664286734.8492465</v>
       </c>
       <c r="C21">
-        <v>744124921.0486915</v>
+        <v>900848305.0362642</v>
       </c>
       <c r="D21">
-        <v>-369975347.8773247</v>
+        <v>776533234.0403554</v>
       </c>
       <c r="E21">
-        <v>488685817.2156267</v>
+        <v>-386088605.9258661</v>
       </c>
       <c r="F21">
-        <v>173444217.47246456</v>
+        <v>509969182.122787</v>
       </c>
       <c r="G21">
-        <v>-487139866.1016035</v>
+        <v>180998103.01969242</v>
       </c>
       <c r="H21">
-        <v>2797501197.629139</v>
+        <v>-508355902.2868843</v>
       </c>
       <c r="I21">
-        <v>-476126297.21313715</v>
+        <v>2919338663.144405</v>
+      </c>
+      <c r="J21">
+        <v>-496862667.7164922</v>
       </c>
     </row>
     <row r="22"/>
@@ -2939,28 +3144,31 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>863251750.8286332</v>
+        <v>664286734.8492465</v>
       </c>
       <c r="C33">
-        <v>744124921.0486915</v>
+        <v>900848305.0362642</v>
       </c>
       <c r="D33">
-        <v>-369975347.8773247</v>
+        <v>776533234.0403554</v>
       </c>
       <c r="E33">
-        <v>488685817.2156267</v>
+        <v>-386088605.9258661</v>
       </c>
       <c r="F33">
-        <v>173444217.47246456</v>
+        <v>509969182.122787</v>
       </c>
       <c r="G33">
-        <v>-487139866.1016035</v>
+        <v>180998103.01969242</v>
       </c>
       <c r="H33">
-        <v>2797501197.629139</v>
+        <v>-508355902.2868843</v>
       </c>
       <c r="I33">
-        <v>-476126297.21313715</v>
+        <v>2919338663.144405</v>
+      </c>
+      <c r="J33">
+        <v>-496862667.7164922</v>
       </c>
     </row>
     <row r="34"/>
@@ -2974,28 +3182,31 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-338816.1017090387</v>
+        <v>-317790.28627473116</v>
       </c>
       <c r="C36">
-        <v>-460533.72164346126</v>
+        <v>-353572.3045456903</v>
       </c>
       <c r="D36">
-        <v>-576577.1766475</v>
+        <v>-480591.0004310112</v>
       </c>
       <c r="E36">
-        <v>-1210886.6377679696</v>
+        <v>-601688.4087485673</v>
       </c>
       <c r="F36">
-        <v>-2339306.4579381067</v>
+        <v>-1263623.7841364685</v>
       </c>
       <c r="G36">
-        <v>-849779.1375308493</v>
+        <v>-2441188.5125875277</v>
       </c>
       <c r="H36">
-        <v>-2454072.404531044</v>
+        <v>-886788.9291449701</v>
       </c>
       <c r="I36">
-        <v>126421710.28221287</v>
+        <v>-2560952.7741310336</v>
+      </c>
+      <c r="J36">
+        <v>131927659.94183907</v>
       </c>
     </row>
     <row r="37">
@@ -3003,25 +3214,28 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-265269556.0021295</v>
+        <v>33759955.70250535</v>
       </c>
       <c r="C37">
-        <v>-52364172.87154274</v>
+        <v>-276822641.45176226</v>
       </c>
       <c r="D37">
-        <v>-19791190.126327753</v>
+        <v>-54644750.30681923</v>
       </c>
       <c r="E37">
-        <v>-156572503.450135</v>
+        <v>-20653140.94392386</v>
       </c>
       <c r="F37">
-        <v>-208520318.8596276</v>
+        <v>-163391587.92091393</v>
       </c>
       <c r="G37">
-        <v>-3772851.2337836027</v>
+        <v>-217601847.46802402</v>
       </c>
       <c r="H37">
-        <v>-860705753.9065888</v>
+        <v>-3937167.385812402</v>
+      </c>
+      <c r="I37">
+        <v>-898191424.2252496</v>
       </c>
     </row>
     <row r="38">
@@ -3029,28 +3243,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>597643378.7247946</v>
+        <v>697728900.2654772</v>
       </c>
       <c r="C38">
-        <v>691300214.4555054</v>
+        <v>623672091.2799561</v>
       </c>
       <c r="D38">
-        <v>-390343115.18029994</v>
+        <v>721407892.7331052</v>
       </c>
       <c r="E38">
-        <v>330902427.12772346</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F38">
-        <v>-37415407.84510112</v>
+        <v>345313970.4177363</v>
       </c>
       <c r="G38">
-        <v>-491762496.47291803</v>
+        <v>-39044932.9609189</v>
       </c>
       <c r="H38">
-        <v>1934341371.3180192</v>
+        <v>-513179858.60184145</v>
       </c>
       <c r="I38">
-        <v>-389077237.54170275</v>
+        <v>2018586286.145024</v>
+      </c>
+      <c r="J38">
+        <v>-406022425.8232794</v>
       </c>
     </row>
     <row r="39"/>
@@ -3074,28 +3291,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>597643378.7247946</v>
+        <v>697728900.2654772</v>
       </c>
       <c r="C43">
-        <v>691300214.4555054</v>
+        <v>623672091.2799561</v>
       </c>
       <c r="D43">
-        <v>-390343115.18029994</v>
+        <v>721407892.7331052</v>
       </c>
       <c r="E43">
-        <v>330902427.12772346</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F43">
-        <v>-37415407.84510112</v>
+        <v>345313970.4177363</v>
       </c>
       <c r="G43">
-        <v>-491762496.47291803</v>
+        <v>-39044932.9609189</v>
       </c>
       <c r="H43">
-        <v>1934341371.3180192</v>
+        <v>-513179858.60184145</v>
       </c>
       <c r="I43">
-        <v>-389077237.54170275</v>
+        <v>2018586286.145024</v>
+      </c>
+      <c r="J43">
+        <v>-406022425.8232794</v>
       </c>
     </row>
     <row r="44">
@@ -3109,28 +3329,31 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>597643378.7247946</v>
+        <v>697728900.2654772</v>
       </c>
       <c r="C46">
-        <v>691300214.4555054</v>
+        <v>623672091.2799561</v>
       </c>
       <c r="D46">
-        <v>-390343115.18029994</v>
+        <v>721407892.7331052</v>
       </c>
       <c r="E46">
-        <v>330902427.12772346</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F46">
-        <v>-37415407.84510112</v>
+        <v>345313970.4177363</v>
       </c>
       <c r="G46">
-        <v>-491762496.47291803</v>
+        <v>-39044932.9609189</v>
       </c>
       <c r="H46">
-        <v>1934341371.3180192</v>
+        <v>-513179858.60184145</v>
       </c>
       <c r="I46">
-        <v>-389077237.54170275</v>
+        <v>2018586286.145024</v>
+      </c>
+      <c r="J46">
+        <v>-406022425.8232794</v>
       </c>
     </row>
     <row r="47">
@@ -3158,34 +3381,40 @@
       <c r="H47">
         <v>0</v>
       </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>597643378.7247946</v>
+        <v>697728900.2654772</v>
       </c>
       <c r="C48">
-        <v>691300214.4555054</v>
+        <v>623672091.2799561</v>
       </c>
       <c r="D48">
-        <v>-390343115.18029994</v>
+        <v>721407892.7331052</v>
       </c>
       <c r="E48">
-        <v>330902427.12772346</v>
+        <v>-407343435.2785385</v>
       </c>
       <c r="F48">
-        <v>-37415407.84510112</v>
+        <v>345313970.4177363</v>
       </c>
       <c r="G48">
-        <v>-491762496.47291803</v>
+        <v>-39044932.9609189</v>
       </c>
       <c r="H48">
-        <v>1934341371.3180192</v>
+        <v>-513179858.60184145</v>
       </c>
       <c r="I48">
-        <v>-389077237.54170275</v>
+        <v>2018586286.145024</v>
+      </c>
+      <c r="J48">
+        <v>-406022425.8232794</v>
       </c>
     </row>
     <row r="49"/>
@@ -3194,42 +3423,45 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>1598161.9437418785</v>
+        <v>1657739.7335873507</v>
       </c>
       <c r="C50">
-        <v>1782315.6337197165</v>
+        <v>1667765.4888175633</v>
       </c>
       <c r="D50">
-        <v>1953673.422538405</v>
+        <v>1859939.4859435083</v>
       </c>
       <c r="E50">
-        <v>-295640.5760220513</v>
+        <v>2038760.2916515777</v>
       </c>
       <c r="F50">
-        <v>-1252835.167114174</v>
+        <v>-308515.7098734267</v>
       </c>
       <c r="G50">
-        <v>10085818.329117633</v>
+        <v>-1307398.9548254889</v>
       </c>
       <c r="H50">
-        <v>2142700.837996541</v>
+        <v>10525078.388741031</v>
       </c>
       <c r="I50">
-        <v>4000769.8252959885</v>
+        <v>2236020.275957884</v>
+      </c>
+      <c r="J50">
+        <v>4175012.3443115726</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:M50"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -3241,6 +3473,7 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3248,36 +3481,39 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -3291,28 +3527,31 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>2163645724.694452</v>
+        <v>1982114356</v>
       </c>
       <c r="C3">
-        <v>2955106301.204753</v>
+        <v>2257877359.652345</v>
       </c>
       <c r="D3">
-        <v>2996708671.5934734</v>
+        <v>3083807823.3530397</v>
       </c>
       <c r="E3">
-        <v>4114980857.694452</v>
+        <v>3127222070.48801</v>
       </c>
       <c r="F3">
-        <v>3291364165.7046475</v>
-      </c>
-      <c r="I3">
-        <v>803333357.234218</v>
-      </c>
-      <c r="K3">
-        <v>466483373.59581345</v>
+        <v>4294197524</v>
+      </c>
+      <c r="G3">
+        <v>3434710473.608671</v>
+      </c>
+      <c r="J3">
+        <v>838320330.7133485</v>
       </c>
       <c r="L3">
-        <v>110558569.10938342</v>
+        <v>486799773.0998037</v>
+      </c>
+      <c r="M3">
+        <v>115373643.3129968</v>
       </c>
     </row>
     <row r="4">
@@ -3335,25 +3574,28 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-1500897734.2285078</v>
+        <v>-1379706610</v>
       </c>
       <c r="C7">
-        <v>-990151011.5780386</v>
-      </c>
-      <c r="E7">
-        <v>-1251414788.2285078</v>
+        <v>-1566265204.0981345</v>
+      </c>
+      <c r="D7">
+        <v>-1033274313.5950475</v>
       </c>
       <c r="F7">
-        <v>-557698292.6382058</v>
-      </c>
-      <c r="I7">
-        <v>-456924642.1423703</v>
-      </c>
-      <c r="K7">
-        <v>-422798939.21516454</v>
+        <v>-1305916715</v>
+      </c>
+      <c r="G7">
+        <v>-581987306.9037997</v>
+      </c>
+      <c r="J7">
+        <v>-476824737.4049841</v>
       </c>
       <c r="L7">
-        <v>-95629062.66234127</v>
+        <v>-441212783.4058927</v>
+      </c>
+      <c r="M7">
+        <v>-99793923.30091919</v>
       </c>
     </row>
     <row r="8">
@@ -3361,28 +3603,31 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>662747990.4659443</v>
+        <v>602407746</v>
       </c>
       <c r="C8">
-        <v>1964955289.6267145</v>
+        <v>691612155.5542107</v>
       </c>
       <c r="D8">
-        <v>1939204798.3455324</v>
+        <v>2050533509.7579923</v>
       </c>
       <c r="E8">
-        <v>2863566069.4659443</v>
+        <v>2023661526.6983147</v>
       </c>
       <c r="F8">
-        <v>2733665873.0664415</v>
-      </c>
-      <c r="I8">
-        <v>346408715.09184784</v>
-      </c>
-      <c r="K8">
-        <v>43684434.380648896</v>
+        <v>2988280809</v>
+      </c>
+      <c r="G8">
+        <v>2852723166.7048717</v>
+      </c>
+      <c r="J8">
+        <v>361495593.30836457</v>
       </c>
       <c r="L8">
-        <v>14929506.447042152</v>
+        <v>45586989.69391092</v>
+      </c>
+      <c r="M8">
+        <v>15579720.01207762</v>
       </c>
     </row>
     <row r="9">
@@ -3410,28 +3655,31 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>662747990.4659443</v>
+        <v>602407746</v>
       </c>
       <c r="C13">
-        <v>1964955289.6267145</v>
+        <v>691612155.5542107</v>
       </c>
       <c r="D13">
-        <v>1939204798.3455324</v>
+        <v>2050533509.7579923</v>
       </c>
       <c r="E13">
-        <v>2863566069.4659443</v>
+        <v>2023661526.6983147</v>
       </c>
       <c r="F13">
-        <v>2733665873.0664415</v>
-      </c>
-      <c r="I13">
-        <v>346408715.09184784</v>
-      </c>
-      <c r="K13">
-        <v>43684434.380648896</v>
+        <v>2988280809</v>
+      </c>
+      <c r="G13">
+        <v>2852723166.7048717</v>
+      </c>
+      <c r="J13">
+        <v>361495593.30836457</v>
       </c>
       <c r="L13">
-        <v>14929506.447042152</v>
+        <v>45586989.69391092</v>
+      </c>
+      <c r="M13">
+        <v>15579720.01207762</v>
       </c>
     </row>
     <row r="14"/>
@@ -3440,28 +3688,31 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-53093390.80626548</v>
+        <v>-57425649</v>
       </c>
       <c r="C15">
-        <v>-52506059.31103374</v>
+        <v>-55405727.73628691</v>
       </c>
       <c r="D15">
-        <v>-56322868.011551276</v>
+        <v>-54792816.63420568</v>
       </c>
       <c r="E15">
-        <v>-47759940.80626548</v>
+        <v>-58775855.933237985</v>
       </c>
       <c r="F15">
-        <v>-40380523.730122834</v>
-      </c>
-      <c r="I15">
-        <v>-24074748.12862491</v>
-      </c>
-      <c r="K15">
-        <v>-15474000.487411726</v>
+        <v>-49839994</v>
+      </c>
+      <c r="G15">
+        <v>-42139186.30786426</v>
+      </c>
+      <c r="J15">
+        <v>-25123257.526009943</v>
       </c>
       <c r="L15">
-        <v>-5928684.365400449</v>
+        <v>-16147927.991845332</v>
+      </c>
+      <c r="M15">
+        <v>-6186891.896297147</v>
       </c>
     </row>
     <row r="16">
@@ -3479,28 +3730,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>1164030975.909903</v>
+        <v>1691186990</v>
       </c>
       <c r="C18">
-        <v>-422991130.479715</v>
+        <v>1214727141.027337</v>
       </c>
       <c r="D18">
-        <v>-1212518230.949728</v>
+        <v>-441413345.48060906</v>
       </c>
       <c r="E18">
-        <v>662504048.9099029</v>
+        <v>-1265326125.9132998</v>
       </c>
       <c r="F18">
-        <v>116547343.61035967</v>
-      </c>
-      <c r="I18">
-        <v>2017183342.3110838</v>
-      </c>
-      <c r="K18">
-        <v>59319700.627830386</v>
+        <v>691357589</v>
+      </c>
+      <c r="G18">
+        <v>121623242.40534759</v>
+      </c>
+      <c r="J18">
+        <v>2105036211.1910264</v>
       </c>
       <c r="L18">
-        <v>86493105.77893722</v>
+        <v>61903206.93186497</v>
+      </c>
+      <c r="M18">
+        <v>90260074.95899707</v>
       </c>
     </row>
     <row r="19">
@@ -3508,28 +3762,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-47598434.35395503</v>
+        <v>-280589419</v>
       </c>
       <c r="C19">
-        <v>-453178491.9765074</v>
+        <v>-49671453.57172084</v>
       </c>
       <c r="D19">
-        <v>-865348878.6750902</v>
+        <v>-472915434.38620824</v>
       </c>
       <c r="E19">
-        <v>-505818811.35395503</v>
+        <v>-903036767.9220476</v>
       </c>
       <c r="F19">
-        <v>-802153441.1598158</v>
-      </c>
-      <c r="I19">
-        <v>-34189854.18043993</v>
-      </c>
-      <c r="K19">
-        <v>-60182911.3131314</v>
+        <v>-527848358</v>
+      </c>
+      <c r="G19">
+        <v>-837089026.6416337</v>
+      </c>
+      <c r="J19">
+        <v>-35678899.18360619</v>
       </c>
       <c r="L19">
-        <v>-1899069.1060107043</v>
+        <v>-62804012.38287757</v>
+      </c>
+      <c r="M19">
+        <v>-1981777.8343968715</v>
       </c>
     </row>
     <row r="20">
@@ -3542,28 +3799,31 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>1726087141.2156267</v>
+        <v>1955579668</v>
       </c>
       <c r="C21">
-        <v>1036279607.8594581</v>
+        <v>1801262115.2735405</v>
       </c>
       <c r="D21">
-        <v>-194985179.29083693</v>
+        <v>1081411913.2569687</v>
       </c>
       <c r="E21">
-        <v>2972491366.2156267</v>
+        <v>-203477223.07027102</v>
       </c>
       <c r="F21">
-        <v>2007679251.7868629</v>
-      </c>
-      <c r="I21">
-        <v>2305327455.093867</v>
-      </c>
-      <c r="K21">
-        <v>27347223.207936157</v>
+        <v>3101950046</v>
+      </c>
+      <c r="G21">
+        <v>2095118196.1607208</v>
+      </c>
+      <c r="J21">
+        <v>2405729647.789775</v>
       </c>
       <c r="L21">
-        <v>93594858.75456822</v>
+        <v>28538256.251052983</v>
+      </c>
+      <c r="M21">
+        <v>97671125.24038067</v>
       </c>
     </row>
     <row r="22"/>
@@ -3622,28 +3882,31 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>1726087141.2156267</v>
+        <v>1955579668</v>
       </c>
       <c r="C33">
-        <v>1036279607.8594581</v>
+        <v>1801262115.2735405</v>
       </c>
       <c r="D33">
-        <v>-194985179.29083693</v>
+        <v>1081411913.2569687</v>
       </c>
       <c r="E33">
-        <v>2972491366.2156267</v>
+        <v>-203477223.07027102</v>
       </c>
       <c r="F33">
-        <v>2007679251.7868629</v>
-      </c>
-      <c r="I33">
-        <v>2305327455.093867</v>
-      </c>
-      <c r="K33">
-        <v>27347223.207936157</v>
+        <v>3101950046</v>
+      </c>
+      <c r="G33">
+        <v>2095118196.1607208</v>
+      </c>
+      <c r="J33">
+        <v>2405729647.789775</v>
       </c>
       <c r="L33">
-        <v>93594858.75456822</v>
+        <v>28538256.251052983</v>
+      </c>
+      <c r="M33">
+        <v>97671125.24038067</v>
       </c>
     </row>
     <row r="34"/>
@@ -3651,11 +3914,11 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
-      <c r="K35">
-        <v>-1836101.0149950914</v>
-      </c>
       <c r="L35">
-        <v>-1724024.7442758973</v>
+        <v>-1916067.3414748076</v>
+      </c>
+      <c r="M35">
+        <v>-1799109.8972353297</v>
       </c>
     </row>
     <row r="36">
@@ -3663,28 +3926,31 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-2586813.6377679696</v>
+        <v>-1753642</v>
       </c>
       <c r="C36">
-        <v>-4587303.993997037</v>
+        <v>-2699475.4978617374</v>
       </c>
       <c r="D36">
-        <v>-4976549.409884426</v>
+        <v>-4787091.705903575</v>
       </c>
       <c r="E36">
-        <v>-6854044.63776797</v>
+        <v>-5193289.634617534</v>
       </c>
       <c r="F36">
-        <v>120778552.28221287</v>
-      </c>
-      <c r="I36">
-        <v>-1711281.0213704344</v>
-      </c>
-      <c r="K36">
-        <v>-28604009.787946925</v>
+        <v>-7152554</v>
+      </c>
+      <c r="G36">
+        <v>126038729.72597554</v>
+      </c>
+      <c r="J36">
+        <v>-1785811.1565513771</v>
       </c>
       <c r="L36">
-        <v>-26231557.663742594</v>
+        <v>-29849778.711688887</v>
+      </c>
+      <c r="M36">
+        <v>-27374000.96456281</v>
       </c>
     </row>
     <row r="37">
@@ -3692,19 +3958,22 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-493997422.450135</v>
+        <v>-318360577</v>
       </c>
       <c r="C37">
-        <v>-437248185.3076331</v>
+        <v>-515512120.6234193</v>
       </c>
       <c r="D37">
-        <v>-388656863.66987395</v>
+        <v>-456291326.63968104</v>
       </c>
       <c r="E37">
-        <v>-1229571427.450135</v>
-      </c>
-      <c r="I37">
-        <v>-42116011.98304371</v>
+        <v>-405583743.7186742</v>
+      </c>
+      <c r="F37">
+        <v>-1283122027</v>
+      </c>
+      <c r="J37">
+        <v>-43950258.97531429</v>
       </c>
     </row>
     <row r="38">
@@ -3712,28 +3981,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>1229502905.1277235</v>
+        <v>1635465449</v>
       </c>
       <c r="C38">
-        <v>594444118.5578277</v>
+        <v>1283050519.152259</v>
       </c>
       <c r="D38">
-        <v>-588618592.3705957</v>
+        <v>620333494.9113841</v>
       </c>
       <c r="E38">
-        <v>1736065894.1277235</v>
+        <v>-614254256.4235625</v>
       </c>
       <c r="F38">
-        <v>1016086229.4582973</v>
-      </c>
-      <c r="I38">
-        <v>2261500162.0894527</v>
-      </c>
-      <c r="K38">
-        <v>-3092887.595005859</v>
+        <v>1811675465</v>
+      </c>
+      <c r="G38">
+        <v>1060339068.7589843</v>
+      </c>
+      <c r="J38">
+        <v>2359993577.6579094</v>
       </c>
       <c r="L38">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M38">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="39"/>
@@ -3757,28 +4029,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>1229502905.1277235</v>
+        <v>1635465449</v>
       </c>
       <c r="C43">
-        <v>594444118.5578277</v>
+        <v>1283050519.152259</v>
       </c>
       <c r="D43">
-        <v>-588618592.3705957</v>
+        <v>620333494.9113841</v>
       </c>
       <c r="E43">
-        <v>1736065894.1277235</v>
+        <v>-614254256.4235625</v>
       </c>
       <c r="F43">
-        <v>1016086229.4582973</v>
-      </c>
-      <c r="I43">
-        <v>2261500162.0894527</v>
-      </c>
-      <c r="K43">
-        <v>-3092887.595005859</v>
+        <v>1811675465</v>
+      </c>
+      <c r="G43">
+        <v>1060339068.7589843</v>
+      </c>
+      <c r="J43">
+        <v>2359993577.6579094</v>
       </c>
       <c r="L43">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M43">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="44">
@@ -3792,28 +4067,31 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>1229502905.1277235</v>
+        <v>1635465449</v>
       </c>
       <c r="C46">
-        <v>594444118.5578277</v>
+        <v>1283050519.152259</v>
       </c>
       <c r="D46">
-        <v>-588618592.3705957</v>
+        <v>620333494.9113841</v>
       </c>
       <c r="E46">
-        <v>1736065894.1277235</v>
+        <v>-614254256.4235625</v>
       </c>
       <c r="F46">
-        <v>1016086229.4582973</v>
-      </c>
-      <c r="I46">
-        <v>2261500162.0894527</v>
-      </c>
-      <c r="K46">
-        <v>-3092887.595005859</v>
+        <v>1811675465</v>
+      </c>
+      <c r="G46">
+        <v>1060339068.7589843</v>
+      </c>
+      <c r="J46">
+        <v>2359993577.6579094</v>
       </c>
       <c r="L46">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M46">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="47">
@@ -3832,7 +4110,10 @@
       <c r="E47">
         <v>0</v>
       </c>
-      <c r="I47">
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="J47">
         <v>0</v>
       </c>
     </row>
@@ -3841,28 +4122,31 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>1229502905.1277235</v>
+        <v>1635465449</v>
       </c>
       <c r="C48">
-        <v>594444118.5578277</v>
+        <v>1283050519.152259</v>
       </c>
       <c r="D48">
-        <v>-588618592.3705957</v>
+        <v>620333494.9113841</v>
       </c>
       <c r="E48">
-        <v>1736065894.1277235</v>
+        <v>-614254256.4235625</v>
       </c>
       <c r="F48">
-        <v>1016086229.4582973</v>
-      </c>
-      <c r="I48">
-        <v>2261500162.0894527</v>
-      </c>
-      <c r="K48">
-        <v>-3092887.595005859</v>
+        <v>1811675465</v>
+      </c>
+      <c r="G48">
+        <v>1060339068.7589843</v>
+      </c>
+      <c r="J48">
+        <v>2359993577.6579094</v>
       </c>
       <c r="L48">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M48">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="49"/>
@@ -3871,42 +4155,45 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>5038510.423977949</v>
+        <v>7224205</v>
       </c>
       <c r="C50">
-        <v>2187513.3131218962</v>
+        <v>5257949.556539223</v>
       </c>
       <c r="D50">
-        <v>10491016.008519813</v>
+        <v>2282785.1128961705</v>
       </c>
       <c r="E50">
-        <v>10680043.423977949</v>
+        <v>10947924.015693694</v>
       </c>
       <c r="F50">
-        <v>14976453.825295988</v>
-      </c>
-      <c r="I50">
-        <v>5964638.482039821</v>
-      </c>
-      <c r="K50">
-        <v>1646486.2848671505</v>
+        <v>11145184</v>
+      </c>
+      <c r="G50">
+        <v>15628712.054185</v>
+      </c>
+      <c r="J50">
+        <v>6224411.895535565</v>
       </c>
       <c r="L50">
-        <v>130292.23032587011</v>
+        <v>1718194.4636246322</v>
+      </c>
+      <c r="M50">
+        <v>135966.74983373977</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:M129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -3918,6 +4205,7 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3925,36 +4213,39 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -3968,37 +4259,40 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-136981649</v>
+        <v>479436490</v>
       </c>
       <c r="C3">
-        <v>-495959224.58418924</v>
+        <v>-142947507.72792688</v>
       </c>
       <c r="D3">
-        <v>-764279187.2035848</v>
+        <v>-517559363.65596694</v>
       </c>
       <c r="E3">
-        <v>1574854424.5341978</v>
+        <v>-797565263.7900287</v>
       </c>
       <c r="F3">
-        <v>1256011395</v>
+        <v>2011037307</v>
       </c>
       <c r="G3">
-        <v>1279395896.5045128</v>
+        <v>1310713514.5754213</v>
       </c>
       <c r="H3">
-        <v>1672694765.0648224</v>
+        <v>1335116463.685269</v>
       </c>
       <c r="I3">
-        <v>2391477238.5059175</v>
+        <v>1745544382.0476024</v>
       </c>
       <c r="J3">
-        <v>2937412188.4093328</v>
+        <v>2495631447.921071</v>
       </c>
       <c r="K3">
-        <v>1387101.4703185863</v>
+        <v>3065343092.0717688</v>
       </c>
       <c r="L3">
-        <v>41518779.917590335</v>
+        <v>1447512.8573447445</v>
+      </c>
+      <c r="M3">
+        <v>43327016.1109233</v>
       </c>
     </row>
     <row r="4">
@@ -4006,37 +4300,40 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>898600478</v>
+        <v>1635465449</v>
       </c>
       <c r="C4">
-        <v>300957099.2752054</v>
+        <v>937736548.7345228</v>
       </c>
       <c r="D4">
-        <v>-390343116.0781266</v>
+        <v>314064457.45456666</v>
       </c>
       <c r="E4">
-        <v>1736065894.1277235</v>
+        <v>-407343436.2154676</v>
       </c>
       <c r="F4">
-        <v>1405163467</v>
+        <v>1811675465</v>
       </c>
       <c r="G4">
-        <v>1442578874.845101</v>
+        <v>1466361494.5822637</v>
       </c>
       <c r="H4">
-        <v>1934341370.6706693</v>
+        <v>1505406427.5431826</v>
       </c>
       <c r="I4">
-        <v>2261500162.0894527</v>
+        <v>2018586285.4694808</v>
       </c>
       <c r="J4">
-        <v>2650577399.6311555</v>
+        <v>2359993577.6579094</v>
       </c>
       <c r="K4">
-        <v>-3092887.595005859</v>
+        <v>2766016003.481189</v>
       </c>
       <c r="L4">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M4">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="5">
@@ -4044,37 +4341,40 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>83191448</v>
+        <v>41595964</v>
       </c>
       <c r="C5">
-        <v>54765618.65597972</v>
+        <v>86814622.56216107</v>
       </c>
       <c r="D5">
-        <v>17289522.37454352</v>
+        <v>57150784.453254454</v>
       </c>
       <c r="E5">
-        <v>-158868639.30878547</v>
+        <v>18042519.93817964</v>
       </c>
       <c r="F5">
-        <v>-147337738</v>
+        <v>201794946</v>
       </c>
       <c r="G5">
-        <v>-165931827.76041532</v>
+        <v>-153754627.68279472</v>
       </c>
       <c r="H5">
-        <v>-229958015.67222282</v>
+        <v>-173158531.84897053</v>
       </c>
       <c r="I5">
-        <v>108755532.8197426</v>
+        <v>-239973204.1654996</v>
       </c>
       <c r="J5">
-        <v>4928254.1599977845</v>
+        <v>113492080.73998995</v>
       </c>
       <c r="K5">
-        <v>7632173.834270199</v>
+        <v>5142890.706633786</v>
       </c>
       <c r="L5">
-        <v>2124778.521502993</v>
+        <v>7964572.160722205</v>
+      </c>
+      <c r="M5">
+        <v>2217317.4022943918</v>
       </c>
     </row>
     <row r="6">
@@ -4082,37 +4382,40 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>5334151</v>
+        <v>7224205</v>
       </c>
       <c r="C6">
-        <v>3735989.0562581215</v>
+        <v>5566465.266412649</v>
       </c>
       <c r="D6">
-        <v>1953673.422538405</v>
+        <v>3898699.777595086</v>
       </c>
       <c r="E6">
-        <v>10680043.423977949</v>
+        <v>2038760.2916515777</v>
       </c>
       <c r="F6">
-        <v>10975684</v>
+        <v>11145184</v>
       </c>
       <c r="G6">
-        <v>12228519.167114174</v>
+        <v>11453699.709873427</v>
       </c>
       <c r="H6">
-        <v>2142700.837996541</v>
+        <v>12761098.664698916</v>
       </c>
       <c r="I6">
-        <v>5964638.482039821</v>
+        <v>2236020.275957884</v>
       </c>
       <c r="J6">
-        <v>1963868.6567438329</v>
+        <v>6224411.895535565</v>
       </c>
       <c r="K6">
-        <v>1646486.2848671505</v>
+        <v>2049399.5512239924</v>
       </c>
       <c r="L6">
-        <v>130292.23032587011</v>
+        <v>1718194.4636246322</v>
+      </c>
+      <c r="M6">
+        <v>135966.74983373977</v>
       </c>
     </row>
     <row r="7">
@@ -4125,37 +4428,37 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>224395</v>
+        <v>1319640</v>
       </c>
       <c r="C8">
-        <v>259748.86252661893</v>
+        <v>234167.90665593575</v>
       </c>
       <c r="D8">
-        <v>219912.22206052073</v>
+        <v>271061.5093657113</v>
       </c>
       <c r="E8">
-        <v>152462.1725950346</v>
-      </c>
-      <c r="F8">
-        <v>73329</v>
+        <v>229489.89366058705</v>
       </c>
       <c r="G8">
-        <v>79869.305523008</v>
+        <v>76522.64278247337</v>
       </c>
       <c r="H8">
-        <v>206653.89801298952</v>
+        <v>83347.79331262351</v>
       </c>
       <c r="I8">
-        <v>236195.20254046304</v>
+        <v>215654.13979808372</v>
       </c>
       <c r="J8">
-        <v>2854843.1516926885</v>
+        <v>246482.03454210205</v>
       </c>
       <c r="K8">
-        <v>5821535.974285082</v>
+        <v>2979177.98820344</v>
       </c>
       <c r="L8">
-        <v>1849379.7644171393</v>
+        <v>6075076.951895368</v>
+      </c>
+      <c r="M8">
+        <v>1929924.4102828011</v>
       </c>
     </row>
     <row r="9">
@@ -4178,25 +4481,28 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>1360024</v>
+        <v>1727000</v>
       </c>
       <c r="C12">
-        <v>1019741.4152999358</v>
+        <v>1419256.102327736</v>
       </c>
       <c r="D12">
-        <v>563639.4582578883</v>
+        <v>1064153.4461603297</v>
       </c>
       <c r="E12">
-        <v>4868735.087280923</v>
+        <v>588187.2236410588</v>
       </c>
       <c r="F12">
-        <v>5174004</v>
+        <v>5080779</v>
       </c>
       <c r="G12">
-        <v>5635501.181564219</v>
-      </c>
-      <c r="I12">
-        <v>1126183.3515561267</v>
+        <v>5399343.504576475</v>
+      </c>
+      <c r="H12">
+        <v>5880939.925773505</v>
+      </c>
+      <c r="J12">
+        <v>1175231.168005811</v>
       </c>
     </row>
     <row r="13">
@@ -4279,37 +4585,40 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-1118726672</v>
+        <v>-1197624923</v>
       </c>
       <c r="C28">
-        <v>-851648880.6177506</v>
+        <v>-1167449733.29353</v>
       </c>
       <c r="D28">
-        <v>-391204442.1767834</v>
+        <v>-888740103.7462047</v>
       </c>
       <c r="E28">
-        <v>-2295071.714879589</v>
+        <v>-408242275.0018513</v>
       </c>
       <c r="F28">
-        <v>-1776258</v>
+        <v>-2395028</v>
       </c>
       <c r="G28">
-        <v>2789782.7882969314</v>
+        <v>-1853618.0286586562</v>
       </c>
       <c r="H28">
-        <v>-31628664.22348876</v>
+        <v>2911284.0997359655</v>
       </c>
       <c r="I28">
-        <v>21221543.596721984</v>
+        <v>-33006163.64686312</v>
       </c>
       <c r="J28">
-        <v>281906533.2852393</v>
+        <v>22145789.52317148</v>
       </c>
       <c r="K28">
-        <v>-3152184.768945752</v>
+        <v>294184196.4929538</v>
       </c>
       <c r="L28">
-        <v>-26245274.950462367</v>
+        <v>-3289469.5012667454</v>
+      </c>
+      <c r="M28">
+        <v>-27388315.66995361</v>
       </c>
     </row>
     <row r="29">
@@ -4317,28 +4626,31 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>-1103130832</v>
+        <v>-1182143764</v>
       </c>
       <c r="C29">
-        <v>-838802881.0067462</v>
+        <v>-1151174659.4044464</v>
       </c>
       <c r="D29">
-        <v>-387470360.68081594</v>
+        <v>-875334631.9762816</v>
       </c>
       <c r="E29">
-        <v>82530.16019817101</v>
+        <v>-404345565.86308545</v>
       </c>
       <c r="F29">
-        <v>82530</v>
+        <v>86124</v>
       </c>
       <c r="G29">
-        <v>82530.03897617308</v>
+        <v>86124.36701492626</v>
       </c>
       <c r="H29">
-        <v>-29440010.54033418</v>
+        <v>86124.40768859928</v>
       </c>
       <c r="I29">
-        <v>21249612.229885828</v>
+        <v>-30722189.17604554</v>
+      </c>
+      <c r="J29">
+        <v>22175080.60840364</v>
       </c>
     </row>
     <row r="30">
@@ -4350,22 +4662,25 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="H31">
-        <v>-572254.9756894971</v>
+      <c r="B31">
+        <v>-25197</v>
+      </c>
+      <c r="I31">
+        <v>-597177.966223191</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="J32">
-        <v>-30511465.753158946</v>
-      </c>
       <c r="K32">
-        <v>-615805.0035627198</v>
+        <v>-31840308.67185768</v>
       </c>
       <c r="L32">
-        <v>-5633486.115851729</v>
+        <v>-642624.6957041519</v>
+      </c>
+      <c r="M32">
+        <v>-5878837.099419674</v>
       </c>
     </row>
     <row r="33">
@@ -4373,37 +4688,40 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1636567</v>
+        <v>-1396549</v>
       </c>
       <c r="C33">
-        <v>-2255724.669752919</v>
+        <v>-1707843.171604469</v>
       </c>
       <c r="D33">
-        <v>-2438450.1265919604</v>
+        <v>-2353966.5496476884</v>
       </c>
       <c r="E33">
-        <v>-615056.5268667002</v>
+        <v>-2544650.110871191</v>
       </c>
       <c r="F33">
-        <v>-664356</v>
+        <v>-641844</v>
       </c>
       <c r="G33">
-        <v>-738889.4425973047</v>
+        <v>-693290.197171554</v>
       </c>
       <c r="H33">
-        <v>-815388.0685418774</v>
+        <v>-771069.738733849</v>
       </c>
       <c r="I33">
-        <v>90108.61589465645</v>
+        <v>-850900.0517956198</v>
       </c>
       <c r="J33">
-        <v>-12552.297059568675</v>
+        <v>94033.04866737442</v>
       </c>
       <c r="K33">
-        <v>-257671.98650125097</v>
+        <v>-13098.977812173418</v>
       </c>
       <c r="L33">
-        <v>-997.0392057510215</v>
+        <v>-268894.18072093616</v>
+      </c>
+      <c r="M33">
+        <v>-1040.4625043544354</v>
       </c>
     </row>
     <row r="34">
@@ -4436,37 +4754,40 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-98445</v>
+        <v>4121</v>
       </c>
       <c r="C39">
-        <v>-71825.82766580358</v>
+        <v>-102732.50103943312</v>
       </c>
       <c r="D39">
-        <v>-64371.36271487026</v>
+        <v>-74954.00391421921</v>
       </c>
       <c r="E39">
-        <v>-33611.366649904085</v>
+        <v>-67174.88025816582</v>
       </c>
       <c r="F39">
-        <v>-62943</v>
+        <v>-35073</v>
       </c>
       <c r="G39">
-        <v>-817285.9380876517</v>
+        <v>-65684.30913632017</v>
       </c>
       <c r="H39">
-        <v>-1164521.6558894503</v>
+        <v>-852880.5778262356</v>
       </c>
       <c r="I39">
-        <v>-43446.30063139073</v>
+        <v>-1215239.1916715459</v>
       </c>
       <c r="J39">
-        <v>-49850.62734743643</v>
+        <v>-45338.484684584</v>
       </c>
       <c r="K39">
-        <v>1131755.4643173832</v>
+        <v>-52021.73422506888</v>
       </c>
       <c r="L39">
-        <v>-312549.1310209963</v>
+        <v>1181045.958803085</v>
+      </c>
+      <c r="M39">
+        <v>-326161.3482400165</v>
       </c>
     </row>
     <row r="40">
@@ -4474,37 +4795,40 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>127926</v>
+        <v>25110</v>
       </c>
       <c r="C40">
-        <v>70548.67560828435</v>
+        <v>133497.464858251</v>
       </c>
       <c r="D40">
-        <v>-15582.006592908225</v>
+        <v>73621.22901375084</v>
       </c>
       <c r="E40">
-        <v>-467953.9605594979</v>
+        <v>-16260.638006017552</v>
       </c>
       <c r="F40">
-        <v>-51712</v>
+        <v>-488335</v>
       </c>
       <c r="G40">
-        <v>3983768.380898866</v>
+        <v>-53964.173840735086</v>
       </c>
       <c r="H40">
-        <v>-299813.16890773654</v>
+        <v>4157270.4487942867</v>
       </c>
       <c r="I40">
-        <v>453278.6987837813</v>
+        <v>-312870.70634821255</v>
       </c>
       <c r="J40">
-        <v>50049.23542451785</v>
+        <v>473020.0050176008</v>
       </c>
       <c r="K40">
-        <v>16241.87529689331</v>
+        <v>52228.992130348044</v>
       </c>
       <c r="L40">
-        <v>13352.061128352916</v>
+        <v>16949.24547534598</v>
+      </c>
+      <c r="M40">
+        <v>13933.573403901575</v>
       </c>
     </row>
     <row r="41">
@@ -4517,37 +4841,40 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-16946</v>
+        <v>83899</v>
       </c>
       <c r="C42">
-        <v>-56935.3957224544</v>
+        <v>-17684.036392038535</v>
       </c>
       <c r="D42">
-        <v>37347.58429479912</v>
+        <v>-59415.060188303956</v>
       </c>
       <c r="E42">
-        <v>-120930.42851129612</v>
+        <v>38974.15554254423</v>
       </c>
       <c r="F42">
-        <v>-40390</v>
+        <v>-126198</v>
       </c>
       <c r="G42">
-        <v>25779.550790665897</v>
+        <v>-42149.0752905958</v>
       </c>
       <c r="H42">
-        <v>-269318.1119034484</v>
+        <v>26902.30817612071</v>
       </c>
       <c r="I42">
-        <v>250659.7426086309</v>
+        <v>-281047.52106312336</v>
       </c>
       <c r="J42">
-        <v>-61145.96187889921</v>
+        <v>261576.5378443315</v>
       </c>
       <c r="K42">
-        <v>37238.34798270894</v>
+        <v>-63809.005965576216</v>
       </c>
       <c r="L42">
-        <v>44033.67668714571</v>
+        <v>38860.161743515855</v>
+      </c>
+      <c r="M42">
+        <v>45951.44228789942</v>
       </c>
     </row>
     <row r="43">
@@ -4560,31 +4887,34 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>-245309</v>
+        <v>136141</v>
       </c>
       <c r="C44">
-        <v>-303919.1879367978</v>
+        <v>-255992.75836743665</v>
       </c>
       <c r="D44">
-        <v>398257.991369653</v>
+        <v>-317155.5517356976</v>
       </c>
       <c r="E44">
-        <v>694026.9953623512</v>
-      </c>
-      <c r="G44">
+        <v>415603.0221173795</v>
+      </c>
+      <c r="F44">
+        <v>724253</v>
+      </c>
+      <c r="H44">
         <v>0</v>
       </c>
-      <c r="H44">
-        <v>228503.80749926387</v>
-      </c>
-      <c r="J44">
-        <v>358559429.9359028</v>
+      <c r="I44">
+        <v>238455.6619577688</v>
       </c>
       <c r="K44">
-        <v>-417932.7094245812</v>
+        <v>374175499.0968427</v>
       </c>
       <c r="L44">
-        <v>113650.47299458466</v>
+        <v>-436134.6183693828</v>
+      </c>
+      <c r="M44">
+        <v>118600.20656252968</v>
       </c>
     </row>
     <row r="45">
@@ -4607,37 +4937,40 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-13726499</v>
+        <v>-14308684</v>
       </c>
       <c r="C48">
-        <v>-10228143.205534821</v>
+        <v>-14324318.88653845</v>
       </c>
       <c r="D48">
-        <v>-1651283.5757321413</v>
+        <v>-10673601.83345093</v>
       </c>
       <c r="E48">
-        <v>-1834076.587852713</v>
+        <v>-1723200.6872903758</v>
       </c>
       <c r="F48">
-        <v>-1039387</v>
+        <v>-1913955</v>
       </c>
       <c r="G48">
-        <v>253880.19831618335</v>
+        <v>-1084654.6402343772</v>
       </c>
       <c r="H48">
-        <v>704138.490278168</v>
+        <v>264937.25163704396</v>
       </c>
       <c r="I48">
-        <v>-778669.3898195229</v>
+        <v>734805.3043263423</v>
       </c>
       <c r="J48">
-        <v>-651493.1421921019</v>
+        <v>-812582.1920768844</v>
       </c>
       <c r="K48">
-        <v>271857.1352012541</v>
+        <v>-679867.132992368</v>
       </c>
       <c r="L48">
-        <v>-114763.47799030942</v>
+        <v>283697.1245328879</v>
+      </c>
+      <c r="M48">
+        <v>-119761.68542768472</v>
       </c>
     </row>
     <row r="49">
@@ -4645,28 +4978,31 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>-136934746</v>
+        <v>479436490</v>
       </c>
       <c r="C49">
-        <v>-495926162.6865656</v>
+        <v>-142898561.99684605</v>
       </c>
       <c r="D49">
-        <v>-764258035.8803666</v>
+        <v>-517524861.8383836</v>
       </c>
       <c r="E49">
-        <v>1574902183.1040587</v>
+        <v>-797543191.2791394</v>
       </c>
       <c r="F49">
-        <v>1256049471</v>
+        <v>2011075383</v>
       </c>
       <c r="G49">
-        <v>1279436829.8729827</v>
+        <v>1310753248.8708103</v>
       </c>
       <c r="H49">
-        <v>1672754690.7749577</v>
+        <v>1335159179.7939482</v>
       </c>
       <c r="I49">
-        <v>2391477238.5059175</v>
+        <v>1745606917.6571178</v>
+      </c>
+      <c r="J49">
+        <v>2495631447.921071</v>
       </c>
     </row>
     <row r="50">
@@ -4733,35 +5069,35 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
-        <v>-46903</v>
-      </c>
       <c r="C62">
-        <v>-33061.8976236922</v>
+        <v>-48945.73108083226</v>
       </c>
       <c r="D62">
-        <v>-21151.32321834101</v>
+        <v>-34501.81758333679</v>
       </c>
       <c r="E62">
-        <v>-47758.569860870535</v>
+        <v>-22072.510889467252</v>
       </c>
       <c r="F62">
         <v>-38076</v>
       </c>
       <c r="G62">
-        <v>-40933.36846978293</v>
+        <v>-39734.295389074665</v>
       </c>
       <c r="H62">
-        <v>-59925.710135411835</v>
-      </c>
-      <c r="J62">
-        <v>-61145.96187889921</v>
+        <v>-42716.10867864771</v>
+      </c>
+      <c r="I62">
+        <v>-62535.60951571907</v>
       </c>
       <c r="K62">
-        <v>37238.34798270894</v>
+        <v>-63809.005965576216</v>
       </c>
       <c r="L62">
-        <v>44033.67668714571</v>
+        <v>38860.161743515855</v>
+      </c>
+      <c r="M62">
+        <v>45951.44228789942</v>
       </c>
     </row>
     <row r="63">
@@ -4771,685 +5107,716 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-1483714794</v>
+      </c>
+      <c r="C67">
+        <v>-783567118.4251786</v>
+      </c>
+      <c r="D67">
+        <v>-345978836.1672866</v>
+      </c>
+      <c r="E67">
+        <v>306552100.46611327</v>
+      </c>
+      <c r="F67">
+        <v>-1805521617</v>
+      </c>
+      <c r="G67">
+        <v>-1451281198.2714732</v>
+      </c>
+      <c r="H67">
+        <v>-1497771157.5865326</v>
+      </c>
+      <c r="I67">
+        <v>-1965501844.4532387</v>
+      </c>
+      <c r="J67">
+        <v>-2768566947.6739235</v>
+      </c>
+      <c r="K67">
+        <v>-3227220055.3986883</v>
+      </c>
+      <c r="L67">
+        <v>-19328581.528869905</v>
+      </c>
+      <c r="M67">
+        <v>-56066903.60578507</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-750865249</v>
-      </c>
-      <c r="C68">
-        <v>-331539543.7848329</v>
-      </c>
-      <c r="D68">
-        <v>293758267.58858633</v>
-      </c>
-      <c r="E68">
-        <v>-1730168872.227889</v>
-      </c>
-      <c r="F68">
-        <v>-1390712541</v>
-      </c>
-      <c r="G68">
-        <v>-1435262259.9152856</v>
-      </c>
-      <c r="H68">
-        <v>-1883472388.187336</v>
-      </c>
-      <c r="I68">
-        <v>-2653021881.1585484</v>
-      </c>
-      <c r="J68">
-        <v>-3092533279.529286</v>
-      </c>
-      <c r="K68">
-        <v>-18521910.68412927</v>
-      </c>
-      <c r="L68">
-        <v>-53726973.15480414</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+      <c r="B73">
+        <v>-1474955288</v>
+      </c>
+      <c r="C73">
+        <v>-775118744.8338838</v>
+      </c>
+      <c r="F73">
+        <v>-1799392782</v>
+      </c>
+      <c r="G73">
+        <v>-1445191666.0070057</v>
+      </c>
+      <c r="K73">
+        <v>-3226982796.5638714</v>
+      </c>
+      <c r="L73">
+        <v>-18727209.50227223</v>
+      </c>
+      <c r="M73">
+        <v>-55246596.2905873</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
-      </c>
-      <c r="B74">
-        <v>-742769465</v>
-      </c>
-      <c r="F74">
-        <v>-1384877153</v>
-      </c>
-      <c r="J74">
-        <v>-3092305922.5998116</v>
-      </c>
-      <c r="K74">
-        <v>-17945636.685546447</v>
-      </c>
-      <c r="L74">
-        <v>-52940901.04687748</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-8759506</v>
+      </c>
+      <c r="C78">
+        <v>-8448373.591294896</v>
+      </c>
+      <c r="D78">
+        <v>-5337099.332654358</v>
+      </c>
+      <c r="E78">
+        <v>-141296.17948752662</v>
+      </c>
+      <c r="F78">
+        <v>-6128835</v>
+      </c>
+      <c r="G78">
+        <v>-6089532.264467424</v>
+      </c>
+      <c r="H78">
+        <v>-6128834.935396226</v>
+      </c>
+      <c r="I78">
+        <v>-2487483.9726198013</v>
+      </c>
+      <c r="J78">
+        <v>-832455.5742861931</v>
+      </c>
+      <c r="K78">
+        <v>-237258.83481648038</v>
+      </c>
+      <c r="L78">
+        <v>-601372.0265976819</v>
+      </c>
+      <c r="M78">
+        <v>-820308.7061904233</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>-8095784</v>
-      </c>
-      <c r="C79">
-        <v>-5114357.564423387</v>
-      </c>
-      <c r="D79">
-        <v>-135399.23830249536</v>
-      </c>
-      <c r="E79">
-        <v>-5873049.79700881</v>
-      </c>
-      <c r="F79">
-        <v>-5835388</v>
-      </c>
-      <c r="G79">
-        <v>-5873050.389218976</v>
-      </c>
-      <c r="H79">
-        <v>-2383669.7949226485</v>
-      </c>
-      <c r="I79">
-        <v>-797713.3641392412</v>
-      </c>
-      <c r="J79">
-        <v>-227356.92947398426</v>
-      </c>
-      <c r="K79">
-        <v>-576273.9985828294</v>
-      </c>
-      <c r="L79">
-        <v>-786073.4408667701</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="E85">
+        <v>306693396.64560074</v>
+      </c>
+      <c r="I85">
+        <v>-1963014360.480619</v>
+      </c>
+      <c r="J85">
+        <v>-2767734492.0996375</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="D86">
-        <v>293893666.8268888</v>
-      </c>
-      <c r="E86">
-        <v>-1724295822.4308805</v>
+        <v>-340641736.8346322</v>
       </c>
       <c r="H86">
-        <v>-1881088718.3924134</v>
-      </c>
-      <c r="I86">
-        <v>-2652224167.7944093</v>
+        <v>-1491642322.6511364</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="C87">
-        <v>-326425186.2204095</v>
-      </c>
-      <c r="G87">
-        <v>-1429389209.5260665</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>964078795</v>
+      </c>
+      <c r="C101">
+        <v>968322147.8365328</v>
+      </c>
+      <c r="D101">
+        <v>974707803.8068814</v>
+      </c>
+      <c r="E101">
+        <v>982478452.7778108</v>
+      </c>
+      <c r="F101">
+        <v>-162060449</v>
+      </c>
+      <c r="G101">
+        <v>178813054.39118025</v>
+      </c>
+      <c r="H101">
+        <v>186356132.24340314</v>
+      </c>
+      <c r="I101">
+        <v>261050475.52867475</v>
+      </c>
+      <c r="J101">
+        <v>246190221.87641504</v>
+      </c>
+      <c r="K101">
+        <v>45543828.5828847</v>
+      </c>
+      <c r="L101">
+        <v>101481342.05209883</v>
+      </c>
+      <c r="M101">
+        <v>45494097.81355893</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>927909599</v>
-      </c>
-      <c r="C102">
-        <v>934028752.0980023</v>
-      </c>
-      <c r="D102">
-        <v>941475096.0515045</v>
-      </c>
-      <c r="E102">
-        <v>194124574.74518263</v>
-      </c>
-      <c r="F102">
-        <v>171350361</v>
-      </c>
-      <c r="G102">
-        <v>178578631.42706814</v>
-      </c>
-      <c r="H102">
-        <v>250155635.29944596</v>
-      </c>
-      <c r="I102">
-        <v>235915568.56306645</v>
-      </c>
-      <c r="J102">
-        <v>43643074.581831716</v>
-      </c>
-      <c r="K102">
-        <v>97246057.64717199</v>
-      </c>
-      <c r="L102">
-        <v>43595419.3068531</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B104">
+        <v>901528763</v>
+      </c>
+      <c r="C104">
+        <v>901528762.8502741</v>
+      </c>
+      <c r="D104">
+        <v>901528763.2534791</v>
+      </c>
+      <c r="E104">
+        <v>903273776.9892476</v>
+      </c>
+      <c r="J104">
+        <v>237760272.93971056</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B105">
-        <v>863903810</v>
-      </c>
-      <c r="C105">
-        <v>863903810.3863775</v>
-      </c>
-      <c r="D105">
-        <v>865575996.6514795</v>
-      </c>
-      <c r="E105">
-        <v>200687340.5226202</v>
-      </c>
-      <c r="I105">
-        <v>227837440.2718519</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+      <c r="K106">
+        <v>-13596.953181904553</v>
+      </c>
+      <c r="L106">
+        <v>47181.079793045574</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-      <c r="J107">
-        <v>-13029.48962060994</v>
-      </c>
-      <c r="K107">
-        <v>45211.995748487825</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="J109">
+        <v>52116.08944515841</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>11861</v>
+      </c>
+      <c r="C110">
+        <v>106612.42829693337</v>
+      </c>
+      <c r="D110">
+        <v>-44016.3495116804</v>
       </c>
       <c r="E110">
-        <v>-4546.822558715614</v>
+        <v>-40555.86025606746</v>
+      </c>
+      <c r="F110">
+        <v>-4745</v>
+      </c>
+      <c r="G110">
+        <v>-36336.48927008036</v>
+      </c>
+      <c r="H110">
+        <v>-55912.59954919433</v>
       </c>
       <c r="I110">
-        <v>49941.04468905403</v>
+        <v>-4409.745171236238</v>
+      </c>
+      <c r="K110">
+        <v>31647499.007263992</v>
+      </c>
+      <c r="L110">
+        <v>-6364283.798326314</v>
+      </c>
+      <c r="M110">
+        <v>3764318.227151091</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B111">
-        <v>102163</v>
-      </c>
-      <c r="C111">
-        <v>-42179.3442565378</v>
-      </c>
-      <c r="D111">
-        <v>-38863.27717628583</v>
-      </c>
-      <c r="F111">
-        <v>-34820</v>
-      </c>
-      <c r="G111">
-        <v>-53579.10891809832</v>
-      </c>
-      <c r="H111">
-        <v>-4225.706168836663</v>
-      </c>
-      <c r="J111">
-        <v>30326702.9250483</v>
-      </c>
-      <c r="K111">
-        <v>-6098672.885280427</v>
-      </c>
-      <c r="L111">
-        <v>3607215.8676410047</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B113">
+        <v>-5461829</v>
+      </c>
+      <c r="C113">
+        <v>-4274780.295727633</v>
+      </c>
+      <c r="D113">
+        <v>-3063721.9117736267</v>
+      </c>
+      <c r="E113">
+        <v>-1623881.5237977586</v>
+      </c>
+      <c r="F113">
+        <v>10413780</v>
+      </c>
+      <c r="G113">
+        <v>11881031.224710591</v>
+      </c>
+      <c r="H113">
+        <v>6913741.749569788</v>
+      </c>
+      <c r="I113">
+        <v>-1729449.0155346245</v>
+      </c>
+      <c r="J113">
+        <v>8377832.8472593175</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B114">
-        <v>-4096374</v>
-      </c>
-      <c r="C114">
-        <v>-2935858.6674414226</v>
-      </c>
-      <c r="D114">
-        <v>-1556109.4589618538</v>
-      </c>
-      <c r="E114">
-        <v>-6558218.954878844</v>
-      </c>
-      <c r="F114">
-        <v>11385181</v>
-      </c>
-      <c r="G114">
-        <v>6625199.422285508</v>
-      </c>
-      <c r="H114">
-        <v>-1657271.1324233676</v>
-      </c>
-      <c r="I114">
-        <v>8028187.246525489</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="B123">
+        <v>68000000</v>
+      </c>
+      <c r="C123">
+        <v>70961552.85368939</v>
+      </c>
+      <c r="D123">
+        <v>76286778.81468758</v>
+      </c>
+      <c r="E123">
+        <v>80869113.1726171</v>
+      </c>
+      <c r="F123">
+        <v>-172469484</v>
+      </c>
+      <c r="G123">
+        <v>166968359.65573975</v>
+      </c>
+      <c r="H123">
+        <v>179498303.09338254</v>
+      </c>
+      <c r="I123">
+        <v>262784334.28938058</v>
+      </c>
+      <c r="K123">
+        <v>13909926.52880261</v>
+      </c>
+      <c r="L123">
+        <v>107798444.77063212</v>
+      </c>
+      <c r="M123">
+        <v>41729779.58640783</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="B124">
-        <v>68000000</v>
-      </c>
-      <c r="C124">
-        <v>73102979.72332281</v>
-      </c>
-      <c r="D124">
-        <v>77494072.13616319</v>
-      </c>
-      <c r="F124">
-        <v>160000000</v>
-      </c>
-      <c r="G124">
-        <v>172007011.11370072</v>
-      </c>
-      <c r="H124">
-        <v>251817132.13803816</v>
-      </c>
-      <c r="J124">
-        <v>13329401.146404028</v>
-      </c>
-      <c r="K124">
-        <v>103299518.53670394</v>
-      </c>
-      <c r="L124">
-        <v>39988203.43921209</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>-40199509</v>
+      </c>
+      <c r="C125">
+        <v>41807521.683427274</v>
+      </c>
+      <c r="D125">
+        <v>111169603.98362796</v>
+      </c>
+      <c r="E125">
+        <v>491465289.45389533</v>
+      </c>
+      <c r="F125">
+        <v>43455241</v>
+      </c>
+      <c r="G125">
+        <v>38245370.69512832</v>
+      </c>
+      <c r="H125">
+        <v>23701438.34213979</v>
+      </c>
+      <c r="I125">
+        <v>41093013.12303829</v>
+      </c>
+      <c r="J125">
+        <v>-26745277.876437392</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B126">
-        <v>40062701</v>
-      </c>
-      <c r="C126">
-        <v>106529983.72898023</v>
-      </c>
-      <c r="D126">
-        <v>470954176.43650603</v>
-      </c>
-      <c r="E126">
-        <v>38810127.05149095</v>
-      </c>
-      <c r="F126">
-        <v>36649215</v>
-      </c>
-      <c r="G126">
-        <v>22712268.01629541</v>
-      </c>
-      <c r="H126">
-        <v>39378012.17693227</v>
-      </c>
-      <c r="I126">
-        <v>-25629074.08956436</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>-40199509</v>
+      </c>
+      <c r="C127">
+        <v>41807521.683427274</v>
+      </c>
+      <c r="D127">
+        <v>111169603.98362796</v>
+      </c>
+      <c r="E127">
+        <v>491465289.45389533</v>
+      </c>
+      <c r="F127">
+        <v>43455241</v>
+      </c>
+      <c r="G127">
+        <v>38245370.69512832</v>
+      </c>
+      <c r="H127">
+        <v>23701438.34213979</v>
+      </c>
+      <c r="I127">
+        <v>41093013.12303829</v>
+      </c>
+      <c r="J127">
+        <v>-26745277.876437392</v>
+      </c>
+      <c r="K127">
+        <v>-116333134.74403445</v>
+      </c>
+      <c r="L127">
+        <v>83600273.3805737</v>
+      </c>
+      <c r="M127">
+        <v>32754210.318697162</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>40062701</v>
+        <v>76446285</v>
       </c>
       <c r="C128">
-        <v>106529983.72898023</v>
+        <v>76446285.02094606</v>
       </c>
       <c r="D128">
-        <v>470954176.43650603</v>
+        <v>76446284.37240955</v>
       </c>
       <c r="E128">
-        <v>38810127.05149095</v>
+        <v>76446285.04382186</v>
       </c>
       <c r="F128">
-        <v>36649215</v>
+        <v>61300127</v>
       </c>
       <c r="G128">
-        <v>22712268.01629541</v>
+        <v>61300126.9971371</v>
       </c>
       <c r="H128">
-        <v>39378012.17693227</v>
+        <v>61300126.68637398</v>
       </c>
       <c r="I128">
-        <v>-25629074.08956436</v>
+        <v>61298196.726766594</v>
       </c>
       <c r="J128">
-        <v>-111478016.53812113</v>
-      </c>
-      <c r="K128">
-        <v>80111248.43336134</v>
-      </c>
-      <c r="L128">
-        <v>31387226.069639303</v>
+        <v>116354487.84161593</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>73255829</v>
+        <v>9243325</v>
       </c>
       <c r="C129">
-        <v>73255828.3785299</v>
+        <v>42989111.89196429</v>
       </c>
       <c r="D129">
-        <v>73255829.02192108</v>
+        <v>131757633.0399691</v>
       </c>
       <c r="E129">
-        <v>58741790.395880125</v>
+        <v>544211238.5259334</v>
       </c>
       <c r="F129">
-        <v>58741790</v>
+        <v>76446285</v>
       </c>
       <c r="G129">
-        <v>58741789.702206455</v>
+        <v>84222011.96563634</v>
       </c>
       <c r="H129">
-        <v>58739940.28871387</v>
+        <v>78252790.07253757</v>
       </c>
       <c r="I129">
-        <v>111498478.47246654</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B130">
-        <v>41194978</v>
-      </c>
-      <c r="C130">
-        <v>126258779.38707031</v>
-      </c>
-      <c r="D130">
-        <v>521498793.80548894</v>
-      </c>
-      <c r="E130">
-        <v>73255828.74229202</v>
-      </c>
-      <c r="F130">
-        <v>80707039</v>
-      </c>
-      <c r="G130">
-        <v>74986940.2647366</v>
-      </c>
-      <c r="H130">
-        <v>81752543.48247024</v>
-      </c>
-      <c r="I130">
-        <v>58741790.395880125</v>
+        <v>85313050.51845372</v>
+      </c>
+      <c r="J129">
+        <v>61300127.410258695</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:M129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -5461,6 +5828,7 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5468,36 +5836,39 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -5511,28 +5882,31 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>358977575.58418924</v>
+        <v>622383997.7279269</v>
       </c>
       <c r="C3">
-        <v>268319962.61939555</v>
+        <v>374611855.92804</v>
       </c>
       <c r="D3">
-        <v>-764279187.2035848</v>
+        <v>280005900.13406175</v>
       </c>
       <c r="E3">
-        <v>318843029.5341978</v>
+        <v>-797565263.7900287</v>
       </c>
       <c r="F3">
-        <v>-23384501.504512787</v>
+        <v>700323792.4245787</v>
       </c>
       <c r="G3">
-        <v>-393298868.56030965</v>
+        <v>-24402949.109847784</v>
       </c>
       <c r="H3">
-        <v>1672694765.0648224</v>
+        <v>-410427918.3623333</v>
       </c>
       <c r="I3">
-        <v>-545934949.9034152</v>
+        <v>1745544382.0476024</v>
+      </c>
+      <c r="J3">
+        <v>-569711644.1506977</v>
       </c>
     </row>
     <row r="4">
@@ -5540,28 +5914,31 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>597643378.7247946</v>
+        <v>697728900.2654772</v>
       </c>
       <c r="C4">
-        <v>691300215.353332</v>
+        <v>623672091.2799561</v>
       </c>
       <c r="D4">
-        <v>-390343116.0781266</v>
+        <v>721407893.6700342</v>
       </c>
       <c r="E4">
-        <v>330902427.12772346</v>
+        <v>-407343436.2154676</v>
       </c>
       <c r="F4">
-        <v>-37415407.84510112</v>
+        <v>345313970.4177363</v>
       </c>
       <c r="G4">
-        <v>-491762495.8255682</v>
+        <v>-39044932.9609189</v>
       </c>
       <c r="H4">
-        <v>1934341370.6706693</v>
+        <v>-513179857.92629814</v>
       </c>
       <c r="I4">
-        <v>-389077237.54170275</v>
+        <v>2018586285.4694808</v>
+      </c>
+      <c r="J4">
+        <v>-406022425.8232794</v>
       </c>
     </row>
     <row r="5">
@@ -5569,28 +5946,31 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>28425829.344020277</v>
+        <v>-45218658.56216107</v>
       </c>
       <c r="C5">
-        <v>37476096.281436205</v>
+        <v>29663838.10890662</v>
       </c>
       <c r="D5">
-        <v>17289522.37454352</v>
+        <v>39108264.51507482</v>
       </c>
       <c r="E5">
-        <v>-11530901.308785468</v>
+        <v>18042519.93817964</v>
       </c>
       <c r="F5">
-        <v>18594089.760415316</v>
+        <v>355549573.6827947</v>
       </c>
       <c r="G5">
-        <v>64026187.91180751</v>
+        <v>19403904.166175812</v>
       </c>
       <c r="H5">
-        <v>-229958015.67222282</v>
+        <v>66814672.316529065</v>
       </c>
       <c r="I5">
-        <v>103827278.65974481</v>
+        <v>-239973204.1654996</v>
+      </c>
+      <c r="J5">
+        <v>108349190.03335616</v>
       </c>
     </row>
     <row r="6">
@@ -5598,28 +5978,31 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>1598161.9437418785</v>
+        <v>1657739.7335873507</v>
       </c>
       <c r="C6">
-        <v>1782315.6337197165</v>
+        <v>1667765.4888175633</v>
       </c>
       <c r="D6">
-        <v>1953673.422538405</v>
+        <v>1859939.4859435083</v>
       </c>
       <c r="E6">
-        <v>-295640.5760220513</v>
+        <v>2038760.2916515777</v>
       </c>
       <c r="F6">
-        <v>-1252835.167114174</v>
+        <v>-308515.7098734267</v>
       </c>
       <c r="G6">
-        <v>10085818.329117633</v>
+        <v>-1307398.9548254889</v>
       </c>
       <c r="H6">
-        <v>2142700.837996541</v>
+        <v>10525078.388741031</v>
       </c>
       <c r="I6">
-        <v>4000769.8252959885</v>
+        <v>2236020.275957884</v>
+      </c>
+      <c r="J6">
+        <v>4175012.3443115726</v>
       </c>
     </row>
     <row r="7">
@@ -5632,28 +6015,28 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-35353.862526618934</v>
+        <v>1085472.0933440642</v>
       </c>
       <c r="C8">
-        <v>39836.64046609821</v>
+        <v>-36893.60270977556</v>
       </c>
       <c r="D8">
-        <v>219912.22206052073</v>
+        <v>41571.61570512425</v>
       </c>
       <c r="E8">
-        <v>79133.17259503459</v>
-      </c>
-      <c r="F8">
-        <v>-6540.305523008006</v>
+        <v>229489.89366058705</v>
       </c>
       <c r="G8">
-        <v>-126784.59248998151</v>
+        <v>-6825.150530150146</v>
       </c>
       <c r="H8">
-        <v>206653.89801298952</v>
+        <v>-132306.3464854602</v>
       </c>
       <c r="I8">
-        <v>-2618647.9491522256</v>
+        <v>215654.13979808372</v>
+      </c>
+      <c r="J8">
+        <v>-2732695.953661338</v>
       </c>
     </row>
     <row r="9">
@@ -5676,19 +6059,22 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>340282.58470006415</v>
+        <v>307743.8976722639</v>
       </c>
       <c r="C12">
-        <v>456101.9570420475</v>
+        <v>355102.65616740636</v>
       </c>
       <c r="D12">
-        <v>563639.4582578883</v>
+        <v>475966.22251927096</v>
       </c>
       <c r="E12">
-        <v>-305268.91271907743</v>
+        <v>588187.2236410588</v>
       </c>
       <c r="F12">
-        <v>-461497.1815642193</v>
+        <v>-318564.50457647536</v>
+      </c>
+      <c r="G12">
+        <v>-481596.42119702976</v>
       </c>
     </row>
     <row r="13">
@@ -5771,28 +6157,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-267077791.38224936</v>
+        <v>-30175189.706470013</v>
       </c>
       <c r="C28">
-        <v>-460444438.44096726</v>
+        <v>-278709629.54732525</v>
       </c>
       <c r="D28">
-        <v>-391204442.1767834</v>
+        <v>-480497828.7443534</v>
       </c>
       <c r="E28">
-        <v>-518813.71487958916</v>
+        <v>-408242275.0018513</v>
       </c>
       <c r="F28">
-        <v>-4566040.788296931</v>
+        <v>-541409.9713413438</v>
       </c>
       <c r="G28">
-        <v>34418447.01178569</v>
+        <v>-4764902.128394621</v>
       </c>
       <c r="H28">
-        <v>-31628664.22348876</v>
+        <v>35917447.746599086</v>
       </c>
       <c r="I28">
-        <v>-260684989.6885173</v>
+        <v>-33006163.64686312</v>
+      </c>
+      <c r="J28">
+        <v>-272038406.9697823</v>
       </c>
     </row>
     <row r="29">
@@ -5800,25 +6189,28 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>-264327950.99325383</v>
+        <v>-30969104.595553637</v>
       </c>
       <c r="C29">
-        <v>-451332520.32593024</v>
+        <v>-275840027.4281647</v>
       </c>
       <c r="D29">
-        <v>-387470360.68081594</v>
+        <v>-470989066.1131962</v>
       </c>
       <c r="E29">
-        <v>0.16019817101187073</v>
+        <v>-404345565.86308545</v>
       </c>
       <c r="F29">
-        <v>-0.038976173076662235</v>
+        <v>-0.3670149262616178</v>
       </c>
       <c r="G29">
-        <v>29522540.579310354</v>
+        <v>-0.04067367302195635</v>
       </c>
       <c r="H29">
-        <v>-29440010.54033418</v>
+        <v>30808313.58373414</v>
+      </c>
+      <c r="I29">
+        <v>-30722189.17604554</v>
       </c>
     </row>
     <row r="30">
@@ -5830,8 +6222,8 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="H31">
-        <v>-572254.9756894971</v>
+      <c r="I31">
+        <v>-597177.966223191</v>
       </c>
     </row>
     <row r="32">
@@ -5844,28 +6236,31 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>619157.6697529191</v>
+        <v>311294.17160446895</v>
       </c>
       <c r="C33">
-        <v>182725.45683904132</v>
+        <v>646123.3780432194</v>
       </c>
       <c r="D33">
-        <v>-2438450.1265919604</v>
+        <v>190683.56122350274</v>
       </c>
       <c r="E33">
-        <v>49299.47313329985</v>
+        <v>-2544650.110871191</v>
       </c>
       <c r="F33">
-        <v>74533.4425973047</v>
+        <v>51446.19717155397</v>
       </c>
       <c r="G33">
-        <v>76498.62594457273</v>
+        <v>77779.54156229505</v>
       </c>
       <c r="H33">
-        <v>-815388.0685418774</v>
+        <v>79830.31306177075</v>
       </c>
       <c r="I33">
-        <v>102660.91295422513</v>
+        <v>-850900.0517956198</v>
+      </c>
+      <c r="J33">
+        <v>107132.02647954783</v>
       </c>
     </row>
     <row r="34">
@@ -5898,28 +6293,31 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-26619.172334196424</v>
+        <v>106853.50103943312</v>
       </c>
       <c r="C39">
-        <v>-7454.464950933318</v>
+        <v>-27778.497125213908</v>
       </c>
       <c r="D39">
-        <v>-64371.36271487026</v>
+        <v>-7779.123656053387</v>
       </c>
       <c r="E39">
-        <v>29331.633350095915</v>
+        <v>-67174.88025816582</v>
       </c>
       <c r="F39">
-        <v>754342.9380876517</v>
+        <v>30611.309136320167</v>
       </c>
       <c r="G39">
-        <v>347235.7178017986</v>
+        <v>787196.2686899154</v>
       </c>
       <c r="H39">
-        <v>-1164521.6558894503</v>
+        <v>362358.6138453103</v>
       </c>
       <c r="I39">
-        <v>6404.326716045696</v>
+        <v>-1215239.1916715459</v>
+      </c>
+      <c r="J39">
+        <v>6683.249540484881</v>
       </c>
     </row>
     <row r="40">
@@ -5927,28 +6325,31 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>57377.32439171565</v>
+        <v>-108387.46485825101</v>
       </c>
       <c r="C40">
-        <v>86130.68220119257</v>
+        <v>59876.235844500174</v>
       </c>
       <c r="D40">
-        <v>-15582.006592908225</v>
+        <v>89881.8670197684</v>
       </c>
       <c r="E40">
-        <v>-416241.9605594979</v>
+        <v>-16260.638006017552</v>
       </c>
       <c r="F40">
-        <v>-4035480.380898866</v>
+        <v>-434370.8261592649</v>
       </c>
       <c r="G40">
-        <v>4283581.549806602</v>
+        <v>-4211234.622635022</v>
       </c>
       <c r="H40">
-        <v>-299813.16890773654</v>
+        <v>4470141.155142499</v>
       </c>
       <c r="I40">
-        <v>403229.4633592635</v>
+        <v>-312870.70634821255</v>
+      </c>
+      <c r="J40">
+        <v>420791.0128872527</v>
       </c>
     </row>
     <row r="41">
@@ -5961,28 +6362,31 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>39989.3957224544</v>
+        <v>101583.03639203854</v>
       </c>
       <c r="C42">
-        <v>-94282.98001725352</v>
+        <v>41731.02379626542</v>
       </c>
       <c r="D42">
-        <v>37347.58429479912</v>
+        <v>-98389.21573084818</v>
       </c>
       <c r="E42">
-        <v>-80540.42851129612</v>
+        <v>38974.15554254423</v>
       </c>
       <c r="F42">
-        <v>-66169.5507906659</v>
+        <v>-84048.92470940421</v>
       </c>
       <c r="G42">
-        <v>295097.6626941143</v>
+        <v>-69051.3834667165</v>
       </c>
       <c r="H42">
-        <v>-269318.1119034484</v>
+        <v>307949.82923924405</v>
       </c>
       <c r="I42">
-        <v>311805.7044875301</v>
+        <v>-281047.52106312336</v>
+      </c>
+      <c r="J42">
+        <v>325385.54380990774</v>
       </c>
     </row>
     <row r="43">
@@ -5995,19 +6399,22 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>58610.187936797796</v>
+        <v>392133.75836743665</v>
       </c>
       <c r="C44">
-        <v>-702177.1793064508</v>
+        <v>61162.79336826096</v>
       </c>
       <c r="D44">
-        <v>398257.991369653</v>
-      </c>
-      <c r="G44">
-        <v>-228503.80749926387</v>
+        <v>-732758.5738530771</v>
+      </c>
+      <c r="E44">
+        <v>415603.0221173795</v>
       </c>
       <c r="H44">
-        <v>228503.80749926387</v>
+        <v>-238455.6619577688</v>
+      </c>
+      <c r="I44">
+        <v>238455.6619577688</v>
       </c>
     </row>
     <row r="45">
@@ -6030,28 +6437,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-3498355.7944651786</v>
+        <v>15634.886538449675</v>
       </c>
       <c r="C48">
-        <v>-8576859.62980268</v>
+        <v>-3650717.0530875195</v>
       </c>
       <c r="D48">
-        <v>-1651283.5757321413</v>
+        <v>-8950401.146160554</v>
       </c>
       <c r="E48">
-        <v>-794689.587852713</v>
+        <v>-1723200.6872903758</v>
       </c>
       <c r="F48">
-        <v>-1293267.1983161834</v>
+        <v>-829300.3597656228</v>
       </c>
       <c r="G48">
-        <v>-450258.29196198465</v>
+        <v>-1349591.8918714211</v>
       </c>
       <c r="H48">
-        <v>704138.490278168</v>
+        <v>-469868.05268929835</v>
       </c>
       <c r="I48">
-        <v>-127176.24762742093</v>
+        <v>734805.3043263423</v>
+      </c>
+      <c r="J48">
+        <v>-132715.05908451648</v>
       </c>
     </row>
     <row r="49">
@@ -6059,25 +6469,28 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>358991416.6865656</v>
+        <v>622335051.9968461</v>
       </c>
       <c r="C49">
-        <v>268331873.193801</v>
+        <v>374626299.8415376</v>
       </c>
       <c r="D49">
-        <v>-764258035.8803666</v>
+        <v>280018329.4407558</v>
       </c>
       <c r="E49">
-        <v>318852712.10405874</v>
+        <v>-797543191.2791394</v>
       </c>
       <c r="F49">
-        <v>-23387358.87298274</v>
+        <v>700322134.1291897</v>
       </c>
       <c r="G49">
-        <v>-393317860.9019749</v>
+        <v>-24405930.923137903</v>
       </c>
       <c r="H49">
-        <v>1672754690.7749577</v>
+        <v>-410447737.86316967</v>
+      </c>
+      <c r="I49">
+        <v>1745606917.6571178</v>
       </c>
     </row>
     <row r="50">
@@ -6144,26 +6557,26 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
-        <v>-13841.102376307797</v>
-      </c>
       <c r="C62">
-        <v>-11910.574405351192</v>
+        <v>-14443.913497495465</v>
       </c>
       <c r="D62">
-        <v>-21151.32321834101</v>
+        <v>-12429.306693869541</v>
       </c>
       <c r="E62">
-        <v>-9682.569860870535</v>
+        <v>-22072.510889467252</v>
       </c>
       <c r="F62">
-        <v>2857.3684697829303</v>
+        <v>1658.2953890746649</v>
       </c>
       <c r="G62">
-        <v>18992.341665628905</v>
+        <v>2981.813289573045</v>
       </c>
       <c r="H62">
-        <v>-59925.710135411835</v>
+        <v>19819.500837071362</v>
+      </c>
+      <c r="I62">
+        <v>-62535.60951571907</v>
       </c>
     </row>
     <row r="63">
@@ -6173,574 +6586,614 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-700147675.5748214</v>
+      </c>
+      <c r="C67">
+        <v>-437588282.2578921</v>
+      </c>
+      <c r="D67">
+        <v>-652530936.6333998</v>
+      </c>
+      <c r="E67">
+        <v>306552100.46611327</v>
+      </c>
+      <c r="F67">
+        <v>-354240418.72852683</v>
+      </c>
+      <c r="G67">
+        <v>46489959.31505942</v>
+      </c>
+      <c r="H67">
+        <v>467730686.86670613</v>
+      </c>
+      <c r="I67">
+        <v>-1965501844.4532387</v>
+      </c>
+      <c r="J67">
+        <v>458653107.7247648</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-419325705.2151671</v>
-      </c>
-      <c r="C68">
-        <v>-625297811.3734193</v>
-      </c>
-      <c r="D68">
-        <v>293758267.58858633</v>
-      </c>
-      <c r="E68">
-        <v>-339456331.22788906</v>
-      </c>
-      <c r="F68">
-        <v>44549718.91528559</v>
-      </c>
-      <c r="G68">
-        <v>448210128.2720504</v>
-      </c>
-      <c r="H68">
-        <v>-1883472388.187336</v>
-      </c>
-      <c r="I68">
-        <v>439511398.37073755</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+      <c r="B73">
+        <v>-699836543.1661162</v>
+      </c>
+      <c r="F73">
+        <v>-354201115.9929943</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-311132.40870510414</v>
+      </c>
+      <c r="C78">
+        <v>-3111274.258640538</v>
+      </c>
+      <c r="D78">
+        <v>-5195803.1531668315</v>
+      </c>
+      <c r="E78">
+        <v>-141296.17948752662</v>
+      </c>
+      <c r="F78">
+        <v>-39302.73553257622</v>
+      </c>
+      <c r="G78">
+        <v>39302.67092880234</v>
+      </c>
+      <c r="H78">
+        <v>-3641350.962776425</v>
+      </c>
+      <c r="I78">
+        <v>-2487483.9726198013</v>
+      </c>
+      <c r="J78">
+        <v>-595196.7394697127</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>-2981426.435576613</v>
-      </c>
-      <c r="C79">
-        <v>-4978958.326120892</v>
-      </c>
-      <c r="D79">
-        <v>-135399.23830249536</v>
-      </c>
-      <c r="E79">
-        <v>-37661.79700880963</v>
-      </c>
-      <c r="F79">
-        <v>37662.38921897579</v>
-      </c>
-      <c r="G79">
-        <v>-3489380.5942963273</v>
-      </c>
-      <c r="H79">
-        <v>-2383669.7949226485</v>
-      </c>
-      <c r="I79">
-        <v>-570356.4346652569</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="E85">
+        <v>306693396.64560074</v>
+      </c>
+      <c r="I85">
+        <v>-1963014360.480619</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="D86">
-        <v>293893666.8268888</v>
-      </c>
-      <c r="H86">
-        <v>-1881088718.3924134</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>-4243352.836532831</v>
+      </c>
+      <c r="C101">
+        <v>-6385655.970348597</v>
+      </c>
+      <c r="D101">
+        <v>-7770648.970929384</v>
+      </c>
+      <c r="E101">
+        <v>982478452.7778108</v>
+      </c>
+      <c r="F101">
+        <v>-340873503.3911803</v>
+      </c>
+      <c r="G101">
+        <v>-7543077.85222289</v>
+      </c>
+      <c r="H101">
+        <v>-74694343.28527161</v>
+      </c>
+      <c r="I101">
+        <v>261050475.52867475</v>
+      </c>
+      <c r="J101">
+        <v>200646393.29353034</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>-6119153.098002315</v>
-      </c>
-      <c r="C102">
-        <v>-7446343.953502178</v>
-      </c>
-      <c r="D102">
-        <v>941475096.0515045</v>
-      </c>
-      <c r="E102">
-        <v>22774213.745182633</v>
-      </c>
-      <c r="F102">
-        <v>-7228270.427068144</v>
-      </c>
-      <c r="G102">
-        <v>-71577003.87237781</v>
-      </c>
-      <c r="H102">
-        <v>250155635.29944596</v>
-      </c>
-      <c r="I102">
-        <v>192272493.98123473</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B104">
+        <v>0.14972591400146484</v>
+      </c>
+      <c r="C104">
+        <v>-0.4032050371170044</v>
+      </c>
+      <c r="D104">
+        <v>-1745013.7357684374</v>
+      </c>
+      <c r="E104">
+        <v>903273776.9892476</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="B105">
-        <v>-0.3863774538040161</v>
-      </c>
-      <c r="C105">
-        <v>-1672186.2651020288</v>
-      </c>
-      <c r="D105">
-        <v>865575996.6514795</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>-94751.42829693337</v>
+      </c>
+      <c r="C110">
+        <v>150628.77780861378</v>
+      </c>
+      <c r="D110">
+        <v>-3460.4892556129344</v>
+      </c>
+      <c r="E110">
+        <v>-40555.86025606746</v>
+      </c>
+      <c r="F110">
+        <v>31591.48927008036</v>
+      </c>
+      <c r="G110">
+        <v>19576.11027911397</v>
+      </c>
+      <c r="H110">
+        <v>-51502.854377958094</v>
+      </c>
+      <c r="I110">
+        <v>-4409.745171236238</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B111">
-        <v>144342.3442565378</v>
-      </c>
-      <c r="C111">
-        <v>-3316.067080251967</v>
-      </c>
-      <c r="D111">
-        <v>-38863.27717628583</v>
-      </c>
-      <c r="F111">
-        <v>18759.108918098318</v>
-      </c>
-      <c r="G111">
-        <v>-49353.40274926166</v>
-      </c>
-      <c r="H111">
-        <v>-4225.706168836663</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B113">
+        <v>-1187048.704272367</v>
+      </c>
+      <c r="C113">
+        <v>-1211058.3839540062</v>
+      </c>
+      <c r="D113">
+        <v>-1439840.387975868</v>
+      </c>
+      <c r="E113">
+        <v>-1623881.5237977586</v>
+      </c>
+      <c r="F113">
+        <v>-1467251.2247105911</v>
+      </c>
+      <c r="G113">
+        <v>4967289.4751408035</v>
+      </c>
+      <c r="H113">
+        <v>8643190.765104413</v>
+      </c>
+      <c r="I113">
+        <v>-1729449.0155346245</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B114">
-        <v>-1160515.3325585774</v>
-      </c>
-      <c r="C114">
-        <v>-1379749.2084795688</v>
-      </c>
-      <c r="D114">
-        <v>-1556109.4589618538</v>
-      </c>
-      <c r="E114">
-        <v>-17943399.954878844</v>
-      </c>
-      <c r="F114">
-        <v>4759981.577714492</v>
-      </c>
-      <c r="G114">
-        <v>8282470.554708876</v>
-      </c>
-      <c r="H114">
-        <v>-1657271.1324233676</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="B123">
+        <v>-2961552.8536893874</v>
+      </c>
+      <c r="C123">
+        <v>-5325225.960998192</v>
+      </c>
+      <c r="D123">
+        <v>-4582334.357929513</v>
+      </c>
+      <c r="E123">
+        <v>80869113.1726171</v>
+      </c>
+      <c r="F123">
+        <v>-339437843.6557398</v>
+      </c>
+      <c r="G123">
+        <v>-12529943.437642783</v>
+      </c>
+      <c r="H123">
+        <v>-83286031.19599804</v>
+      </c>
+      <c r="I123">
+        <v>262784334.28938058</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="B124">
-        <v>-5102979.723322809</v>
-      </c>
-      <c r="C124">
-        <v>-4391092.412840381</v>
-      </c>
-      <c r="D124">
-        <v>77494072.13616319</v>
-      </c>
-      <c r="F124">
-        <v>-12007011.113700718</v>
-      </c>
-      <c r="G124">
-        <v>-79810121.02433744</v>
-      </c>
-      <c r="H124">
-        <v>251817132.13803816</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>-82007030.68342727</v>
+      </c>
+      <c r="C125">
+        <v>-69362082.30020069</v>
+      </c>
+      <c r="D125">
+        <v>-380295685.47026736</v>
+      </c>
+      <c r="E125">
+        <v>491465289.45389533</v>
+      </c>
+      <c r="F125">
+        <v>5209870.304871678</v>
+      </c>
+      <c r="G125">
+        <v>14543932.35298853</v>
+      </c>
+      <c r="H125">
+        <v>-17391574.7808985</v>
+      </c>
+      <c r="I125">
+        <v>41093013.12303829</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B126">
-        <v>-66467282.72898023</v>
-      </c>
-      <c r="C126">
-        <v>-364424192.7075258</v>
-      </c>
-      <c r="D126">
-        <v>470954176.43650603</v>
-      </c>
-      <c r="E126">
-        <v>2160912.0514909476</v>
-      </c>
-      <c r="F126">
-        <v>13936946.98370459</v>
-      </c>
-      <c r="G126">
-        <v>-16665744.160636857</v>
-      </c>
-      <c r="H126">
-        <v>39378012.17693227</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>-82007030.68342727</v>
+      </c>
+      <c r="C127">
+        <v>-69362082.30020069</v>
+      </c>
+      <c r="D127">
+        <v>-380295685.47026736</v>
+      </c>
+      <c r="E127">
+        <v>491465289.45389533</v>
+      </c>
+      <c r="F127">
+        <v>5209870.304871678</v>
+      </c>
+      <c r="G127">
+        <v>14543932.35298853</v>
+      </c>
+      <c r="H127">
+        <v>-17391574.7808985</v>
+      </c>
+      <c r="I127">
+        <v>41093013.12303829</v>
+      </c>
+      <c r="J127">
+        <v>89587856.86759706</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>-66467282.72898023</v>
+        <v>-0.02094605565071106</v>
       </c>
       <c r="C128">
-        <v>-364424192.7075258</v>
+        <v>0.6485365033149719</v>
       </c>
       <c r="D128">
-        <v>470954176.43650603</v>
+        <v>-0.6714123040437698</v>
       </c>
       <c r="E128">
-        <v>2160912.0514909476</v>
+        <v>76446285.04382186</v>
       </c>
       <c r="F128">
-        <v>13936946.98370459</v>
+        <v>0.002862900495529175</v>
       </c>
       <c r="G128">
-        <v>-16665744.160636857</v>
+        <v>0.3107631206512451</v>
       </c>
       <c r="H128">
-        <v>39378012.17693227</v>
+        <v>1929.959607385099</v>
       </c>
       <c r="I128">
-        <v>85848942.44855678</v>
+        <v>61298196.726766594</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>0.6214700937271118</v>
+        <v>-33745786.89196429</v>
       </c>
       <c r="C129">
-        <v>-0.6433911770582199</v>
+        <v>-88768521.14800481</v>
       </c>
       <c r="D129">
-        <v>73255829.02192108</v>
+        <v>-412453605.4859643</v>
       </c>
       <c r="E129">
-        <v>0.3958801254630089</v>
+        <v>544211238.5259334</v>
       </c>
       <c r="F129">
-        <v>0.29779354482889175</v>
+        <v>-7775726.965636343</v>
       </c>
       <c r="G129">
-        <v>1849.4134925827384</v>
+        <v>5969221.893098772</v>
       </c>
       <c r="H129">
-        <v>58739940.28871387</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B130">
-        <v>-85063801.38707031</v>
-      </c>
-      <c r="C130">
-        <v>-395240014.41841865</v>
-      </c>
-      <c r="D130">
-        <v>521498793.80548894</v>
-      </c>
-      <c r="E130">
-        <v>-7451210.257707983</v>
-      </c>
-      <c r="F130">
-        <v>5720098.735263407</v>
-      </c>
-      <c r="G130">
-        <v>-6765603.217733651</v>
-      </c>
-      <c r="H130">
-        <v>81752543.48247024</v>
+        <v>-7060260.445916146</v>
+      </c>
+      <c r="I129">
+        <v>85313050.51845372</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:M129"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="40"/>
+    <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
@@ -6752,6 +7205,7 @@
     <col min="10" max="10" customWidth="1" width="20"/>
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
+    <col min="13" max="13" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6759,36 +7213,39 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="C1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -6802,28 +7259,31 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>181861380.5341978</v>
+        <v>479436490</v>
       </c>
       <c r="C3">
-        <v>-200500696.55450422</v>
+        <v>557376284.6966518</v>
       </c>
       <c r="D3">
-        <v>-862119527.7342094</v>
+        <v>158361479.65876395</v>
       </c>
       <c r="E3">
-        <v>1574854424.5341978</v>
+        <v>-532072338.8376311</v>
       </c>
       <c r="F3">
-        <v>710076445.0965848</v>
-      </c>
-      <c r="I3">
-        <v>2391477238.5059175</v>
-      </c>
-      <c r="K3">
-        <v>1387101.4703185863</v>
+        <v>2011037307</v>
+      </c>
+      <c r="G3">
+        <v>741001870.4247236</v>
+      </c>
+      <c r="J3">
+        <v>2495631447.921071</v>
       </c>
       <c r="L3">
-        <v>41518779.917590335</v>
+        <v>1447512.8573447445</v>
+      </c>
+      <c r="M3">
+        <v>43327016.1109233</v>
       </c>
     </row>
     <row r="4">
@@ -6831,28 +7291,31 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>1229502905.1277235</v>
+        <v>1635465449</v>
       </c>
       <c r="C4">
-        <v>594444118.5578277</v>
+        <v>1283050519.152259</v>
       </c>
       <c r="D4">
-        <v>-588618592.6210725</v>
+        <v>620333494.9113841</v>
       </c>
       <c r="E4">
-        <v>1736065894.1277235</v>
+        <v>-614254256.6849483</v>
       </c>
       <c r="F4">
-        <v>1016086229.4582973</v>
-      </c>
-      <c r="I4">
-        <v>2261500162.0894527</v>
-      </c>
-      <c r="K4">
-        <v>-3092887.595005859</v>
+        <v>1811675465</v>
+      </c>
+      <c r="G4">
+        <v>1060339068.7589843</v>
+      </c>
+      <c r="J4">
+        <v>2359993577.6579094</v>
       </c>
       <c r="L4">
-        <v>65639276.346549705</v>
+        <v>-3227589.802110714</v>
+      </c>
+      <c r="M4">
+        <v>68498014.3785825</v>
       </c>
     </row>
     <row r="5">
@@ -6860,28 +7323,31 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>71660546.69121453</v>
+        <v>41595964</v>
       </c>
       <c r="C5">
-        <v>61828807.10760957</v>
+        <v>442364196.2449558</v>
       </c>
       <c r="D5">
-        <v>88378898.73798087</v>
+        <v>432104262.302225</v>
       </c>
       <c r="E5">
-        <v>-158868639.30878547</v>
+        <v>459810670.1036792</v>
       </c>
       <c r="F5">
-        <v>-43510459.340255186</v>
-      </c>
-      <c r="I5">
-        <v>108755532.8197426</v>
-      </c>
-      <c r="K5">
-        <v>7632173.834270199</v>
+        <v>201794946</v>
+      </c>
+      <c r="G5">
+        <v>-45405437.64943856</v>
+      </c>
+      <c r="J5">
+        <v>113492080.73998995</v>
       </c>
       <c r="L5">
-        <v>2124778.521502993</v>
+        <v>7964572.160722205</v>
+      </c>
+      <c r="M5">
+        <v>2217317.4022943918</v>
       </c>
     </row>
     <row r="6">
@@ -6889,28 +7355,31 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>5038510.423977949</v>
+        <v>7224205</v>
       </c>
       <c r="C6">
-        <v>2187513.3131218962</v>
+        <v>5257949.556539223</v>
       </c>
       <c r="D6">
-        <v>10491016.008519813</v>
+        <v>2282785.1128961705</v>
       </c>
       <c r="E6">
-        <v>10680043.423977949</v>
+        <v>10947924.015693694</v>
       </c>
       <c r="F6">
-        <v>14976453.825295988</v>
-      </c>
-      <c r="I6">
-        <v>5964638.482039821</v>
-      </c>
-      <c r="K6">
-        <v>1646486.2848671505</v>
+        <v>11145184</v>
+      </c>
+      <c r="G6">
+        <v>15628712.054185</v>
+      </c>
+      <c r="J6">
+        <v>6224411.895535565</v>
       </c>
       <c r="L6">
-        <v>130292.23032587011</v>
+        <v>1718194.4636246322</v>
+      </c>
+      <c r="M6">
+        <v>135966.74983373977</v>
       </c>
     </row>
     <row r="7">
@@ -6923,28 +7392,19 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>303528.1725950346</v>
-      </c>
-      <c r="C8">
-        <v>332341.7295986455</v>
-      </c>
-      <c r="D8">
-        <v>165720.4966425658</v>
-      </c>
-      <c r="E8">
-        <v>152462.1725950346</v>
-      </c>
-      <c r="F8">
-        <v>-2545318.9491522256</v>
-      </c>
-      <c r="I8">
-        <v>236195.20254046304</v>
-      </c>
-      <c r="K8">
-        <v>5821535.974285082</v>
+        <v>1319640</v>
+      </c>
+      <c r="G8">
+        <v>-2656173.3108788645</v>
+      </c>
+      <c r="J8">
+        <v>246482.03454210205</v>
       </c>
       <c r="L8">
-        <v>1849379.7644171393</v>
+        <v>6075076.951895368</v>
+      </c>
+      <c r="M8">
+        <v>1929924.4102828011</v>
       </c>
     </row>
     <row r="9">
@@ -6967,16 +7427,19 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>1054755.0872809226</v>
+        <v>1727000</v>
       </c>
       <c r="C12">
-        <v>252975.32101663912</v>
-      </c>
-      <c r="E12">
-        <v>4868735.087280923</v>
-      </c>
-      <c r="I12">
-        <v>1126183.3515561267</v>
+        <v>1100691.5977512607</v>
+      </c>
+      <c r="D12">
+        <v>263992.5203868246</v>
+      </c>
+      <c r="F12">
+        <v>5080779</v>
+      </c>
+      <c r="J12">
+        <v>1175231.168005811</v>
       </c>
     </row>
     <row r="13">
@@ -7059,28 +7522,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-1119245485.7148795</v>
+        <v>-1197624923</v>
       </c>
       <c r="C28">
-        <v>-856733735.1209272</v>
+        <v>-1167991143.2648714</v>
       </c>
       <c r="D28">
-        <v>-361870849.6681742</v>
+        <v>-894046415.8459407</v>
       </c>
       <c r="E28">
-        <v>-2295071.714879589</v>
+        <v>-377631139.3549882</v>
       </c>
       <c r="F28">
-        <v>-262461247.6885173</v>
-      </c>
-      <c r="I28">
-        <v>21221543.596721984</v>
-      </c>
-      <c r="K28">
-        <v>-3152184.768945752</v>
+        <v>-2395028</v>
+      </c>
+      <c r="G28">
+        <v>-273892024.9984409</v>
+      </c>
+      <c r="J28">
+        <v>22145789.52317148</v>
       </c>
       <c r="L28">
-        <v>-26245274.950462367</v>
+        <v>-3289469.5012667454</v>
+      </c>
+      <c r="M28">
+        <v>-27388315.66995361</v>
       </c>
     </row>
     <row r="29">
@@ -7088,19 +7554,22 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>-1103130831.8398018</v>
+        <v>-1182143764</v>
       </c>
       <c r="C29">
-        <v>-838802880.8855242</v>
+        <v>-1151174659.7714612</v>
       </c>
       <c r="D29">
-        <v>-357947819.98028356</v>
+        <v>-875334632.3839703</v>
       </c>
       <c r="E29">
-        <v>82530.16019817101</v>
-      </c>
-      <c r="I29">
-        <v>21249612.229885828</v>
+        <v>-373537252.6870399</v>
+      </c>
+      <c r="F29">
+        <v>86124</v>
+      </c>
+      <c r="J29">
+        <v>22175080.60840364</v>
       </c>
     </row>
     <row r="30">
@@ -7112,16 +7581,19 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B31">
+        <v>-25197</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="K32">
-        <v>-615805.0035627198</v>
-      </c>
       <c r="L32">
-        <v>-5633486.115851729</v>
+        <v>-642624.6957041519</v>
+      </c>
+      <c r="M32">
+        <v>-5878837.099419674</v>
       </c>
     </row>
     <row r="33">
@@ -7129,28 +7601,31 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1587267.5268667</v>
+        <v>-1396549</v>
       </c>
       <c r="C33">
-        <v>-2131891.7540223147</v>
+        <v>-1656396.974432915</v>
       </c>
       <c r="D33">
-        <v>-2238118.584916783</v>
+        <v>-2224740.8109138394</v>
       </c>
       <c r="E33">
-        <v>-615056.5268667002</v>
+        <v>-2335594.0590755716</v>
       </c>
       <c r="F33">
-        <v>-561695.0870457749</v>
-      </c>
-      <c r="I33">
-        <v>90108.61589465645</v>
-      </c>
-      <c r="K33">
-        <v>-257671.98650125097</v>
+        <v>-641844</v>
+      </c>
+      <c r="G33">
+        <v>-586158.1706920061</v>
+      </c>
+      <c r="J33">
+        <v>94033.04866737442</v>
       </c>
       <c r="L33">
-        <v>-997.0392057510215</v>
+        <v>-268894.18072093616</v>
+      </c>
+      <c r="M33">
+        <v>-1040.4625043544354</v>
       </c>
     </row>
     <row r="34">
@@ -7183,28 +7658,31 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-69113.36664990408</v>
+        <v>4121</v>
       </c>
       <c r="C39">
-        <v>711848.7437719441</v>
+        <v>-72121.19190311295</v>
       </c>
       <c r="D39">
-        <v>1066538.926524676</v>
+        <v>742853.5739120163</v>
       </c>
       <c r="E39">
-        <v>-33611.366649904085</v>
+        <v>1112991.31141338</v>
       </c>
       <c r="F39">
-        <v>-56538.673283954304</v>
-      </c>
-      <c r="I39">
-        <v>-43446.30063139073</v>
-      </c>
-      <c r="K39">
-        <v>1131755.4643173832</v>
+        <v>-35073</v>
+      </c>
+      <c r="G39">
+        <v>-59001.059595835286</v>
+      </c>
+      <c r="J39">
+        <v>-45338.484684584</v>
       </c>
       <c r="L39">
-        <v>-312549.1310209963</v>
+        <v>1181045.958803085</v>
+      </c>
+      <c r="M39">
+        <v>-326161.3482400165</v>
       </c>
     </row>
     <row r="40">
@@ -7212,28 +7690,31 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-288315.9605594979</v>
+        <v>25110</v>
       </c>
       <c r="C40">
-        <v>-4381173.665850079</v>
+        <v>-300873.36130101385</v>
       </c>
       <c r="D40">
-        <v>-183722.79824466957</v>
+        <v>-4571984.219780535</v>
       </c>
       <c r="E40">
-        <v>-467953.9605594979</v>
+        <v>-191724.931657805</v>
       </c>
       <c r="F40">
-        <v>351517.4633592635</v>
-      </c>
-      <c r="I40">
-        <v>453278.6987837813</v>
-      </c>
-      <c r="K40">
-        <v>16241.87529689331</v>
+        <v>-488335</v>
+      </c>
+      <c r="G40">
+        <v>366826.8390465176</v>
+      </c>
+      <c r="J40">
+        <v>473020.0050176008</v>
       </c>
       <c r="L40">
-        <v>13352.061128352916</v>
+        <v>16949.24547534598</v>
+      </c>
+      <c r="M40">
+        <v>13933.573403901575</v>
       </c>
     </row>
     <row r="41">
@@ -7246,28 +7727,31 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-97486.42851129612</v>
+        <v>83899</v>
       </c>
       <c r="C42">
-        <v>-203645.37502441643</v>
+        <v>-101732.96110144275</v>
       </c>
       <c r="D42">
-        <v>185735.26768695144</v>
+        <v>-212515.36836442468</v>
       </c>
       <c r="E42">
-        <v>-120930.42851129612</v>
+        <v>193823.6766056676</v>
       </c>
       <c r="F42">
-        <v>271415.7044875301</v>
-      </c>
-      <c r="I42">
-        <v>250659.7426086309</v>
-      </c>
-      <c r="K42">
-        <v>37238.34798270894</v>
+        <v>-126198</v>
+      </c>
+      <c r="G42">
+        <v>283236.4685193119</v>
+      </c>
+      <c r="J42">
+        <v>261576.5378443315</v>
       </c>
       <c r="L42">
-        <v>44033.67668714571</v>
+        <v>38860.161743515855</v>
+      </c>
+      <c r="M42">
+        <v>45951.44228789942</v>
       </c>
     </row>
     <row r="43">
@@ -7279,20 +7763,23 @@
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="C44">
-        <v>390107.8074255534</v>
+      <c r="B44">
+        <v>136141</v>
       </c>
       <c r="D44">
-        <v>863781.1792327403</v>
+        <v>407097.4482643024</v>
       </c>
       <c r="E44">
-        <v>694026.9953623512</v>
-      </c>
-      <c r="K44">
-        <v>-417932.7094245812</v>
+        <v>901400.3601596106</v>
+      </c>
+      <c r="F44">
+        <v>724253</v>
       </c>
       <c r="L44">
-        <v>113650.47299458466</v>
+        <v>-436134.6183693828</v>
+      </c>
+      <c r="M44">
+        <v>118600.20656252968</v>
       </c>
     </row>
     <row r="45">
@@ -7315,28 +7802,31 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-14521188.587852713</v>
+        <v>-14308684</v>
       </c>
       <c r="C48">
-        <v>-12316099.991703717</v>
+        <v>-15153619.246304072</v>
       </c>
       <c r="D48">
-        <v>-4189498.653863022</v>
+        <v>-12852494.085087974</v>
       </c>
       <c r="E48">
-        <v>-1834076.587852713</v>
+        <v>-4371960.9916167185</v>
       </c>
       <c r="F48">
-        <v>-1166563.2476274208</v>
-      </c>
-      <c r="I48">
-        <v>-778669.3898195229</v>
-      </c>
-      <c r="K48">
-        <v>271857.1352012541</v>
+        <v>-1913955</v>
+      </c>
+      <c r="G48">
+        <v>-1217369.6993188937</v>
+      </c>
+      <c r="J48">
+        <v>-812582.1920768844</v>
       </c>
       <c r="L48">
-        <v>-114763.47799030942</v>
+        <v>283697.1245328879</v>
+      </c>
+      <c r="M48">
+        <v>-119761.68542768472</v>
       </c>
     </row>
     <row r="49">
@@ -7344,19 +7834,22 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>181917966.10405874</v>
+        <v>479436490</v>
       </c>
       <c r="C49">
-        <v>-200460809.45548958</v>
+        <v>557423572.1323436</v>
       </c>
       <c r="D49">
-        <v>-862110543.5512655</v>
+        <v>158391341.3676682</v>
       </c>
       <c r="E49">
-        <v>1574902183.1040587</v>
-      </c>
-      <c r="I49">
-        <v>2391477238.5059175</v>
+        <v>-532074725.93625724</v>
+      </c>
+      <c r="F49">
+        <v>2011075383</v>
+      </c>
+      <c r="J49">
+        <v>2495631447.921071</v>
       </c>
     </row>
     <row r="50">
@@ -7423,23 +7916,23 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="B62">
-        <v>-56585.569860870535</v>
-      </c>
       <c r="C62">
-        <v>-39887.09901477981</v>
+        <v>-47287.43569175759</v>
       </c>
       <c r="D62">
-        <v>-8984.182943799711</v>
+        <v>-29861.708904689083</v>
       </c>
       <c r="E62">
-        <v>-47758.569860870535</v>
-      </c>
-      <c r="K62">
-        <v>37238.34798270894</v>
+        <v>2387.09862625182</v>
+      </c>
+      <c r="F62">
+        <v>-38076</v>
       </c>
       <c r="L62">
-        <v>44033.67668714571</v>
+        <v>38860.161743515855</v>
+      </c>
+      <c r="M62">
+        <v>45951.44228789942</v>
       </c>
     </row>
     <row r="63">
@@ -7449,532 +7942,581 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="67"/>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" t="str">
+        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
+      </c>
+      <c r="B67">
+        <v>-1483714794</v>
+      </c>
+      <c r="C67">
+        <v>-1137807537.1537056</v>
+      </c>
+      <c r="D67">
+        <v>-653729295.580754</v>
+      </c>
+      <c r="E67">
+        <v>466532327.919352</v>
+      </c>
+      <c r="F67">
+        <v>-1805521617</v>
+      </c>
+      <c r="G67">
+        <v>-992628090.5467083</v>
+      </c>
+      <c r="J67">
+        <v>-2768566947.6739235</v>
+      </c>
+      <c r="L67">
+        <v>-19328581.528869905</v>
+      </c>
+      <c r="M67">
+        <v>-56066903.60578507</v>
+      </c>
+    </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
-      </c>
-      <c r="B68">
-        <v>-1090321580.227889</v>
-      </c>
-      <c r="C68">
-        <v>-626446156.0974364</v>
-      </c>
-      <c r="D68">
-        <v>447061783.54803324</v>
-      </c>
-      <c r="E68">
-        <v>-1730168872.227889</v>
-      </c>
-      <c r="F68">
-        <v>-951201142.6292624</v>
-      </c>
-      <c r="I68">
-        <v>-2653021881.1585484</v>
-      </c>
-      <c r="K68">
-        <v>-18521910.68412927</v>
-      </c>
-      <c r="L68">
-        <v>-53726973.15480414</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğuracak Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Kaybı Sonucunu Doğurmayan Satışlara İlişkin Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıkların Kontrolünün Elde Edilmesine Yönelik Alışlara İlişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklarda İlave Pay Alımlarına ilişkin Nakit Çıkışları</v>
+        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
+        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
+      </c>
+      <c r="B73">
+        <v>-1474955288</v>
+      </c>
+      <c r="C73">
+        <v>-1129319860.826878</v>
+      </c>
+      <c r="F73">
+        <v>-1799392782</v>
+      </c>
+      <c r="L73">
+        <v>-18727209.50227223</v>
+      </c>
+      <c r="M73">
+        <v>-55246596.2905873</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
-      </c>
-      <c r="K74">
-        <v>-17945636.685546447</v>
-      </c>
-      <c r="L74">
-        <v>-52940901.04687748</v>
+        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v xml:space="preserve">    İştirakler ve/veya İş Ortaklıkları Sermaye Avansı Ödemelerinden Nakit Çıkışları</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
+      </c>
+      <c r="B78">
+        <v>-8759506</v>
+      </c>
+      <c r="C78">
+        <v>-8487676.326827472</v>
+      </c>
+      <c r="D78">
+        <v>-5337099.397258132</v>
+      </c>
+      <c r="E78">
+        <v>-3782647.206867725</v>
+      </c>
+      <c r="F78">
+        <v>-6128835</v>
+      </c>
+      <c r="G78">
+        <v>-6684729.003937136</v>
+      </c>
+      <c r="J78">
+        <v>-832455.5742861931</v>
+      </c>
+      <c r="L78">
+        <v>-601372.0265976819</v>
+      </c>
+      <c r="M78">
+        <v>-820308.7061904233</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
-      </c>
-      <c r="B79">
-        <v>-8133445.79700881</v>
-      </c>
-      <c r="C79">
-        <v>-5114356.972213221</v>
-      </c>
-      <c r="D79">
-        <v>-3624779.2403886565</v>
-      </c>
-      <c r="E79">
-        <v>-5873049.79700881</v>
-      </c>
-      <c r="F79">
-        <v>-6405744.434665257</v>
-      </c>
-      <c r="I79">
-        <v>-797713.3641392412</v>
-      </c>
-      <c r="K79">
-        <v>-576273.9985828294</v>
-      </c>
-      <c r="L79">
-        <v>-786073.4408667701</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Satımından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">    Yatırım Amaçlı Gayrimenkul Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Satışlarından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">    Satış Amacıyla Elde Tutulan Duran Varlık Alımlarından Nakit Çıkışları</v>
+        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">    Canlı Varlık Satışından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">    Canlı Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="J85">
+        <v>-2767734492.0996375</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="D86">
-        <v>450686562.78842163</v>
-      </c>
-      <c r="E86">
-        <v>-1724295822.4308805</v>
-      </c>
-      <c r="I86">
-        <v>-2652224167.7944093</v>
+        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlar</v>
+        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">    Verilen Nakit Avans ve Borçlardan Geri Ödemeler</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Alınan Temettüler</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    Alınan Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
         <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
-    <row r="101"/>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
+      </c>
+      <c r="B101">
+        <v>964078795</v>
+      </c>
+      <c r="C101">
+        <v>627448644.4453526</v>
+      </c>
+      <c r="D101">
+        <v>626291222.5634782</v>
+      </c>
+      <c r="E101">
+        <v>559367528.2491361</v>
+      </c>
+      <c r="F101">
+        <v>-162060449</v>
+      </c>
+      <c r="G101">
+        <v>379459447.6847106</v>
+      </c>
+      <c r="J101">
+        <v>246190221.87641504</v>
+      </c>
+      <c r="L101">
+        <v>101481342.05209883</v>
+      </c>
+      <c r="M101">
+        <v>45494097.81355893</v>
+      </c>
+    </row>
     <row r="102">
       <c r="A102" t="str">
-        <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
-      </c>
-      <c r="B102">
-        <v>950683812.7451826</v>
-      </c>
-      <c r="C102">
-        <v>949574695.4161168</v>
-      </c>
-      <c r="D102">
-        <v>885444035.4972411</v>
-      </c>
-      <c r="E102">
-        <v>194124574.74518263</v>
-      </c>
-      <c r="F102">
-        <v>363622854.9812347</v>
-      </c>
-      <c r="I102">
-        <v>235915568.56306645</v>
-      </c>
-      <c r="K102">
-        <v>97246057.64717199</v>
-      </c>
-      <c r="L102">
-        <v>43595419.3068531</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v xml:space="preserve">    Bağlı Ortaklıklardaki Kontrolün Kaybına Yol Açmayan Şekilde Ortaklık Payları Değişmelerinden Kaynaklanan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="B104">
+        <v>901528763</v>
+      </c>
+      <c r="J104">
+        <v>237760272.93971056</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
-      </c>
-      <c r="E105">
-        <v>200687340.5226202</v>
-      </c>
-      <c r="I105">
-        <v>227837440.2718519</v>
+        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
+      </c>
+      <c r="L106">
+        <v>47181.079793045574</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
-      </c>
-      <c r="K107">
-        <v>45211.995748487825</v>
+        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v xml:space="preserve">    Ortak Kontrole Tabi İşletmelerin Birleşme Etkisinden Kaynaklanan Nakit Girişleri (Çıkışları)</v>
+        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+      </c>
+      <c r="J109">
+        <v>52116.08944515841</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
+        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B110">
+        <v>11861</v>
+      </c>
+      <c r="C110">
+        <v>138203.91756701373</v>
+      </c>
+      <c r="D110">
+        <v>7151.250037513935</v>
       </c>
       <c r="E110">
-        <v>-4546.822558715614</v>
-      </c>
-      <c r="I110">
-        <v>49941.04468905403</v>
+        <v>-40891.115084831225</v>
+      </c>
+      <c r="F110">
+        <v>-4745</v>
+      </c>
+      <c r="L110">
+        <v>-6364283.798326314</v>
+      </c>
+      <c r="M110">
+        <v>3764318.227151091</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="K111">
-        <v>-6098672.885280427</v>
-      </c>
-      <c r="L111">
-        <v>3607215.8676410047</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Artış</v>
+        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v xml:space="preserve">    İlişkili Taraflardan Alınan Diğer Borçlardaki Azalış</v>
+        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
+      </c>
+      <c r="B113">
+        <v>-5461829</v>
+      </c>
+      <c r="C113">
+        <v>-5742031.520438224</v>
+      </c>
+      <c r="D113">
+        <v>436316.33865658566</v>
+      </c>
+      <c r="E113">
+        <v>10519347.491736867</v>
+      </c>
+      <c r="F113">
+        <v>10413780</v>
+      </c>
+      <c r="J113">
+        <v>8377832.8472593175</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
-      </c>
-      <c r="B114">
-        <v>-22039773.954878844</v>
-      </c>
-      <c r="C114">
-        <v>-16119277.044605775</v>
-      </c>
-      <c r="D114">
-        <v>-6457057.281417331</v>
-      </c>
-      <c r="E114">
-        <v>-6558218.954878844</v>
-      </c>
-      <c r="I114">
-        <v>8028187.246525489</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v xml:space="preserve">    Türev Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v xml:space="preserve">    Devlet Teşviklerinden Elde Edilen Nakit Girişleri</v>
+        <v xml:space="preserve">    Ödenen Temettüler</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v xml:space="preserve">    Ödenen Temettüler</v>
+        <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v xml:space="preserve">    Ödenen Faiz</v>
+        <v xml:space="preserve">    Alınan Faiz</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v xml:space="preserve">    Alınan Faiz</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Çıkışları</v>
+        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v xml:space="preserve">    Katılım (Kar) Payı ve Diğer Finansal Araçlardan Nakit Girişleri</v>
+        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
+        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
+      </c>
+      <c r="B123">
+        <v>68000000</v>
+      </c>
+      <c r="C123">
+        <v>-268476290.8020504</v>
+      </c>
+      <c r="D123">
+        <v>-275681008.278695</v>
+      </c>
+      <c r="E123">
+        <v>-354384705.1167635</v>
+      </c>
+      <c r="F123">
+        <v>-172469484</v>
+      </c>
+      <c r="L123">
+        <v>107798444.77063212</v>
+      </c>
+      <c r="M123">
+        <v>41729779.58640783</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="K124">
-        <v>103299518.53670394</v>
-      </c>
-      <c r="L124">
-        <v>39988203.43921209</v>
+        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v xml:space="preserve">    Durdurulan Faaliyetlere İlişkin Net Nakit Akışları</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B125">
+        <v>-40199509</v>
+      </c>
+      <c r="C125">
+        <v>47017391.98829895</v>
+      </c>
+      <c r="D125">
+        <v>130923406.64148816</v>
+      </c>
+      <c r="E125">
+        <v>493827517.33085704</v>
+      </c>
+      <c r="F125">
+        <v>43455241</v>
+      </c>
+      <c r="J125">
+        <v>-26745277.876437392</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
-      </c>
-      <c r="B126">
-        <v>42223613.05149095</v>
-      </c>
-      <c r="C126">
-        <v>122627842.76417577</v>
-      </c>
-      <c r="D126">
-        <v>470386291.3110647</v>
-      </c>
-      <c r="E126">
-        <v>38810127.05149095</v>
-      </c>
-      <c r="I126">
-        <v>-25629074.08956436</v>
+        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Nakit ve Nakit Benzerleri Üzerindeki Etkisi</v>
+        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+      </c>
+      <c r="B127">
+        <v>-40199509</v>
+      </c>
+      <c r="C127">
+        <v>47017391.98829895</v>
+      </c>
+      <c r="D127">
+        <v>130923406.64148816</v>
+      </c>
+      <c r="E127">
+        <v>493827517.33085704</v>
+      </c>
+      <c r="F127">
+        <v>43455241</v>
+      </c>
+      <c r="G127">
+        <v>127833227.56272538</v>
+      </c>
+      <c r="J127">
+        <v>-26745277.876437392</v>
+      </c>
+      <c r="L127">
+        <v>83600273.3805737</v>
+      </c>
+      <c r="M127">
+        <v>32754210.318697162</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
+        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>42223613.05149095</v>
+        <v>76446285</v>
       </c>
       <c r="C128">
-        <v>122627842.76417577</v>
+        <v>76446285.02380896</v>
       </c>
       <c r="D128">
-        <v>470386291.3110647</v>
+        <v>76446284.68603557</v>
       </c>
       <c r="E128">
-        <v>38810127.05149095</v>
+        <v>76448215.31705526</v>
       </c>
       <c r="F128">
-        <v>122498157.44855678</v>
-      </c>
-      <c r="I128">
-        <v>-25629074.08956436</v>
-      </c>
-      <c r="K128">
-        <v>80111248.43336134</v>
-      </c>
-      <c r="L128">
-        <v>31387226.069639303</v>
+        <v>61300127</v>
+      </c>
+      <c r="J128">
+        <v>116354487.84161593</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
+        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>73255829.39588013</v>
+        <v>9243325</v>
       </c>
       <c r="C129">
-        <v>73255829.07220358</v>
+        <v>35213384.926327944</v>
       </c>
       <c r="D129">
-        <v>73257679.12908733</v>
+        <v>129951127.96743153</v>
       </c>
       <c r="E129">
-        <v>58741790.395880125</v>
-      </c>
-      <c r="I129">
-        <v>111498478.47246654</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
-      </c>
-      <c r="B130">
-        <v>33743767.74229202</v>
-      </c>
-      <c r="C130">
-        <v>124527667.86462574</v>
-      </c>
-      <c r="D130">
-        <v>513002079.0653107</v>
-      </c>
-      <c r="E130">
-        <v>73255828.74229202</v>
-      </c>
-      <c r="I130">
-        <v>58741790.395880125</v>
+        <v>535344473.00747967</v>
+      </c>
+      <c r="F129">
+        <v>76446285</v>
+      </c>
+      <c r="J129">
+        <v>61300127.410258695</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/BULGS (TRY).xlsx
+++ b/data/BULGS (TRY).xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:L108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -415,6 +415,8 @@
     <col min="8" max="8" customWidth="1" width="20"/>
     <col min="9" max="9" customWidth="1" width="20"/>
     <col min="10" max="10" customWidth="1" width="20"/>
+    <col min="11" max="11" customWidth="1" width="20"/>
+    <col min="12" max="12" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,30 +424,36 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -459,31 +467,37 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>9243325</v>
+        <v>20502322</v>
       </c>
       <c r="C3">
-        <v>42989111.89196429</v>
+        <v>33711112.3898452</v>
       </c>
       <c r="D3">
-        <v>131757633.0399691</v>
+        <v>10884798</v>
       </c>
       <c r="E3">
-        <v>544211238.5259334</v>
+        <v>50623937.644567326</v>
       </c>
       <c r="F3">
-        <v>76446285</v>
+        <v>155157664.47964194</v>
       </c>
       <c r="G3">
-        <v>84222012.32159483</v>
+        <v>640862641.5415528</v>
       </c>
       <c r="H3">
-        <v>61300127.410258695</v>
+        <v>90023073.16151424</v>
       </c>
       <c r="I3">
-        <v>116354487.87224881</v>
+        <v>99179762.32640848</v>
       </c>
       <c r="J3">
-        <v>32754210.318697162</v>
+        <v>72186972.2598536</v>
+      </c>
+      <c r="K3">
+        <v>137018935.24837703</v>
+      </c>
+      <c r="L3">
+        <v>38571327.198799774</v>
       </c>
     </row>
     <row r="4">
@@ -496,25 +510,31 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
-        <v>1182143764</v>
+        <v>972561277</v>
       </c>
       <c r="C5">
-        <v>1151174659.4044464</v>
+        <v>1149543920.3070366</v>
       </c>
       <c r="D5">
-        <v>875334631.9762816</v>
+        <v>1392074424</v>
       </c>
       <c r="E5">
-        <v>404345565.86308545</v>
-      </c>
-      <c r="H5">
-        <v>86124.53419008772</v>
-      </c>
-      <c r="I5">
-        <v>22261204.3839741</v>
+        <v>1355622193.874401</v>
+      </c>
+      <c r="F5">
+        <v>1030793237.5681559</v>
+      </c>
+      <c r="G5">
+        <v>476156957.24424565</v>
       </c>
       <c r="J5">
-        <v>21618579.688269947</v>
+        <v>101420.17028552273</v>
+      </c>
+      <c r="K5">
+        <v>26214773.30025811</v>
+      </c>
+      <c r="L5">
+        <v>25458019.06430314</v>
       </c>
     </row>
     <row r="6">
@@ -526,8 +546,8 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
-      <c r="B7">
-        <v>25197</v>
+      <c r="D7">
+        <v>29672</v>
       </c>
     </row>
     <row r="8">
@@ -545,28 +565,34 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>2217080</v>
+        <v>24124268</v>
       </c>
       <c r="C10">
-        <v>2528374.737908423</v>
+        <v>25816198.696398</v>
       </c>
       <c r="D10">
-        <v>3174497.045798919</v>
+        <v>2610800</v>
       </c>
       <c r="E10">
-        <v>3354537.6297716512</v>
+        <v>2977411.708240032</v>
       </c>
       <c r="F10">
-        <v>808816</v>
+        <v>3738284.7290089624</v>
       </c>
       <c r="G10">
-        <v>859527.7440383824</v>
+        <v>3950300.3509979057</v>
       </c>
       <c r="H10">
-        <v>114522.93374308544</v>
+        <v>952460.9592500577</v>
       </c>
       <c r="I10">
-        <v>270392.2798080882</v>
+        <v>1012179.0612312761</v>
+      </c>
+      <c r="J10">
+        <v>134862.09883220654</v>
+      </c>
+      <c r="K10">
+        <v>318413.6938436204</v>
       </c>
     </row>
     <row r="11">
@@ -604,31 +630,37 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>94661</v>
+        <v>278721</v>
       </c>
       <c r="C17">
-        <v>201514.1132685123</v>
+        <v>1102607.2313757844</v>
       </c>
       <c r="D17">
-        <v>173735.28569969063</v>
+        <v>111471</v>
       </c>
       <c r="E17">
-        <v>165666.32459242764</v>
+        <v>237302.8298477676</v>
       </c>
       <c r="F17">
-        <v>64470</v>
+        <v>204590.5086856716</v>
       </c>
       <c r="G17">
-        <v>129392.91855622765</v>
+        <v>195088.50769116223</v>
       </c>
       <c r="H17">
-        <v>62803.448052746266</v>
+        <v>75919.8112337679</v>
       </c>
       <c r="I17">
-        <v>14046.243808784877</v>
+        <v>152372.97893245087</v>
       </c>
       <c r="J17">
-        <v>1186843.6161802895</v>
+        <v>73957.28123149132</v>
+      </c>
+      <c r="K17">
+        <v>16540.84346993065</v>
+      </c>
+      <c r="L17">
+        <v>1397625.92375384</v>
       </c>
     </row>
     <row r="18">
@@ -641,31 +673,37 @@
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
       <c r="B19">
-        <v>17058319</v>
+        <v>894488</v>
       </c>
       <c r="C19">
-        <v>17101819.809023466</v>
+        <v>608329.4521302183</v>
       </c>
       <c r="D19">
-        <v>13443913.575259324</v>
+        <v>20087616</v>
       </c>
       <c r="E19">
-        <v>4580558.57703177</v>
+        <v>20139086.887776863</v>
       </c>
       <c r="F19">
-        <v>2883283</v>
+        <v>15831539.954657635</v>
       </c>
       <c r="G19">
-        <v>2116577.5413948447</v>
+        <v>5394061.462904738</v>
       </c>
       <c r="H19">
-        <v>1005990.0053305023</v>
+        <v>3395351.343160106</v>
       </c>
       <c r="I19">
-        <v>171313.26413608008</v>
+        <v>2492479.7177653047</v>
       </c>
       <c r="J19">
-        <v>444181.51086629514</v>
+        <v>1184652.8820807957</v>
+      </c>
+      <c r="K19">
+        <v>201738.33837524152</v>
+      </c>
+      <c r="L19">
+        <v>523067.7285326346</v>
       </c>
     </row>
     <row r="20">
@@ -678,16 +716,22 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>133648</v>
+        <v>810587</v>
       </c>
       <c r="C21">
-        <v>105781.76070764607</v>
+        <v>342943.7074227903</v>
       </c>
       <c r="D21">
-        <v>112971.74450939763</v>
+        <v>157382</v>
       </c>
       <c r="E21">
-        <v>25925.686281809598</v>
+        <v>124568.50170467033</v>
+      </c>
+      <c r="F21">
+        <v>133035.41985268999</v>
+      </c>
+      <c r="G21">
+        <v>30530.063729189867</v>
       </c>
     </row>
     <row r="22">
@@ -705,31 +749,37 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>1210915994</v>
+        <v>1019171663</v>
       </c>
       <c r="C24">
-        <v>1214101261.7173188</v>
+        <v>1211125111.7842085</v>
       </c>
       <c r="D24">
-        <v>1023997382.6675181</v>
+        <v>1425956163</v>
       </c>
       <c r="E24">
-        <v>956683492.6066964</v>
+        <v>1429724501.4465377</v>
       </c>
       <c r="F24">
-        <v>80202854</v>
+        <v>1205858352.6600027</v>
       </c>
       <c r="G24">
-        <v>87327510.5255843</v>
+        <v>1126589579.1711211</v>
       </c>
       <c r="H24">
-        <v>62569568.331575125</v>
+        <v>94446805.27515818</v>
       </c>
       <c r="I24">
-        <v>139071444.04397586</v>
+        <v>102836794.08433752</v>
       </c>
       <c r="J24">
-        <v>56003815.13401369</v>
+        <v>73681864.69228365</v>
+      </c>
+      <c r="K24">
+        <v>163770401.42432392</v>
+      </c>
+      <c r="L24">
+        <v>65950039.91538939</v>
       </c>
     </row>
     <row r="25">
@@ -742,31 +792,37 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B26">
-        <v>6263971198</v>
+        <v>6694281091</v>
       </c>
       <c r="C26">
-        <v>5564134654.217678</v>
+        <v>7399472302.91061</v>
       </c>
       <c r="D26">
-        <v>5129657646.933014</v>
+        <v>7376356718</v>
       </c>
       <c r="E26">
-        <v>4482322512.5999</v>
+        <v>6552319724.32872</v>
       </c>
       <c r="F26">
-        <v>4789015910</v>
+        <v>6040680010.06683</v>
       </c>
       <c r="G26">
-        <v>4434814794.8650875</v>
+        <v>5278378766.0222225</v>
       </c>
       <c r="H26">
-        <v>2989623127.8053975</v>
+        <v>5639540621.726559</v>
       </c>
       <c r="I26">
-        <v>221888635.85472813</v>
+        <v>5222433722.3961315</v>
       </c>
       <c r="J26">
-        <v>203161426.3524559</v>
+        <v>3520577377.4327993</v>
+      </c>
+      <c r="K26">
+        <v>261295848.4412785</v>
+      </c>
+      <c r="L26">
+        <v>239242704.18274382</v>
       </c>
     </row>
     <row r="27">
@@ -788,23 +844,23 @@
       <c r="A30" t="str">
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
-      <c r="E30">
-        <v>10643.802395513574</v>
-      </c>
-      <c r="F30">
-        <v>11715</v>
-      </c>
       <c r="G30">
-        <v>12449.384243278335</v>
+        <v>12534.131668635291</v>
       </c>
       <c r="H30">
-        <v>64164.72826730738</v>
+        <v>13795.572958020646</v>
       </c>
       <c r="I30">
-        <v>2328.5217009215576</v>
+        <v>14660.38315071096</v>
       </c>
       <c r="J30">
-        <v>3826.6207880735983</v>
+        <v>75560.3235290831</v>
+      </c>
+      <c r="K30">
+        <v>2742.0649602558838</v>
+      </c>
+      <c r="L30">
+        <v>4506.225033252052</v>
       </c>
     </row>
     <row r="31">
@@ -852,31 +908,37 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>6284121</v>
+        <v>11046643</v>
       </c>
       <c r="C39">
-        <v>6314770.494538521</v>
+        <v>9239156.115208162</v>
       </c>
       <c r="D39">
-        <v>6610242.653106312</v>
+        <v>7400085</v>
       </c>
       <c r="E39">
-        <v>6786489.596631118</v>
+        <v>7436267.782378343</v>
       </c>
       <c r="F39">
-        <v>6967616</v>
+        <v>7784215.517810336</v>
       </c>
       <c r="G39">
-        <v>7256911.603532635</v>
+        <v>7991763.752383499</v>
       </c>
       <c r="H39">
-        <v>1825300.0630831984</v>
+        <v>8205058.034269908</v>
       </c>
       <c r="I39">
-        <v>1098382.0474277164</v>
+        <v>8545732.264314217</v>
       </c>
       <c r="J39">
-        <v>731122.4302656999</v>
+        <v>2149471.6338492488</v>
+      </c>
+      <c r="K39">
+        <v>1293453.6637703076</v>
+      </c>
+      <c r="L39">
+        <v>860969.0847610605</v>
       </c>
     </row>
     <row r="40">
@@ -884,31 +946,37 @@
         <v xml:space="preserve">    Kullanım Hakkı Varlıkları</v>
       </c>
       <c r="B40">
-        <v>5287643</v>
+        <v>11800364</v>
       </c>
       <c r="C40">
-        <v>7022820.694703642</v>
+        <v>14364311.497119023</v>
       </c>
       <c r="D40">
-        <v>9167663.798123984</v>
+        <v>6226648</v>
       </c>
       <c r="E40">
-        <v>11433340.629186142</v>
+        <v>8270067.030719704</v>
       </c>
       <c r="F40">
-        <v>17772560</v>
+        <v>10795832.247684512</v>
       </c>
       <c r="G40">
-        <v>20818376.389884252</v>
+        <v>13463891.148428435</v>
       </c>
       <c r="H40">
-        <v>17896825.58946192</v>
+        <v>20928949.90446431</v>
       </c>
       <c r="I40">
-        <v>8119855.625526492</v>
+        <v>24515700.414356183</v>
       </c>
       <c r="J40">
-        <v>12243756.581388354</v>
+        <v>21075284.94548807</v>
+      </c>
+      <c r="K40">
+        <v>9561934.331245845</v>
+      </c>
+      <c r="L40">
+        <v>14418236.20988378</v>
       </c>
     </row>
     <row r="41">
@@ -916,51 +984,57 @@
         <v xml:space="preserve">    Maddi Olmayan Duran Varlıklar</v>
       </c>
       <c r="B41">
-        <v>8127278</v>
+        <v>6821031</v>
       </c>
       <c r="C41">
-        <v>8189569.503171756</v>
+        <v>7668995.561335906</v>
       </c>
       <c r="D41">
-        <v>5171563.753812852</v>
+        <v>9570558</v>
       </c>
       <c r="E41">
-        <v>138808.26500580434</v>
+        <v>9644029.327852057</v>
       </c>
       <c r="F41">
-        <v>140145</v>
+        <v>6090028.602029904</v>
       </c>
       <c r="G41">
-        <v>146368.59289197836</v>
+        <v>163460.48203703266</v>
       </c>
       <c r="H41">
-        <v>38236.26694976811</v>
+        <v>165034.6199062572</v>
       </c>
       <c r="I41">
-        <v>37954.6255264908</v>
+        <v>172363.51702980022</v>
       </c>
       <c r="J41">
-        <v>20931.65744054217</v>
+        <v>45026.9919204336</v>
+      </c>
+      <c r="K41">
+        <v>44695.3312458435</v>
+      </c>
+      <c r="L41">
+        <v>24649.10007283783</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
-      <c r="E42">
-        <v>288.98815442567576</v>
-      </c>
-      <c r="F42">
-        <v>34312</v>
+      <c r="G42">
+        <v>340.3121782657402</v>
       </c>
       <c r="H42">
-        <v>903.1570654299603</v>
-      </c>
-      <c r="I42">
-        <v>4319.03218719321</v>
+        <v>40405.77885920652</v>
       </c>
       <c r="J42">
-        <v>12567.618618773158</v>
+        <v>1063.5569089791586</v>
+      </c>
+      <c r="K42">
+        <v>5086.088232732685</v>
+      </c>
+      <c r="L42">
+        <v>14799.615839851795</v>
       </c>
     </row>
     <row r="43">
@@ -988,31 +1062,37 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>6283670240</v>
+        <v>6723949129</v>
       </c>
       <c r="C47">
-        <v>5585661814.910092</v>
+        <v>7430744766.084273</v>
       </c>
       <c r="D47">
-        <v>5150607117.138058</v>
+        <v>7399554009</v>
       </c>
       <c r="E47">
-        <v>4500692083.881274</v>
+        <v>6577670088.46967</v>
       </c>
       <c r="F47">
-        <v>4813942258</v>
+        <v>6065350086.434355</v>
       </c>
       <c r="G47">
-        <v>4463048900.83564</v>
+        <v>5300010755.848919</v>
       </c>
       <c r="H47">
-        <v>3009448557.610225</v>
+        <v>5668893865.637016</v>
       </c>
       <c r="I47">
-        <v>231151475.707097</v>
+        <v>5255682178.974982</v>
       </c>
       <c r="J47">
-        <v>216173631.26095736</v>
+        <v>3543923784.8844953</v>
+      </c>
+      <c r="K47">
+        <v>272203759.9207336</v>
+      </c>
+      <c r="L47">
+        <v>254565864.4183346</v>
       </c>
     </row>
     <row r="48">
@@ -1020,31 +1100,37 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>7494586234</v>
+        <v>7743120792</v>
       </c>
       <c r="C48">
-        <v>6799763076.627411</v>
+        <v>8641869877.868483</v>
       </c>
       <c r="D48">
-        <v>6174604499.805576</v>
+        <v>8825510172</v>
       </c>
       <c r="E48">
-        <v>5457375576.48797</v>
+        <v>8007394589.916208</v>
       </c>
       <c r="F48">
-        <v>4894145112</v>
+        <v>7271208439.0943575</v>
       </c>
       <c r="G48">
-        <v>4550376411.361224</v>
+        <v>6426600335.0200405</v>
       </c>
       <c r="H48">
-        <v>3072018125.9418006</v>
+        <v>5763340670.912175</v>
       </c>
       <c r="I48">
-        <v>370222919.7510728</v>
+        <v>5358518973.05932</v>
       </c>
       <c r="J48">
-        <v>272177446.394971</v>
+        <v>3617605649.576779</v>
+      </c>
+      <c r="K48">
+        <v>435974161.3450574</v>
+      </c>
+      <c r="L48">
+        <v>320515904.33372396</v>
       </c>
     </row>
     <row r="49">
@@ -1057,31 +1143,37 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>7427565</v>
+        <v>8846562</v>
       </c>
       <c r="C50">
-        <v>7397419.427352534</v>
+        <v>7295143.173166544</v>
       </c>
       <c r="D50">
-        <v>6550442.793430752</v>
+        <v>8746586</v>
       </c>
       <c r="E50">
-        <v>5692087.888066092</v>
+        <v>8711194.145208808</v>
       </c>
       <c r="F50">
-        <v>10646397</v>
+        <v>7713795.259420785</v>
       </c>
       <c r="G50">
-        <v>8525329.98384109</v>
+        <v>6702997.3319062255</v>
       </c>
       <c r="H50">
-        <v>6854451.646532939</v>
+        <v>12537187.07243296</v>
       </c>
       <c r="I50">
-        <v>2471824.5460065873</v>
+        <v>10039420.55341705</v>
       </c>
       <c r="J50">
-        <v>4445558.269891852</v>
+        <v>8071795.798290217</v>
+      </c>
+      <c r="K50">
+        <v>2910818.2555578435</v>
+      </c>
+      <c r="L50">
+        <v>5235085.22846138</v>
       </c>
     </row>
     <row r="51">
@@ -1094,31 +1186,37 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>77984</v>
+        <v>468902</v>
       </c>
       <c r="C52">
-        <v>186371.12659998456</v>
+        <v>71787.80010810141</v>
       </c>
       <c r="D52">
-        <v>126494.69791869535</v>
+        <v>91833</v>
       </c>
       <c r="E52">
-        <v>36613.49098890239</v>
+        <v>219470.46301993934</v>
       </c>
       <c r="F52">
-        <v>52874</v>
+        <v>148960.03704141223</v>
       </c>
       <c r="G52">
-        <v>487245.2524068151</v>
+        <v>43116.012478466444</v>
       </c>
       <c r="H52">
-        <v>541208.3634575628</v>
+        <v>62264.37256358375</v>
       </c>
       <c r="I52">
-        <v>68187.85083684328</v>
+        <v>573779.5499809989</v>
       </c>
       <c r="J52">
-        <v>51238.6053614973</v>
+        <v>637326.4586914008</v>
+      </c>
+      <c r="K52">
+        <v>80297.94887497231</v>
+      </c>
+      <c r="L52">
+        <v>60338.533378725035</v>
       </c>
     </row>
     <row r="53">
@@ -1131,31 +1229,37 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>427118</v>
+        <v>512298</v>
       </c>
       <c r="C54">
-        <v>325535.08016405225</v>
+        <v>759194.8052545557</v>
       </c>
       <c r="D54">
-        <v>283804.7670209472</v>
+        <v>502968</v>
       </c>
       <c r="E54">
-        <v>382193.37511210993</v>
+        <v>383349.80356792855</v>
       </c>
       <c r="F54">
-        <v>343219</v>
+        <v>334208.2261435364</v>
       </c>
       <c r="G54">
-        <v>427267.0402072712</v>
+        <v>450070.5582954558</v>
       </c>
       <c r="H54">
-        <v>469416.53921886353</v>
+        <v>404174.3708987527</v>
       </c>
       <c r="I54">
-        <v>207839.34020806284</v>
+        <v>503149.26382731117</v>
       </c>
       <c r="J54">
-        <v>168979.17846454703</v>
+        <v>552784.4741353301</v>
+      </c>
+      <c r="K54">
+        <v>244751.4111299364</v>
+      </c>
+      <c r="L54">
+        <v>198989.72128843787</v>
       </c>
     </row>
     <row r="55">
@@ -1163,22 +1267,28 @@
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
       <c r="B55">
-        <v>860394</v>
+        <v>25748100</v>
       </c>
       <c r="C55">
-        <v>468260.67755002645</v>
+        <v>1182518.4187894715</v>
       </c>
       <c r="D55">
-        <v>407097.6639582143</v>
+        <v>1013187</v>
       </c>
       <c r="E55">
-        <v>1139856.0964263594</v>
+        <v>551423.3325235655</v>
       </c>
       <c r="F55">
-        <v>724253</v>
-      </c>
-      <c r="J55">
-        <v>436134.6183693828</v>
+        <v>479397.82536707784</v>
+      </c>
+      <c r="G55">
+        <v>1342293.4647797232</v>
+      </c>
+      <c r="H55">
+        <v>852879.6501549575</v>
+      </c>
+      <c r="L55">
+        <v>513591.7155128734</v>
       </c>
     </row>
     <row r="56">
@@ -1216,24 +1326,30 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>976495</v>
+        <v>1356797</v>
+      </c>
+      <c r="C62">
+        <v>1451954.6207425378</v>
+      </c>
+      <c r="D62">
+        <v>1149906</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
-      <c r="G63">
-        <v>62594.669379611754</v>
-      </c>
-      <c r="H63">
-        <v>36661.63224004023</v>
-      </c>
       <c r="I63">
-        <v>14566.475060962093</v>
+        <v>73711.42366279257</v>
       </c>
       <c r="J63">
-        <v>3737.5972582892614</v>
+        <v>43172.7035704308</v>
+      </c>
+      <c r="K63">
+        <v>17153.467302150304</v>
+      </c>
+      <c r="L63">
+        <v>4401.39100848719</v>
       </c>
     </row>
     <row r="64">
@@ -1251,31 +1367,37 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>9769556</v>
+        <v>36932659</v>
       </c>
       <c r="C66">
-        <v>8377586.311666598</v>
+        <v>10760598.81806121</v>
       </c>
       <c r="D66">
-        <v>7367839.922328609</v>
+        <v>11504480</v>
       </c>
       <c r="E66">
-        <v>7250750.850593463</v>
+        <v>9865437.744320242</v>
       </c>
       <c r="F66">
-        <v>11766743</v>
+        <v>8676361.347972812</v>
       </c>
       <c r="G66">
-        <v>9502436.945834786</v>
+        <v>8538477.367459869</v>
       </c>
       <c r="H66">
-        <v>7901738.181449405</v>
+        <v>13856505.466050254</v>
       </c>
       <c r="I66">
-        <v>2762418.212112455</v>
+        <v>11190060.79088815</v>
       </c>
       <c r="J66">
-        <v>5105648.269345568</v>
+        <v>9305079.434687378</v>
+      </c>
+      <c r="K66">
+        <v>3253021.082864902</v>
+      </c>
+      <c r="L66">
+        <v>6012406.589649904</v>
       </c>
     </row>
     <row r="67">
@@ -1287,29 +1409,35 @@
       <c r="A68" t="str">
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
+      <c r="B68">
+        <v>5210144</v>
+      </c>
       <c r="C68">
-        <v>1485713.683679712</v>
-      </c>
-      <c r="D68">
-        <v>3903834.550927951</v>
+        <v>8134334.776555963</v>
       </c>
       <c r="E68">
-        <v>6474556.020594377</v>
+        <v>1749575.033541022</v>
       </c>
       <c r="F68">
-        <v>15718225</v>
+        <v>4597151.8876114655</v>
       </c>
       <c r="G68">
-        <v>19274951.807138104</v>
+        <v>7624431.067255788</v>
       </c>
       <c r="H68">
-        <v>9101134.691110242</v>
+        <v>18509766.944778834</v>
       </c>
       <c r="I68">
-        <v>5053812.9281359855</v>
+        <v>22698165.080469962</v>
       </c>
       <c r="J68">
-        <v>9397181.92278399</v>
+        <v>10717487.633972175</v>
+      </c>
+      <c r="K68">
+        <v>5951365.340698928</v>
+      </c>
+      <c r="L68">
+        <v>11066112.574951708</v>
       </c>
     </row>
     <row r="69">
@@ -1332,19 +1460,22 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B72">
-        <v>702955</v>
-      </c>
-      <c r="C72">
-        <v>437877.65385392105</v>
+        <v>603184</v>
       </c>
       <c r="D72">
-        <v>447553.2158822797</v>
+        <v>827789</v>
       </c>
       <c r="E72">
-        <v>356239.14679035696</v>
+        <v>515644.3124565666</v>
       </c>
       <c r="F72">
-        <v>241419</v>
+        <v>527038.2451814557</v>
+      </c>
+      <c r="G72">
+        <v>419506.8834869309</v>
+      </c>
+      <c r="H72">
+        <v>284294.7868503957</v>
       </c>
     </row>
     <row r="73">
@@ -1386,17 +1517,20 @@
       <c r="A80" t="str">
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
-      <c r="G80">
-        <v>264654.4351149571</v>
-      </c>
-      <c r="H80">
-        <v>411545.11409733474</v>
+      <c r="C80">
+        <v>581290.3759808005</v>
       </c>
       <c r="I80">
-        <v>158916.73761361119</v>
+        <v>311656.8133411978</v>
       </c>
       <c r="J80">
-        <v>41888.352748836194</v>
+        <v>484635.13845895964</v>
+      </c>
+      <c r="K80">
+        <v>187140.2004267347</v>
+      </c>
+      <c r="L80">
+        <v>49327.68471514079</v>
       </c>
     </row>
     <row r="81">
@@ -1419,31 +1553,37 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>702955</v>
+        <v>5813328</v>
       </c>
       <c r="C84">
-        <v>1923591.337533633</v>
+        <v>8715625.152536763</v>
       </c>
       <c r="D84">
-        <v>4351387.766810231</v>
+        <v>827789</v>
       </c>
       <c r="E84">
-        <v>6830795.167384734</v>
+        <v>2265219.3459975887</v>
       </c>
       <c r="F84">
-        <v>15959644</v>
+        <v>5124190.132792922</v>
       </c>
       <c r="G84">
-        <v>19539606.24225307</v>
+        <v>8043937.95074272</v>
       </c>
       <c r="H84">
-        <v>9512679.805207578</v>
+        <v>18794061.73162923</v>
       </c>
       <c r="I84">
-        <v>5212729.665749596</v>
+        <v>23009821.89381117</v>
       </c>
       <c r="J84">
-        <v>9439070.275532823</v>
+        <v>11202122.772431137</v>
+      </c>
+      <c r="K84">
+        <v>6138505.541125663</v>
+      </c>
+      <c r="L84">
+        <v>11115440.259666845</v>
       </c>
     </row>
     <row r="85">
@@ -1456,31 +1596,37 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>7484113723</v>
+        <v>7700374805</v>
       </c>
       <c r="C86">
-        <v>6789461898.97821</v>
+        <v>8622393653.897884</v>
       </c>
       <c r="D86">
-        <v>6162885272.116437</v>
+        <v>8813177903</v>
       </c>
       <c r="E86">
-        <v>5443294030.469992</v>
+        <v>7995263932.82589</v>
       </c>
       <c r="F86">
-        <v>4866418725</v>
+        <v>7257407887.613591</v>
       </c>
       <c r="G86">
-        <v>4521334368.173137</v>
+        <v>6410017919.701838</v>
       </c>
       <c r="H86">
-        <v>3054603707.9551435</v>
+        <v>5730690103.714495</v>
       </c>
       <c r="I86">
-        <v>362247771.8732108</v>
+        <v>5324319090.37462</v>
       </c>
       <c r="J86">
-        <v>257632727.85009265</v>
+        <v>3597098447.3696604</v>
+      </c>
+      <c r="K86">
+        <v>426582634.7210669</v>
+      </c>
+      <c r="L86">
+        <v>303388057.48440725</v>
       </c>
     </row>
     <row r="87">
@@ -1500,18 +1646,24 @@
         <v>268000000</v>
       </c>
       <c r="F87">
+        <v>268000000</v>
+      </c>
+      <c r="G87">
+        <v>268000000</v>
+      </c>
+      <c r="H87">
         <v>200000000</v>
       </c>
-      <c r="G87">
+      <c r="I87">
         <v>200000000</v>
       </c>
-      <c r="H87">
+      <c r="J87">
         <v>40000000</v>
       </c>
-      <c r="I87">
+      <c r="K87">
         <v>30000000</v>
       </c>
-      <c r="J87">
+      <c r="L87">
         <v>30000000</v>
       </c>
     </row>
@@ -1520,31 +1672,37 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>363670888</v>
+        <v>475845980</v>
       </c>
       <c r="C88">
-        <v>363670888.2403377</v>
+        <v>475841281.1366604</v>
       </c>
       <c r="D88">
-        <v>363670887.61221135</v>
+        <v>475845980</v>
       </c>
       <c r="E88">
-        <v>363670927.5437592</v>
+        <v>475855042.6100969</v>
       </c>
       <c r="F88">
-        <v>350801815</v>
+        <v>475855041.8704158</v>
       </c>
       <c r="G88">
-        <v>350801773.7319964</v>
+        <v>475855088.89376897</v>
       </c>
       <c r="H88">
-        <v>178332249.25967482</v>
+        <v>448623698.1854623</v>
       </c>
       <c r="I88">
-        <v>159134713.4715101</v>
+        <v>448623649.5883001</v>
       </c>
       <c r="J88">
-        <v>159134713.4715101</v>
+        <v>217107850.93901774</v>
+      </c>
+      <c r="K88">
+        <v>192724860.31502756</v>
+      </c>
+      <c r="L88">
+        <v>192724860.31502756</v>
       </c>
     </row>
     <row r="89">
@@ -1556,8 +1714,8 @@
       <c r="A90" t="str">
         <v xml:space="preserve">    Pay Sahiplerinin İlave Sermaye Katkıları</v>
       </c>
-      <c r="H90">
-        <v>332469483.88781357</v>
+      <c r="J90">
+        <v>391515750.857004</v>
       </c>
     </row>
     <row r="91">
@@ -1580,25 +1738,31 @@
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
       <c r="B94">
-        <v>980129631</v>
+        <v>1154185669</v>
       </c>
       <c r="C94">
-        <v>980129630.5423672</v>
+        <v>1154178377.507981</v>
       </c>
       <c r="D94">
-        <v>980129630.8260535</v>
+        <v>1154185669</v>
       </c>
       <c r="E94">
-        <v>981874643.5443075</v>
+        <v>1154199729.1049979</v>
       </c>
       <c r="F94">
-        <v>78600868</v>
+        <v>1154199729.4390664</v>
       </c>
       <c r="G94">
-        <v>78600867.73906247</v>
+        <v>1156254654.7713196</v>
       </c>
       <c r="H94">
-        <v>78600868.02761357</v>
+        <v>92560308.07151091</v>
+      </c>
+      <c r="I94">
+        <v>92560307.76423113</v>
+      </c>
+      <c r="J94">
+        <v>92560308.10402863</v>
       </c>
     </row>
     <row r="95">
@@ -1616,70 +1780,82 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>-91723</v>
-      </c>
-      <c r="C97">
-        <v>28199.912393606595</v>
+        <v>157952</v>
       </c>
       <c r="D97">
-        <v>80819.1109677955</v>
+        <v>-108009</v>
       </c>
       <c r="E97">
-        <v>152418.06105209008</v>
+        <v>33208.190254869005</v>
       </c>
       <c r="F97">
-        <v>76564</v>
+        <v>95172.50889958082</v>
       </c>
       <c r="G97">
-        <v>306222.8595536309</v>
+        <v>179487.36503321843</v>
       </c>
       <c r="H97">
-        <v>-62904.235145555125</v>
+        <v>90161.6942345619</v>
       </c>
       <c r="I97">
-        <v>44182.09963343574</v>
+        <v>360607.7507798399</v>
+      </c>
+      <c r="J97">
+        <v>-74075.9680169861</v>
+      </c>
+      <c r="K97">
+        <v>52028.7988844729</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
+      <c r="C98">
+        <v>219686.7417436911</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
         <v xml:space="preserve">    Kardan Ayrılan Kısıtlanmış Yedekler</v>
       </c>
       <c r="B99">
-        <v>59178021</v>
+        <v>73383244</v>
       </c>
       <c r="C99">
-        <v>59178021.75904752</v>
+        <v>69686692.56283589</v>
       </c>
       <c r="D99">
-        <v>797436.9175938726</v>
+        <v>69687133</v>
       </c>
       <c r="E99">
-        <v>797436.0539752055</v>
+        <v>69687982.64517912</v>
       </c>
       <c r="F99">
-        <v>797437</v>
+        <v>939060.9625339622</v>
       </c>
       <c r="G99">
-        <v>797436.6139991134</v>
+        <v>939059.9455374338</v>
       </c>
       <c r="H99">
-        <v>797436.6407666089</v>
+        <v>939061.0595753401</v>
       </c>
       <c r="I99">
-        <v>797436.6139991134</v>
+        <v>939060.60502106</v>
+      </c>
+      <c r="J99">
+        <v>939060.6365424374</v>
+      </c>
+      <c r="K99">
+        <v>939060.60502106</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
         <v xml:space="preserve">    Diğer Özkaynak Payları</v>
       </c>
-      <c r="I100">
-        <v>107798444.77063212</v>
+      <c r="K100">
+        <v>126943346.9564161</v>
       </c>
     </row>
     <row r="101">
@@ -1697,28 +1873,34 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>4177761457</v>
+        <v>6845567130</v>
       </c>
       <c r="C103">
-        <v>4180718609.7895412</v>
+        <v>6845523883.109408</v>
       </c>
       <c r="D103">
-        <v>4236142040.1950436</v>
+        <v>4919668021</v>
       </c>
       <c r="E103">
-        <v>4236142041.4823656</v>
+        <v>4923210294.349659</v>
       </c>
       <c r="F103">
-        <v>2424466574</v>
+        <v>4988476873.7557955</v>
       </c>
       <c r="G103">
-        <v>2424466572.2868824</v>
+        <v>4988476875.271746</v>
       </c>
       <c r="H103">
-        <v>64472996.71651116</v>
+        <v>2855049552.3601675</v>
       </c>
       <c r="I103">
-        <v>67700583.32855402</v>
+        <v>2855049550.342802</v>
+      </c>
+      <c r="J103">
+        <v>75923340.16430688</v>
+      </c>
+      <c r="K103">
+        <v>79724143.11648512</v>
       </c>
     </row>
     <row r="104">
@@ -1726,31 +1908,37 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>1635465449</v>
+        <v>-1116765170</v>
       </c>
       <c r="C104">
-        <v>937736548.7345228</v>
+        <v>-191056267.16074526</v>
       </c>
       <c r="D104">
-        <v>314064457.45456666</v>
+        <v>1925899109</v>
       </c>
       <c r="E104">
-        <v>-407343436.2154676</v>
+        <v>1104277675.9257014</v>
       </c>
       <c r="F104">
-        <v>1811675467</v>
+        <v>369842009.0768797</v>
       </c>
       <c r="G104">
-        <v>1466361494.9416425</v>
+        <v>-479687246.54556656</v>
       </c>
       <c r="H104">
-        <v>2359993577.6579094</v>
+        <v>2133427322.3435447</v>
       </c>
       <c r="I104">
-        <v>-3227588.411118061</v>
+        <v>1726785914.323487</v>
       </c>
       <c r="J104">
-        <v>68498014.3785825</v>
+        <v>2779126212.6367774</v>
+      </c>
+      <c r="K104">
+        <v>-3800805.0707674897</v>
+      </c>
+      <c r="L104">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="105">
@@ -1763,31 +1951,37 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>7484113723</v>
+        <v>7700374805</v>
       </c>
       <c r="C106">
-        <v>6789461898.97821</v>
+        <v>8622393653.897884</v>
       </c>
       <c r="D106">
-        <v>6162885272.116437</v>
+        <v>8813177903</v>
       </c>
       <c r="E106">
-        <v>5443294030.469992</v>
+        <v>7995263932.82589</v>
       </c>
       <c r="F106">
-        <v>4866418725</v>
+        <v>7257407887.613591</v>
       </c>
       <c r="G106">
-        <v>4521334368.173137</v>
+        <v>6410017919.701838</v>
       </c>
       <c r="H106">
-        <v>3054603707.9551435</v>
+        <v>5730690103.714495</v>
       </c>
       <c r="I106">
-        <v>362247771.8732108</v>
+        <v>5324319090.37462</v>
       </c>
       <c r="J106">
-        <v>257632727.85009265</v>
+        <v>3597098447.3696604</v>
+      </c>
+      <c r="K106">
+        <v>426582634.7210669</v>
+      </c>
+      <c r="L106">
+        <v>303388057.48440725</v>
       </c>
     </row>
     <row r="107">
@@ -1795,31 +1989,37 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>7494586234</v>
+        <v>7743120792</v>
       </c>
       <c r="C107">
-        <v>6799763076.627411</v>
+        <v>8641869877.868483</v>
       </c>
       <c r="D107">
-        <v>6174604499.805576</v>
+        <v>8825510172</v>
       </c>
       <c r="E107">
-        <v>5457375576.48797</v>
+        <v>8007394589.916208</v>
       </c>
       <c r="F107">
-        <v>4894145112</v>
+        <v>7271208439.0943575</v>
       </c>
       <c r="G107">
-        <v>4550376411.361224</v>
+        <v>6426600335.0200405</v>
       </c>
       <c r="H107">
-        <v>3072018125.9418006</v>
+        <v>5763340670.912175</v>
       </c>
       <c r="I107">
-        <v>370222919.7510728</v>
+        <v>5358518973.05932</v>
       </c>
       <c r="J107">
-        <v>272177446.394971</v>
+        <v>3617605649.576779</v>
+      </c>
+      <c r="K107">
+        <v>435974161.3450574</v>
+      </c>
+      <c r="L107">
+        <v>320515904.33372396</v>
       </c>
     </row>
     <row r="108">
@@ -1829,14 +2029,14 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:O50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -1851,6 +2051,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1858,39 +2060,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -1904,40 +2112,46 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1982114356</v>
+        <v>354298634</v>
       </c>
       <c r="C3">
-        <v>1162234583.0220122</v>
+        <v>325792206</v>
       </c>
       <c r="D3">
-        <v>201360939.50321025</v>
+        <v>2334135997.382681</v>
       </c>
       <c r="E3">
-        <v>96481389.09963061</v>
+        <v>1368646349.5019097</v>
       </c>
       <c r="F3">
-        <v>4294197524</v>
+        <v>237119563</v>
       </c>
       <c r="G3">
-        <v>3198554747.369667</v>
+        <v>113615009</v>
       </c>
       <c r="H3">
-        <v>1411750640.1501706</v>
+        <v>5056842956.764286</v>
       </c>
       <c r="I3">
-        <v>1263456842.6116207</v>
+        <v>3766615055.703076</v>
       </c>
       <c r="J3">
-        <v>838320330.7133485</v>
+        <v>1662476223.1945393</v>
       </c>
       <c r="K3">
-        <v>602164604.4743445</v>
+        <v>1487845586.9875393</v>
       </c>
       <c r="L3">
-        <v>486799773.0998037</v>
+        <v>987205231.2887747</v>
       </c>
       <c r="M3">
-        <v>115373643.3129968</v>
+        <v>709108470.6584264</v>
+      </c>
+      <c r="N3">
+        <v>573254953.968949</v>
+      </c>
+      <c r="O3">
+        <v>135863893.61989743</v>
       </c>
     </row>
     <row r="4">
@@ -1960,37 +2174,43 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-1379706610</v>
+        <v>-192466584</v>
       </c>
       <c r="C7">
-        <v>-656544968.3134841</v>
+        <v>-191853765</v>
       </c>
       <c r="D7">
-        <v>-59887952.95526105</v>
+        <v>-1624741203.4928157</v>
+      </c>
+      <c r="E7">
+        <v>-773146735.8591568</v>
       </c>
       <c r="F7">
-        <v>-1305916715</v>
-      </c>
-      <c r="G7">
-        <v>-396196479.21534973</v>
+        <v>-70523138</v>
       </c>
       <c r="H7">
-        <v>-332530354.3602135</v>
+        <v>-1537846292.6915197</v>
       </c>
       <c r="I7">
-        <v>-262244124.16556573</v>
+        <v>-466560600.4887979</v>
       </c>
       <c r="J7">
-        <v>-476824737.4049841</v>
+        <v>-391587431.8679286</v>
       </c>
       <c r="K7">
-        <v>-291033909.7165342</v>
+        <v>-308818433.43903434</v>
       </c>
       <c r="L7">
-        <v>-441212783.4058927</v>
+        <v>-561508361.3367046</v>
       </c>
       <c r="M7">
-        <v>-99793923.30091919</v>
+        <v>-342721257.7680274</v>
+      </c>
+      <c r="N7">
+        <v>-519571757.8734404</v>
+      </c>
+      <c r="O7">
+        <v>-117517230.01834804</v>
       </c>
     </row>
     <row r="8">
@@ -1998,40 +2218,46 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>602407746</v>
+        <v>161832050</v>
       </c>
       <c r="C8">
-        <v>505689614.7085281</v>
+        <v>133938441</v>
       </c>
       <c r="D8">
-        <v>141472986.5479492</v>
+        <v>709394793.8898652</v>
       </c>
       <c r="E8">
-        <v>36593436.14436956</v>
+        <v>595499613.6427529</v>
       </c>
       <c r="F8">
-        <v>2988280809</v>
+        <v>166596425</v>
       </c>
       <c r="G8">
-        <v>2802358268.1543174</v>
+        <v>43091871</v>
       </c>
       <c r="H8">
-        <v>1079220285.789957</v>
+        <v>3518996664.0727663</v>
       </c>
       <c r="I8">
-        <v>1001212718.446055</v>
+        <v>3300054455.214278</v>
       </c>
       <c r="J8">
-        <v>361495593.30836457</v>
+        <v>1270888791.3266108</v>
       </c>
       <c r="K8">
-        <v>311130694.7578103</v>
+        <v>1179027153.548505</v>
       </c>
       <c r="L8">
-        <v>45586989.69391092</v>
+        <v>425696869.9520703</v>
       </c>
       <c r="M8">
-        <v>15579720.01207762</v>
+        <v>366387212.8903989</v>
+      </c>
+      <c r="N8">
+        <v>53683196.095508605</v>
+      </c>
+      <c r="O8">
+        <v>18346663.60154939</v>
       </c>
     </row>
     <row r="9">
@@ -2059,40 +2285,46 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>602407746</v>
+        <v>161832050</v>
       </c>
       <c r="C13">
-        <v>505689614.7085281</v>
+        <v>133938441</v>
       </c>
       <c r="D13">
-        <v>141472986.5479492</v>
+        <v>709394793.8898652</v>
       </c>
       <c r="E13">
-        <v>36593436.14436956</v>
+        <v>595499613.6427529</v>
       </c>
       <c r="F13">
-        <v>2988280809</v>
+        <v>166596425</v>
       </c>
       <c r="G13">
-        <v>2802358268.1543174</v>
+        <v>43091871</v>
       </c>
       <c r="H13">
-        <v>1079220285.789957</v>
+        <v>3518996664.0727663</v>
       </c>
       <c r="I13">
-        <v>1001212718.446055</v>
+        <v>3300054455.214278</v>
       </c>
       <c r="J13">
-        <v>361495593.30836457</v>
+        <v>1270888791.3266108</v>
       </c>
       <c r="K13">
-        <v>311130694.7578103</v>
+        <v>1179027153.548505</v>
       </c>
       <c r="L13">
-        <v>45586989.69391092</v>
+        <v>425696869.9520703</v>
       </c>
       <c r="M13">
-        <v>15579720.01207762</v>
+        <v>366387212.8903989</v>
+      </c>
+      <c r="N13">
+        <v>53683196.095508605</v>
+      </c>
+      <c r="O13">
+        <v>18346663.60154939</v>
       </c>
     </row>
     <row r="14"/>
@@ -2101,40 +2333,46 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-57425649</v>
+        <v>-43497296</v>
       </c>
       <c r="C15">
-        <v>-42292120.21496962</v>
+        <v>-23441381</v>
       </c>
       <c r="D15">
-        <v>-30460836.232065946</v>
+        <v>-67624390.13582462</v>
       </c>
       <c r="E15">
-        <v>-18512190.639879063</v>
+        <v>-49803160.90268827</v>
       </c>
       <c r="F15">
-        <v>-49839994</v>
+        <v>-35870215</v>
       </c>
       <c r="G15">
-        <v>-36726386.47868271</v>
+        <v>-21799673</v>
       </c>
       <c r="H15">
-        <v>-25508013.59786027</v>
+        <v>-58691529.95768768</v>
       </c>
       <c r="I15">
-        <v>-9576328.706641082</v>
+        <v>-43248958.100822054</v>
       </c>
       <c r="J15">
-        <v>-25123257.526009943</v>
+        <v>-30038212.770248745</v>
       </c>
       <c r="K15">
-        <v>-19710457.69682839</v>
+        <v>-11277075.658766925</v>
       </c>
       <c r="L15">
-        <v>-16147927.991845332</v>
+        <v>-29585124.382689837</v>
       </c>
       <c r="M15">
-        <v>-6186891.896297147</v>
+        <v>-23211016.40568294</v>
+      </c>
+      <c r="N15">
+        <v>-19015784.782959122</v>
+      </c>
+      <c r="O15">
+        <v>-7285678.065621339</v>
       </c>
     </row>
     <row r="16">
@@ -2152,40 +2390,46 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>1691186990</v>
+        <v>628713727</v>
       </c>
       <c r="C18">
-        <v>1154253338.8976307</v>
+        <v>396824145</v>
       </c>
       <c r="D18">
-        <v>653038828.9424425</v>
+        <v>1991540205.3948212</v>
       </c>
       <c r="E18">
-        <v>215468451.57381943</v>
+        <v>1359247643.943764</v>
       </c>
       <c r="F18">
-        <v>691357589</v>
+        <v>769008539</v>
       </c>
       <c r="G18">
-        <v>630883786.8702936</v>
+        <v>253732355</v>
       </c>
       <c r="H18">
-        <v>1785809763.4230516</v>
+        <v>814142045.1669441</v>
       </c>
       <c r="I18">
-        <v>2172152166.487119</v>
+        <v>742928152.7786158</v>
       </c>
       <c r="J18">
-        <v>2105036211.1910264</v>
+        <v>2102967894.1910625</v>
       </c>
       <c r="K18">
-        <v>2614296755.6559725</v>
+        <v>2557924343.892075</v>
       </c>
       <c r="L18">
-        <v>61903206.93186497</v>
+        <v>2478888658.195575</v>
       </c>
       <c r="M18">
-        <v>90260074.95899707</v>
+        <v>3078593395.3537035</v>
+      </c>
+      <c r="N18">
+        <v>72897158.13606425</v>
+      </c>
+      <c r="O18">
+        <v>106290179.19703425</v>
       </c>
     </row>
     <row r="19">
@@ -2193,40 +2437,46 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-280589419</v>
+        <v>-1600693816</v>
       </c>
       <c r="C19">
-        <v>-326357900.2404357</v>
+        <v>-561751632</v>
       </c>
       <c r="D19">
-        <v>-373606351.1438364</v>
+        <v>-330421835.34469694</v>
       </c>
       <c r="E19">
-        <v>-619638303.004176</v>
+        <v>-384318755.7143282</v>
       </c>
       <c r="F19">
-        <v>-527848358</v>
+        <v>-439953126</v>
       </c>
       <c r="G19">
-        <v>-804534804.6687149</v>
+        <v>-729676594</v>
       </c>
       <c r="H19">
-        <v>-428539274.75762814</v>
+        <v>-621593728.8570551</v>
       </c>
       <c r="I19">
-        <v>-244449893.08212838</v>
+        <v>-947419427.6631793</v>
       </c>
       <c r="J19">
-        <v>-35678899.18360619</v>
+        <v>-504647446.0346662</v>
       </c>
       <c r="K19">
-        <v>-3124677.210687368</v>
+        <v>-287863963.6871402</v>
       </c>
       <c r="L19">
-        <v>-62804012.38287757</v>
+        <v>-42015438.04944963</v>
       </c>
       <c r="M19">
-        <v>-1981777.8343968715</v>
+        <v>-3679616.938139312</v>
+      </c>
+      <c r="N19">
+        <v>-73957945.78612202</v>
+      </c>
+      <c r="O19">
+        <v>-2333739.7098600254</v>
       </c>
     </row>
     <row r="20">
@@ -2239,40 +2489,46 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>1955579668</v>
+        <v>-853645335</v>
       </c>
       <c r="C21">
-        <v>1291292933.1507535</v>
+        <v>-54430427</v>
       </c>
       <c r="D21">
-        <v>390444628.1144893</v>
+        <v>2302888773.804165</v>
       </c>
       <c r="E21">
-        <v>-386088605.9258661</v>
+        <v>1520625340.9695003</v>
       </c>
       <c r="F21">
-        <v>3101950046</v>
+        <v>459781623</v>
       </c>
       <c r="G21">
-        <v>2591980863.877213</v>
+        <v>-454652041</v>
       </c>
       <c r="H21">
-        <v>2410982760.8575206</v>
+        <v>3652853450.424968</v>
       </c>
       <c r="I21">
-        <v>2919338663.144405</v>
+        <v>3052314222.2288923</v>
       </c>
       <c r="J21">
-        <v>2405729647.789775</v>
+        <v>2839171026.7127585</v>
       </c>
       <c r="K21">
-        <v>2902592315.506267</v>
+        <v>3437810458.094673</v>
       </c>
       <c r="L21">
-        <v>28538256.251052983</v>
+        <v>2832984965.7155056</v>
       </c>
       <c r="M21">
-        <v>97671125.24038067</v>
+        <v>3418089974.900281</v>
+      </c>
+      <c r="N21">
+        <v>33606623.662491694</v>
+      </c>
+      <c r="O21">
+        <v>115017425.02310228</v>
       </c>
     </row>
     <row r="22"/>
@@ -2331,40 +2587,46 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>1955579668</v>
+        <v>-853645335</v>
       </c>
       <c r="C33">
-        <v>1291292933.1507535</v>
+        <v>-54430427</v>
       </c>
       <c r="D33">
-        <v>390444628.1144893</v>
+        <v>2302888773.804165</v>
       </c>
       <c r="E33">
-        <v>-386088605.9258661</v>
+        <v>1520625340.9695003</v>
       </c>
       <c r="F33">
-        <v>3101950046</v>
+        <v>459781623</v>
       </c>
       <c r="G33">
-        <v>2591980863.877213</v>
+        <v>-454652041</v>
       </c>
       <c r="H33">
-        <v>2410982760.8575206</v>
+        <v>3652853450.424968</v>
       </c>
       <c r="I33">
-        <v>2919338663.144405</v>
+        <v>3052314222.2288923</v>
       </c>
       <c r="J33">
-        <v>2405729647.789775</v>
+        <v>2839171026.7127585</v>
       </c>
       <c r="K33">
-        <v>2902592315.506267</v>
+        <v>3437810458.094673</v>
       </c>
       <c r="L33">
-        <v>28538256.251052983</v>
+        <v>2832984965.7155056</v>
       </c>
       <c r="M33">
-        <v>97671125.24038067</v>
+        <v>3418089974.900281</v>
+      </c>
+      <c r="N33">
+        <v>33606623.662491694</v>
+      </c>
+      <c r="O33">
+        <v>115017425.02310228</v>
       </c>
     </row>
     <row r="34"/>
@@ -2372,14 +2634,14 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
-      <c r="K35">
-        <v>-2862840.926687146</v>
-      </c>
-      <c r="L35">
-        <v>-1916067.3414748076</v>
-      </c>
       <c r="M35">
-        <v>-1799109.8972353297</v>
+        <v>-3371278.7768945764</v>
+      </c>
+      <c r="N35">
+        <v>-2256359.0953304623</v>
+      </c>
+      <c r="O35">
+        <v>-2118630.1192323533</v>
       </c>
     </row>
     <row r="36">
@@ -2387,40 +2649,46 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-1753642</v>
+        <v>-1402306</v>
       </c>
       <c r="C36">
-        <v>-1435851.7137252688</v>
+        <v>-761665</v>
       </c>
       <c r="D36">
-        <v>-1082279.4091795785</v>
+        <v>-2065087.1663038193</v>
       </c>
       <c r="E36">
-        <v>-601688.4087485673</v>
+        <v>-1690857.6247200957</v>
       </c>
       <c r="F36">
-        <v>-7152554</v>
+        <v>-1274476</v>
       </c>
       <c r="G36">
-        <v>-5888930.215863531</v>
+        <v>-708540</v>
       </c>
       <c r="H36">
-        <v>-3447741.7032760037</v>
+        <v>-8422840.8487565</v>
       </c>
       <c r="I36">
-        <v>-2560952.7741310336</v>
+        <v>-6934798.671586651</v>
       </c>
       <c r="J36">
-        <v>-1785811.1565513771</v>
+        <v>-4060057.3801070834</v>
       </c>
       <c r="K36">
-        <v>-133713471.09839045</v>
+        <v>-3015775.5729893334</v>
       </c>
       <c r="L36">
-        <v>-29849778.711688887</v>
+        <v>-2102969.5347376657</v>
       </c>
       <c r="M36">
-        <v>-27374000.96456281</v>
+        <v>-157460857.53376272</v>
+      </c>
+      <c r="N36">
+        <v>-35151071.275960356</v>
+      </c>
+      <c r="O36">
+        <v>-32235597.734490294</v>
       </c>
     </row>
     <row r="37">
@@ -2428,31 +2696,37 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-318360577</v>
+        <v>-261717529</v>
       </c>
       <c r="C37">
-        <v>-352120532.70250535</v>
+        <v>-54578531</v>
       </c>
       <c r="D37">
-        <v>-75297891.25074309</v>
+        <v>-374901115.40427226</v>
       </c>
       <c r="E37">
-        <v>-20653140.94392386</v>
+        <v>-414656807.4190787</v>
       </c>
       <c r="F37">
-        <v>-1283122027</v>
+        <v>-88669645</v>
       </c>
       <c r="G37">
-        <v>-1119730439.079086</v>
+        <v>-24320824</v>
       </c>
       <c r="H37">
-        <v>-902128591.611062</v>
+        <v>-1511003289.5878649</v>
       </c>
       <c r="I37">
-        <v>-898191424.2252496</v>
+        <v>-1318593509.657023</v>
       </c>
       <c r="J37">
-        <v>-43950258.97531429</v>
+        <v>-1062345779.1794126</v>
+      </c>
+      <c r="K37">
+        <v>-1057709374.5768591</v>
+      </c>
+      <c r="L37">
+        <v>-51755783.54399061</v>
       </c>
     </row>
     <row r="38">
@@ -2460,40 +2734,46 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>1635465449</v>
+        <v>-1116765170</v>
       </c>
       <c r="C38">
-        <v>937736548.7345228</v>
+        <v>-109770623</v>
       </c>
       <c r="D38">
-        <v>314064457.45456666</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E38">
-        <v>-407343435.2785385</v>
+        <v>1104277675.9257014</v>
       </c>
       <c r="F38">
-        <v>1811675465</v>
+        <v>369837502</v>
       </c>
       <c r="G38">
-        <v>1466361494.5822637</v>
+        <v>-479681405</v>
       </c>
       <c r="H38">
-        <v>1505406427.5431826</v>
+        <v>2133427319.9883466</v>
       </c>
       <c r="I38">
-        <v>2018586286.145024</v>
+        <v>1726785913.900283</v>
       </c>
       <c r="J38">
-        <v>2359993577.6579094</v>
+        <v>1772765190.1532393</v>
       </c>
       <c r="K38">
-        <v>2766016003.481189</v>
+        <v>2377085307.9448247</v>
       </c>
       <c r="L38">
-        <v>-3227589.802110714</v>
+        <v>2779126212.6367774</v>
       </c>
       <c r="M38">
-        <v>68498014.3785825</v>
+        <v>3257257838.5896225</v>
+      </c>
+      <c r="N38">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O38">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="39"/>
@@ -2517,40 +2797,46 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>1635465449</v>
+        <v>-1116765170</v>
       </c>
       <c r="C43">
-        <v>937736548.7345228</v>
+        <v>-109770623</v>
       </c>
       <c r="D43">
-        <v>314064457.45456666</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E43">
-        <v>-407343435.2785385</v>
+        <v>1104277675.9257014</v>
       </c>
       <c r="F43">
-        <v>1811675465</v>
+        <v>369837502</v>
       </c>
       <c r="G43">
-        <v>1466361494.5822637</v>
+        <v>-479681405</v>
       </c>
       <c r="H43">
-        <v>1505406427.5431826</v>
+        <v>2133427319.9883466</v>
       </c>
       <c r="I43">
-        <v>2018586286.145024</v>
+        <v>1726785913.900283</v>
       </c>
       <c r="J43">
-        <v>2359993577.6579094</v>
+        <v>1772765190.1532393</v>
       </c>
       <c r="K43">
-        <v>2766016003.481189</v>
+        <v>2377085307.9448247</v>
       </c>
       <c r="L43">
-        <v>-3227589.802110714</v>
+        <v>2779126212.6367774</v>
       </c>
       <c r="M43">
-        <v>68498014.3785825</v>
+        <v>3257257838.5896225</v>
+      </c>
+      <c r="N43">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O43">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="44">
@@ -2564,40 +2850,46 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>1635465449</v>
+        <v>-1116765170</v>
       </c>
       <c r="C46">
-        <v>937736548.7345228</v>
+        <v>-109770623</v>
       </c>
       <c r="D46">
-        <v>314064457.45456666</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E46">
-        <v>-407343435.2785385</v>
+        <v>1104277675.9257014</v>
       </c>
       <c r="F46">
-        <v>1811675465</v>
+        <v>369837502</v>
       </c>
       <c r="G46">
-        <v>1466361494.5822637</v>
+        <v>-479681405</v>
       </c>
       <c r="H46">
-        <v>1505406427.5431826</v>
+        <v>2133427319.9883466</v>
       </c>
       <c r="I46">
-        <v>2018586286.145024</v>
+        <v>1726785913.900283</v>
       </c>
       <c r="J46">
-        <v>2359993577.6579094</v>
+        <v>1772765190.1532393</v>
       </c>
       <c r="K46">
-        <v>2766016003.481189</v>
+        <v>2377085307.9448247</v>
       </c>
       <c r="L46">
-        <v>-3227589.802110714</v>
+        <v>2779126212.6367774</v>
       </c>
       <c r="M46">
-        <v>68498014.3785825</v>
+        <v>3257257838.5896225</v>
+      </c>
+      <c r="N46">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O46">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="47">
@@ -2631,46 +2923,58 @@
       <c r="J47">
         <v>0</v>
       </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>1635465449</v>
+        <v>-1116765170</v>
       </c>
       <c r="C48">
-        <v>937736548.7345228</v>
+        <v>-109770623</v>
       </c>
       <c r="D48">
-        <v>314064457.45456666</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E48">
-        <v>-407343435.2785385</v>
+        <v>1104277675.9257014</v>
       </c>
       <c r="F48">
-        <v>1811675465</v>
+        <v>369837502</v>
       </c>
       <c r="G48">
-        <v>1466361494.5822637</v>
+        <v>-479681405</v>
       </c>
       <c r="H48">
-        <v>1505406427.5431826</v>
+        <v>2133427319.9883466</v>
       </c>
       <c r="I48">
-        <v>2018586286.145024</v>
+        <v>1726785913.900283</v>
       </c>
       <c r="J48">
-        <v>2359993577.6579094</v>
+        <v>1772765190.1532393</v>
       </c>
       <c r="K48">
-        <v>2766016003.481189</v>
+        <v>2377085307.9448247</v>
       </c>
       <c r="L48">
-        <v>-3227589.802110714</v>
+        <v>2779126212.6367774</v>
       </c>
       <c r="M48">
-        <v>68498014.3785825</v>
+        <v>3257257838.5896225</v>
+      </c>
+      <c r="N48">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O48">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="49"/>
@@ -2679,52 +2983,58 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>7224205</v>
+        <v>8464364</v>
       </c>
       <c r="C50">
-        <v>5566465.266412649</v>
+        <v>4471336.673083787</v>
       </c>
       <c r="D50">
-        <v>3898699.777595086</v>
+        <v>8507216.998821812</v>
       </c>
       <c r="E50">
-        <v>2038760.2916515777</v>
+        <v>6555064.251052799</v>
       </c>
       <c r="F50">
-        <v>11145184</v>
+        <v>4591049</v>
       </c>
       <c r="G50">
-        <v>11453699.709873427</v>
+        <v>2400798.576082178</v>
       </c>
       <c r="H50">
-        <v>12761098.664698916</v>
+        <v>13124558.173501015</v>
       </c>
       <c r="I50">
-        <v>2236020.275957884</v>
+        <v>13487865.982656317</v>
       </c>
       <c r="J50">
-        <v>6224411.895535565</v>
+        <v>15027457.759569246</v>
       </c>
       <c r="K50">
-        <v>2049399.5512239924</v>
+        <v>2633135.3694059276</v>
       </c>
       <c r="L50">
-        <v>1718194.4636246322</v>
+        <v>7329861.581360006</v>
       </c>
       <c r="M50">
-        <v>135966.74983373977</v>
+        <v>2413370.979858759</v>
+      </c>
+      <c r="N50">
+        <v>2023344.18087928</v>
+      </c>
+      <c r="O50">
+        <v>160114.31644868103</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:O50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -2739,6 +3049,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2746,39 +3058,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -2792,31 +3110,37 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>819879772.9779878</v>
+        <v>28506428</v>
       </c>
       <c r="C3">
-        <v>960873643.5188019</v>
+        <v>325792206</v>
       </c>
       <c r="D3">
-        <v>104879550.40357964</v>
+        <v>965489647.8807712</v>
       </c>
       <c r="E3">
-        <v>96481389.09963061</v>
+        <v>1131526786.5019097</v>
       </c>
       <c r="F3">
-        <v>1095642776.630333</v>
+        <v>123504554</v>
       </c>
       <c r="G3">
-        <v>1786804107.2194965</v>
+        <v>113615009</v>
       </c>
       <c r="H3">
-        <v>148293797.5385499</v>
+        <v>1290227901.0612102</v>
       </c>
       <c r="I3">
-        <v>1263456842.6116207</v>
+        <v>2104138832.5085366</v>
       </c>
       <c r="J3">
-        <v>236155726.23900402</v>
+        <v>174630636.20700002</v>
+      </c>
+      <c r="K3">
+        <v>1487845586.9875393</v>
+      </c>
+      <c r="L3">
+        <v>278096760.6303483</v>
       </c>
     </row>
     <row r="4">
@@ -2839,25 +3163,31 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-723161641.6865159</v>
+        <v>-612819</v>
       </c>
       <c r="C7">
-        <v>-596657015.358223</v>
-      </c>
-      <c r="F7">
-        <v>-909720235.7846503</v>
-      </c>
-      <c r="G7">
-        <v>-63666124.855136216</v>
+        <v>-191853765</v>
+      </c>
+      <c r="D7">
+        <v>-851594467.6336589</v>
+      </c>
+      <c r="E7">
+        <v>-702623597.8591568</v>
       </c>
       <c r="H7">
-        <v>-70286230.19464779</v>
+        <v>-1071285692.2027218</v>
       </c>
       <c r="I7">
-        <v>-262244124.16556573</v>
+        <v>-74973168.62086928</v>
       </c>
       <c r="J7">
-        <v>-185790827.68844992</v>
+        <v>-82768998.42889428</v>
+      </c>
+      <c r="K7">
+        <v>-308818433.43903434</v>
+      </c>
+      <c r="L7">
+        <v>-218787103.5686772</v>
       </c>
     </row>
     <row r="8">
@@ -2865,31 +3195,37 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>96718131.2914719</v>
+        <v>27893609</v>
       </c>
       <c r="C8">
-        <v>364216628.1605789</v>
+        <v>133938441</v>
       </c>
       <c r="D8">
-        <v>104879550.40357964</v>
+        <v>113895180.24711227</v>
       </c>
       <c r="E8">
-        <v>36593436.14436956</v>
+        <v>428903188.6427529</v>
       </c>
       <c r="F8">
-        <v>185922540.84568262</v>
+        <v>123504554</v>
       </c>
       <c r="G8">
-        <v>1723137982.3643603</v>
+        <v>43091871</v>
       </c>
       <c r="H8">
-        <v>78007567.34390199</v>
+        <v>218942208.85848808</v>
       </c>
       <c r="I8">
-        <v>1001212718.446055</v>
+        <v>2029165663.8876674</v>
       </c>
       <c r="J8">
-        <v>50364898.550554276</v>
+        <v>91861637.77810574</v>
+      </c>
+      <c r="K8">
+        <v>1179027153.548505</v>
+      </c>
+      <c r="L8">
+        <v>59309657.061671376</v>
       </c>
     </row>
     <row r="9">
@@ -2917,31 +3253,37 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>96718131.2914719</v>
+        <v>27893609</v>
       </c>
       <c r="C13">
-        <v>364216628.1605789</v>
+        <v>133938441</v>
       </c>
       <c r="D13">
-        <v>104879550.40357964</v>
+        <v>113895180.24711227</v>
       </c>
       <c r="E13">
-        <v>36593436.14436956</v>
+        <v>428903188.6427529</v>
       </c>
       <c r="F13">
-        <v>185922540.84568262</v>
+        <v>123504554</v>
       </c>
       <c r="G13">
-        <v>1723137982.3643603</v>
+        <v>43091871</v>
       </c>
       <c r="H13">
-        <v>78007567.34390199</v>
+        <v>218942208.85848808</v>
       </c>
       <c r="I13">
-        <v>1001212718.446055</v>
+        <v>2029165663.8876674</v>
       </c>
       <c r="J13">
-        <v>50364898.550554276</v>
+        <v>91861637.77810574</v>
+      </c>
+      <c r="K13">
+        <v>1179027153.548505</v>
+      </c>
+      <c r="L13">
+        <v>59309657.061671376</v>
       </c>
     </row>
     <row r="14"/>
@@ -2950,31 +3292,37 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-15133528.78503038</v>
+        <v>-20055915</v>
       </c>
       <c r="C15">
-        <v>-11831283.982903674</v>
+        <v>-23441381</v>
       </c>
       <c r="D15">
-        <v>-11948645.592186883</v>
+        <v>-17821229.23313635</v>
       </c>
       <c r="E15">
-        <v>-18512190.639879063</v>
+        <v>-13932945.902688272</v>
       </c>
       <c r="F15">
-        <v>-13113607.521317288</v>
+        <v>-14070542</v>
       </c>
       <c r="G15">
-        <v>-11218372.880822442</v>
+        <v>-21799673</v>
       </c>
       <c r="H15">
-        <v>-15931684.891219188</v>
+        <v>-15442571.85686563</v>
       </c>
       <c r="I15">
-        <v>-9576328.706641082</v>
+        <v>-13210745.33057331</v>
       </c>
       <c r="J15">
-        <v>-5412799.829181552</v>
+        <v>-18761137.11148182</v>
+      </c>
+      <c r="K15">
+        <v>-11277075.658766925</v>
+      </c>
+      <c r="L15">
+        <v>-6374107.977006897</v>
       </c>
     </row>
     <row r="16">
@@ -2992,31 +3340,37 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>536933651.1023693</v>
+        <v>231889582</v>
       </c>
       <c r="C18">
-        <v>501214509.95518816</v>
+        <v>396824145</v>
       </c>
       <c r="D18">
-        <v>437570377.36862314</v>
+        <v>632292561.4510572</v>
       </c>
       <c r="E18">
-        <v>215468451.57381943</v>
+        <v>590239104.943764</v>
       </c>
       <c r="F18">
-        <v>60473802.12970638</v>
+        <v>515276184</v>
       </c>
       <c r="G18">
-        <v>-1154925976.552758</v>
+        <v>253732355</v>
       </c>
       <c r="H18">
-        <v>-386342403.0640676</v>
+        <v>71213892.38832831</v>
       </c>
       <c r="I18">
-        <v>2172152166.487119</v>
+        <v>-1360039741.4124465</v>
       </c>
       <c r="J18">
-        <v>-509260544.46494603</v>
+        <v>-454956449.7010126</v>
+      </c>
+      <c r="K18">
+        <v>2557924343.892075</v>
+      </c>
+      <c r="L18">
+        <v>-599704737.1581283</v>
       </c>
     </row>
     <row r="19">
@@ -3024,31 +3378,37 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>45768481.24043572</v>
+        <v>-1038942184</v>
       </c>
       <c r="C19">
-        <v>47248450.90340066</v>
+        <v>-561751632</v>
       </c>
       <c r="D19">
-        <v>246031951.86033964</v>
+        <v>53896920.36963129</v>
       </c>
       <c r="E19">
-        <v>-619638303.004176</v>
+        <v>55634370.28567177</v>
       </c>
       <c r="F19">
-        <v>276686446.6687149</v>
+        <v>289723468</v>
       </c>
       <c r="G19">
-        <v>-375995529.91108674</v>
+        <v>-729676594</v>
       </c>
       <c r="H19">
-        <v>-184089381.67549977</v>
+        <v>325825698.8061242</v>
       </c>
       <c r="I19">
-        <v>-244449893.08212838</v>
+        <v>-442771981.6285131</v>
       </c>
       <c r="J19">
-        <v>-32554221.972918823</v>
+        <v>-216783482.34752595</v>
+      </c>
+      <c r="K19">
+        <v>-287863963.6871402</v>
+      </c>
+      <c r="L19">
+        <v>-38335821.11131032</v>
       </c>
     </row>
     <row r="20">
@@ -3061,31 +3421,37 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>664286734.8492465</v>
+        <v>-799214908</v>
       </c>
       <c r="C21">
-        <v>900848305.0362642</v>
+        <v>-54430427</v>
       </c>
       <c r="D21">
-        <v>776533234.0403554</v>
+        <v>782263432.8346646</v>
       </c>
       <c r="E21">
-        <v>-386088605.9258661</v>
+        <v>1060843717.9695003</v>
       </c>
       <c r="F21">
-        <v>509969182.122787</v>
+        <v>914433664</v>
       </c>
       <c r="G21">
-        <v>180998103.01969242</v>
+        <v>-454652041</v>
       </c>
       <c r="H21">
-        <v>-508355902.2868843</v>
+        <v>600539228.1960754</v>
       </c>
       <c r="I21">
-        <v>2919338663.144405</v>
+        <v>213143195.5161338</v>
       </c>
       <c r="J21">
-        <v>-496862667.7164922</v>
+        <v>-598639431.3819146</v>
+      </c>
+      <c r="K21">
+        <v>3437810458.094673</v>
+      </c>
+      <c r="L21">
+        <v>-585105009.1847754</v>
       </c>
     </row>
     <row r="22"/>
@@ -3144,31 +3510,37 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>664286734.8492465</v>
+        <v>-799214908</v>
       </c>
       <c r="C33">
-        <v>900848305.0362642</v>
+        <v>-54430427</v>
       </c>
       <c r="D33">
-        <v>776533234.0403554</v>
+        <v>782263432.8346646</v>
       </c>
       <c r="E33">
-        <v>-386088605.9258661</v>
+        <v>1060843717.9695003</v>
       </c>
       <c r="F33">
-        <v>509969182.122787</v>
+        <v>914433664</v>
       </c>
       <c r="G33">
-        <v>180998103.01969242</v>
+        <v>-454652041</v>
       </c>
       <c r="H33">
-        <v>-508355902.2868843</v>
+        <v>600539228.1960754</v>
       </c>
       <c r="I33">
-        <v>2919338663.144405</v>
+        <v>213143195.5161338</v>
       </c>
       <c r="J33">
-        <v>-496862667.7164922</v>
+        <v>-598639431.3819146</v>
+      </c>
+      <c r="K33">
+        <v>3437810458.094673</v>
+      </c>
+      <c r="L33">
+        <v>-585105009.1847754</v>
       </c>
     </row>
     <row r="34"/>
@@ -3182,31 +3554,37 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-317790.28627473116</v>
+        <v>-640641</v>
       </c>
       <c r="C36">
-        <v>-353572.3045456903</v>
+        <v>-761665</v>
       </c>
       <c r="D36">
-        <v>-480591.0004310112</v>
+        <v>-374229.5415837236</v>
       </c>
       <c r="E36">
-        <v>-601688.4087485673</v>
+        <v>-416381.62472009566</v>
       </c>
       <c r="F36">
-        <v>-1263623.7841364685</v>
+        <v>-565936</v>
       </c>
       <c r="G36">
-        <v>-2441188.5125875277</v>
+        <v>-708540</v>
       </c>
       <c r="H36">
-        <v>-886788.9291449701</v>
+        <v>-1488042.1771698482</v>
       </c>
       <c r="I36">
-        <v>-2560952.7741310336</v>
+        <v>-2874741.291479568</v>
       </c>
       <c r="J36">
-        <v>131927659.94183907</v>
+        <v>-1044281.8071177499</v>
+      </c>
+      <c r="K36">
+        <v>-3015775.5729893334</v>
+      </c>
+      <c r="L36">
+        <v>155357887.99902505</v>
       </c>
     </row>
     <row r="37">
@@ -3214,28 +3592,34 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>33759955.70250535</v>
+        <v>-207138998</v>
       </c>
       <c r="C37">
-        <v>-276822641.45176226</v>
+        <v>-54578531</v>
       </c>
       <c r="D37">
-        <v>-54644750.30681923</v>
+        <v>39755692.01480645</v>
       </c>
       <c r="E37">
-        <v>-20653140.94392386</v>
+        <v>-325987162.4190787</v>
       </c>
       <c r="F37">
-        <v>-163391587.92091393</v>
+        <v>-64348821</v>
       </c>
       <c r="G37">
-        <v>-217601847.46802402</v>
+        <v>-24320824</v>
       </c>
       <c r="H37">
-        <v>-3937167.385812402</v>
+        <v>-192409779.93084192</v>
       </c>
       <c r="I37">
-        <v>-898191424.2252496</v>
+        <v>-256247730.47761035</v>
+      </c>
+      <c r="J37">
+        <v>-4636404.602553487</v>
+      </c>
+      <c r="K37">
+        <v>-1057709374.5768591</v>
       </c>
     </row>
     <row r="38">
@@ -3243,31 +3627,37 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>697728900.2654772</v>
+        <v>-1006994547</v>
       </c>
       <c r="C38">
-        <v>623672091.2799561</v>
+        <v>-109770623</v>
       </c>
       <c r="D38">
-        <v>721407892.7331052</v>
+        <v>821644895.3078876</v>
       </c>
       <c r="E38">
-        <v>-407343435.2785385</v>
+        <v>734440173.9257014</v>
       </c>
       <c r="F38">
-        <v>345313970.4177363</v>
+        <v>849518907</v>
       </c>
       <c r="G38">
-        <v>-39044932.9609189</v>
+        <v>-479681405</v>
       </c>
       <c r="H38">
-        <v>-513179858.60184145</v>
+        <v>406641406.0880635</v>
       </c>
       <c r="I38">
-        <v>2018586286.145024</v>
+        <v>-45979276.25295615</v>
       </c>
       <c r="J38">
-        <v>-406022425.8232794</v>
+        <v>-604320117.7915854</v>
+      </c>
+      <c r="K38">
+        <v>2377085307.9448247</v>
+      </c>
+      <c r="L38">
+        <v>-478131625.9528451</v>
       </c>
     </row>
     <row r="39"/>
@@ -3291,31 +3681,37 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>697728900.2654772</v>
+        <v>-1006994547</v>
       </c>
       <c r="C43">
-        <v>623672091.2799561</v>
+        <v>-109770623</v>
       </c>
       <c r="D43">
-        <v>721407892.7331052</v>
+        <v>821644895.3078876</v>
       </c>
       <c r="E43">
-        <v>-407343435.2785385</v>
+        <v>734440173.9257014</v>
       </c>
       <c r="F43">
-        <v>345313970.4177363</v>
+        <v>849518907</v>
       </c>
       <c r="G43">
-        <v>-39044932.9609189</v>
+        <v>-479681405</v>
       </c>
       <c r="H43">
-        <v>-513179858.60184145</v>
+        <v>406641406.0880635</v>
       </c>
       <c r="I43">
-        <v>2018586286.145024</v>
+        <v>-45979276.25295615</v>
       </c>
       <c r="J43">
-        <v>-406022425.8232794</v>
+        <v>-604320117.7915854</v>
+      </c>
+      <c r="K43">
+        <v>2377085307.9448247</v>
+      </c>
+      <c r="L43">
+        <v>-478131625.9528451</v>
       </c>
     </row>
     <row r="44">
@@ -3329,31 +3725,37 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>697728900.2654772</v>
+        <v>-1006994547</v>
       </c>
       <c r="C46">
-        <v>623672091.2799561</v>
+        <v>-109770623</v>
       </c>
       <c r="D46">
-        <v>721407892.7331052</v>
+        <v>821644895.3078876</v>
       </c>
       <c r="E46">
-        <v>-407343435.2785385</v>
+        <v>734440173.9257014</v>
       </c>
       <c r="F46">
-        <v>345313970.4177363</v>
+        <v>849518907</v>
       </c>
       <c r="G46">
-        <v>-39044932.9609189</v>
+        <v>-479681405</v>
       </c>
       <c r="H46">
-        <v>-513179858.60184145</v>
+        <v>406641406.0880635</v>
       </c>
       <c r="I46">
-        <v>2018586286.145024</v>
+        <v>-45979276.25295615</v>
       </c>
       <c r="J46">
-        <v>-406022425.8232794</v>
+        <v>-604320117.7915854</v>
+      </c>
+      <c r="K46">
+        <v>2377085307.9448247</v>
+      </c>
+      <c r="L46">
+        <v>-478131625.9528451</v>
       </c>
     </row>
     <row r="47">
@@ -3384,37 +3786,49 @@
       <c r="I47">
         <v>0</v>
       </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>697728900.2654772</v>
+        <v>-1006994547</v>
       </c>
       <c r="C48">
-        <v>623672091.2799561</v>
+        <v>-109770623</v>
       </c>
       <c r="D48">
-        <v>721407892.7331052</v>
+        <v>821644895.3078876</v>
       </c>
       <c r="E48">
-        <v>-407343435.2785385</v>
+        <v>734440173.9257014</v>
       </c>
       <c r="F48">
-        <v>345313970.4177363</v>
+        <v>849518907</v>
       </c>
       <c r="G48">
-        <v>-39044932.9609189</v>
+        <v>-479681405</v>
       </c>
       <c r="H48">
-        <v>-513179858.60184145</v>
+        <v>406641406.0880635</v>
       </c>
       <c r="I48">
-        <v>2018586286.145024</v>
+        <v>-45979276.25295615</v>
       </c>
       <c r="J48">
-        <v>-406022425.8232794</v>
+        <v>-604320117.7915854</v>
+      </c>
+      <c r="K48">
+        <v>2377085307.9448247</v>
+      </c>
+      <c r="L48">
+        <v>-478131625.9528451</v>
       </c>
     </row>
     <row r="49"/>
@@ -3423,43 +3837,49 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>1657739.7335873507</v>
+        <v>3993027.326916213</v>
       </c>
       <c r="C50">
-        <v>1667765.4888175633</v>
+        <v>4471336.673083787</v>
       </c>
       <c r="D50">
-        <v>1859939.4859435083</v>
+        <v>1952152.747769013</v>
       </c>
       <c r="E50">
-        <v>2038760.2916515777</v>
+        <v>1964015.2510527987</v>
       </c>
       <c r="F50">
-        <v>-308515.7098734267</v>
+        <v>2190250.423917822</v>
       </c>
       <c r="G50">
-        <v>-1307398.9548254889</v>
+        <v>2400798.576082178</v>
       </c>
       <c r="H50">
-        <v>10525078.388741031</v>
+        <v>-363307.8091553021</v>
       </c>
       <c r="I50">
-        <v>2236020.275957884</v>
+        <v>-1539591.7769129295</v>
       </c>
       <c r="J50">
-        <v>4175012.3443115726</v>
+        <v>12394322.39016332</v>
+      </c>
+      <c r="K50">
+        <v>2633135.3694059276</v>
+      </c>
+      <c r="L50">
+        <v>4916490.601501247</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:O50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -3474,6 +3894,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3481,39 +3903,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -3527,31 +3955,37 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1982114356</v>
+        <v>2451315068.382681</v>
       </c>
       <c r="C3">
-        <v>2257877359.652345</v>
+        <v>2546313194.382681</v>
       </c>
       <c r="D3">
-        <v>3083807823.3530397</v>
+        <v>2334135997.382681</v>
       </c>
       <c r="E3">
-        <v>3127222070.48801</v>
+        <v>2658874250.56312</v>
       </c>
       <c r="F3">
-        <v>4294197524</v>
+        <v>3631486296.569747</v>
       </c>
       <c r="G3">
-        <v>3434710473.608671</v>
-      </c>
-      <c r="J3">
-        <v>838320330.7133485</v>
+        <v>3682612378.7767467</v>
+      </c>
+      <c r="H3">
+        <v>5056842956.764286</v>
+      </c>
+      <c r="I3">
+        <v>4044711816.333424</v>
       </c>
       <c r="L3">
-        <v>486799773.0998037</v>
-      </c>
-      <c r="M3">
-        <v>115373643.3129968</v>
+        <v>987205231.2887747</v>
+      </c>
+      <c r="N3">
+        <v>573254953.968949</v>
+      </c>
+      <c r="O3">
+        <v>135863893.61989743</v>
       </c>
     </row>
     <row r="4">
@@ -3574,28 +4008,31 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-1379706610</v>
-      </c>
-      <c r="C7">
-        <v>-1566265204.0981345</v>
+        <v>-1746684649.4928157</v>
       </c>
       <c r="D7">
-        <v>-1033274313.5950475</v>
+        <v>-1624741203.4928157</v>
+      </c>
+      <c r="E7">
+        <v>-1844432428.0618787</v>
       </c>
       <c r="F7">
-        <v>-1305916715</v>
-      </c>
-      <c r="G7">
-        <v>-581987306.9037997</v>
-      </c>
-      <c r="J7">
-        <v>-476824737.4049841</v>
+        <v>-1216781998.8235912</v>
+      </c>
+      <c r="H7">
+        <v>-1537846292.6915197</v>
+      </c>
+      <c r="I7">
+        <v>-685347704.0574751</v>
       </c>
       <c r="L7">
-        <v>-441212783.4058927</v>
-      </c>
-      <c r="M7">
-        <v>-99793923.30091919</v>
+        <v>-561508361.3367046</v>
+      </c>
+      <c r="N7">
+        <v>-519571757.8734404</v>
+      </c>
+      <c r="O7">
+        <v>-117517230.01834804</v>
       </c>
     </row>
     <row r="8">
@@ -3603,31 +4040,37 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>602407746</v>
+        <v>704630418.8898652</v>
       </c>
       <c r="C8">
-        <v>691612155.5542107</v>
+        <v>800241363.8898652</v>
       </c>
       <c r="D8">
-        <v>2050533509.7579923</v>
+        <v>709394793.8898652</v>
       </c>
       <c r="E8">
-        <v>2023661526.6983147</v>
+        <v>814441822.501241</v>
       </c>
       <c r="F8">
-        <v>2988280809</v>
+        <v>2414704297.7461557</v>
       </c>
       <c r="G8">
-        <v>2852723166.7048717</v>
-      </c>
-      <c r="J8">
-        <v>361495593.30836457</v>
+        <v>2383061381.5242615</v>
+      </c>
+      <c r="H8">
+        <v>3518996664.0727663</v>
+      </c>
+      <c r="I8">
+        <v>3359364112.2759495</v>
       </c>
       <c r="L8">
-        <v>45586989.69391092</v>
-      </c>
-      <c r="M8">
-        <v>15579720.01207762</v>
+        <v>425696869.9520703</v>
+      </c>
+      <c r="N8">
+        <v>53683196.095508605</v>
+      </c>
+      <c r="O8">
+        <v>18346663.60154939</v>
       </c>
     </row>
     <row r="9">
@@ -3655,31 +4098,37 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>602407746</v>
+        <v>704630418.8898652</v>
       </c>
       <c r="C13">
-        <v>691612155.5542107</v>
+        <v>800241363.8898652</v>
       </c>
       <c r="D13">
-        <v>2050533509.7579923</v>
+        <v>709394793.8898652</v>
       </c>
       <c r="E13">
-        <v>2023661526.6983147</v>
+        <v>814441822.501241</v>
       </c>
       <c r="F13">
-        <v>2988280809</v>
+        <v>2414704297.7461557</v>
       </c>
       <c r="G13">
-        <v>2852723166.7048717</v>
-      </c>
-      <c r="J13">
-        <v>361495593.30836457</v>
+        <v>2383061381.5242615</v>
+      </c>
+      <c r="H13">
+        <v>3518996664.0727663</v>
+      </c>
+      <c r="I13">
+        <v>3359364112.2759495</v>
       </c>
       <c r="L13">
-        <v>45586989.69391092</v>
-      </c>
-      <c r="M13">
-        <v>15579720.01207762</v>
+        <v>425696869.9520703</v>
+      </c>
+      <c r="N13">
+        <v>53683196.095508605</v>
+      </c>
+      <c r="O13">
+        <v>18346663.60154939</v>
       </c>
     </row>
     <row r="14"/>
@@ -3688,31 +4137,37 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-57425649</v>
+        <v>-75251471.13582462</v>
       </c>
       <c r="C15">
-        <v>-55405727.73628691</v>
+        <v>-69266098.13582462</v>
       </c>
       <c r="D15">
-        <v>-54792816.63420568</v>
+        <v>-67624390.13582462</v>
       </c>
       <c r="E15">
-        <v>-58775855.933237985</v>
+        <v>-65245732.7595539</v>
       </c>
       <c r="F15">
-        <v>-49839994</v>
+        <v>-64523532.187438935</v>
       </c>
       <c r="G15">
-        <v>-42139186.30786426</v>
-      </c>
-      <c r="J15">
-        <v>-25123257.526009943</v>
+        <v>-69214127.29892075</v>
+      </c>
+      <c r="H15">
+        <v>-58691529.95768768</v>
+      </c>
+      <c r="I15">
+        <v>-49623066.07782895</v>
       </c>
       <c r="L15">
-        <v>-16147927.991845332</v>
-      </c>
-      <c r="M15">
-        <v>-6186891.896297147</v>
+        <v>-29585124.382689837</v>
+      </c>
+      <c r="N15">
+        <v>-19015784.782959122</v>
+      </c>
+      <c r="O15">
+        <v>-7285678.065621339</v>
       </c>
     </row>
     <row r="16">
@@ -3730,31 +4185,37 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>1691186990</v>
+        <v>1851245393.3948212</v>
       </c>
       <c r="C18">
-        <v>1214727141.027337</v>
+        <v>2134631995.3948212</v>
       </c>
       <c r="D18">
-        <v>-441413345.48060906</v>
+        <v>1991540205.3948212</v>
       </c>
       <c r="E18">
-        <v>-1265326125.9132998</v>
+        <v>1430461536.3320923</v>
       </c>
       <c r="F18">
-        <v>691357589</v>
+        <v>-519817310.0241184</v>
       </c>
       <c r="G18">
-        <v>121623242.40534759</v>
-      </c>
-      <c r="J18">
-        <v>2105036211.1910264</v>
+        <v>-1490049943.725131</v>
+      </c>
+      <c r="H18">
+        <v>814142045.1669441</v>
+      </c>
+      <c r="I18">
+        <v>143223415.62048757</v>
       </c>
       <c r="L18">
-        <v>61903206.93186497</v>
-      </c>
-      <c r="M18">
-        <v>90260074.95899707</v>
+        <v>2478888658.195575</v>
+      </c>
+      <c r="N18">
+        <v>72897158.13606425</v>
+      </c>
+      <c r="O18">
+        <v>106290179.19703425</v>
       </c>
     </row>
     <row r="19">
@@ -3762,31 +4223,37 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-280589419</v>
+        <v>-1491162525.344697</v>
       </c>
       <c r="C19">
-        <v>-49671453.57172084</v>
+        <v>-162496873.34469694</v>
       </c>
       <c r="D19">
-        <v>-472915434.38620824</v>
+        <v>-330421835.34469694</v>
       </c>
       <c r="E19">
-        <v>-903036767.9220476</v>
+        <v>-58493056.90820402</v>
       </c>
       <c r="F19">
-        <v>-527848358</v>
+        <v>-556899408.8223889</v>
       </c>
       <c r="G19">
-        <v>-837089026.6416337</v>
-      </c>
-      <c r="J19">
-        <v>-35678899.18360619</v>
+        <v>-1063406359.1699148</v>
+      </c>
+      <c r="H19">
+        <v>-621593728.8570551</v>
+      </c>
+      <c r="I19">
+        <v>-985755248.7744896</v>
       </c>
       <c r="L19">
-        <v>-62804012.38287757</v>
-      </c>
-      <c r="M19">
-        <v>-1981777.8343968715</v>
+        <v>-42015438.04944963</v>
+      </c>
+      <c r="N19">
+        <v>-73957945.78612202</v>
+      </c>
+      <c r="O19">
+        <v>-2333739.7098600254</v>
       </c>
     </row>
     <row r="20">
@@ -3799,31 +4266,37 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>1955579668</v>
+        <v>989461815.8041649</v>
       </c>
       <c r="C21">
-        <v>1801262115.2735405</v>
+        <v>2703110387.804165</v>
       </c>
       <c r="D21">
-        <v>1081411913.2569687</v>
+        <v>2302888773.804165</v>
       </c>
       <c r="E21">
-        <v>-203477223.07027102</v>
+        <v>2121164569.1655757</v>
       </c>
       <c r="F21">
-        <v>3101950046</v>
+        <v>1273464046.7122092</v>
       </c>
       <c r="G21">
-        <v>2095118196.1607208</v>
-      </c>
-      <c r="J21">
-        <v>2405729647.789775</v>
+        <v>-239609048.6697054</v>
+      </c>
+      <c r="H21">
+        <v>3652853450.424968</v>
+      </c>
+      <c r="I21">
+        <v>2467209213.044117</v>
       </c>
       <c r="L21">
-        <v>28538256.251052983</v>
-      </c>
-      <c r="M21">
-        <v>97671125.24038067</v>
+        <v>2832984965.7155056</v>
+      </c>
+      <c r="N21">
+        <v>33606623.662491694</v>
+      </c>
+      <c r="O21">
+        <v>115017425.02310228</v>
       </c>
     </row>
     <row r="22"/>
@@ -3882,31 +4355,37 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>1955579668</v>
+        <v>989461815.8041649</v>
       </c>
       <c r="C33">
-        <v>1801262115.2735405</v>
+        <v>2703110387.804165</v>
       </c>
       <c r="D33">
-        <v>1081411913.2569687</v>
+        <v>2302888773.804165</v>
       </c>
       <c r="E33">
-        <v>-203477223.07027102</v>
+        <v>2121164569.1655757</v>
       </c>
       <c r="F33">
-        <v>3101950046</v>
+        <v>1273464046.7122092</v>
       </c>
       <c r="G33">
-        <v>2095118196.1607208</v>
-      </c>
-      <c r="J33">
-        <v>2405729647.789775</v>
+        <v>-239609048.6697054</v>
+      </c>
+      <c r="H33">
+        <v>3652853450.424968</v>
+      </c>
+      <c r="I33">
+        <v>2467209213.044117</v>
       </c>
       <c r="L33">
-        <v>28538256.251052983</v>
-      </c>
-      <c r="M33">
-        <v>97671125.24038067</v>
+        <v>2832984965.7155056</v>
+      </c>
+      <c r="N33">
+        <v>33606623.662491694</v>
+      </c>
+      <c r="O33">
+        <v>115017425.02310228</v>
       </c>
     </row>
     <row r="34"/>
@@ -3914,11 +4393,11 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
-      <c r="L35">
-        <v>-1916067.3414748076</v>
-      </c>
-      <c r="M35">
-        <v>-1799109.8972353297</v>
+      <c r="N35">
+        <v>-2256359.0953304623</v>
+      </c>
+      <c r="O35">
+        <v>-2118630.1192323533</v>
       </c>
     </row>
     <row r="36">
@@ -3926,31 +4405,37 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-1753642</v>
+        <v>-2192917.166303819</v>
       </c>
       <c r="C36">
-        <v>-2699475.4978617374</v>
+        <v>-2118212.166303819</v>
       </c>
       <c r="D36">
-        <v>-4787091.705903575</v>
+        <v>-2065087.1663038193</v>
       </c>
       <c r="E36">
-        <v>-5193289.634617534</v>
+        <v>-3178899.801889944</v>
       </c>
       <c r="F36">
-        <v>-7152554</v>
+        <v>-5637259.468649416</v>
       </c>
       <c r="G36">
-        <v>126038729.72597554</v>
-      </c>
-      <c r="J36">
-        <v>-1785811.1565513771</v>
+        <v>-6115605.275767166</v>
+      </c>
+      <c r="H36">
+        <v>-8422840.8487565</v>
+      </c>
+      <c r="I36">
+        <v>148423089.32743838</v>
       </c>
       <c r="L36">
-        <v>-29849778.711688887</v>
-      </c>
-      <c r="M36">
-        <v>-27374000.96456281</v>
+        <v>-2102969.5347376657</v>
+      </c>
+      <c r="N36">
+        <v>-35151071.275960356</v>
+      </c>
+      <c r="O36">
+        <v>-32235597.734490294</v>
       </c>
     </row>
     <row r="37">
@@ -3958,22 +4443,28 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>-318360577</v>
+        <v>-547948999.4042723</v>
       </c>
       <c r="C37">
-        <v>-515512120.6234193</v>
+        <v>-405158822.40427226</v>
       </c>
       <c r="D37">
-        <v>-456291326.63968104</v>
+        <v>-374901115.40427226</v>
       </c>
       <c r="E37">
-        <v>-405583743.7186742</v>
+        <v>-607066587.3499206</v>
       </c>
       <c r="F37">
-        <v>-1283122027</v>
-      </c>
-      <c r="J37">
-        <v>-43950258.97531429</v>
+        <v>-537327155.4084523</v>
+      </c>
+      <c r="G37">
+        <v>-477614739.01100576</v>
+      </c>
+      <c r="H37">
+        <v>-1511003289.5878649</v>
+      </c>
+      <c r="L37">
+        <v>-51755783.54399061</v>
       </c>
     </row>
     <row r="38">
@@ -3981,31 +4472,37 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>1635465449</v>
+        <v>439319899.23358893</v>
       </c>
       <c r="C38">
-        <v>1283050519.152259</v>
+        <v>2295833353.233589</v>
       </c>
       <c r="D38">
-        <v>620333494.9113841</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E38">
-        <v>-614254256.4235625</v>
+        <v>1510919082.0137649</v>
       </c>
       <c r="F38">
-        <v>1811675465</v>
+        <v>730499631.8351073</v>
       </c>
       <c r="G38">
-        <v>1060339068.7589843</v>
-      </c>
-      <c r="J38">
-        <v>2359993577.6579094</v>
+        <v>-723339392.9564781</v>
+      </c>
+      <c r="H38">
+        <v>2133427319.9883466</v>
+      </c>
+      <c r="I38">
+        <v>1248654287.947438</v>
       </c>
       <c r="L38">
-        <v>-3227589.802110714</v>
-      </c>
-      <c r="M38">
-        <v>68498014.3785825</v>
+        <v>2779126212.6367774</v>
+      </c>
+      <c r="N38">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O38">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="39"/>
@@ -4029,31 +4526,37 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>1635465449</v>
+        <v>439319899.23358893</v>
       </c>
       <c r="C43">
-        <v>1283050519.152259</v>
+        <v>2295833353.233589</v>
       </c>
       <c r="D43">
-        <v>620333494.9113841</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E43">
-        <v>-614254256.4235625</v>
+        <v>1510919082.0137649</v>
       </c>
       <c r="F43">
-        <v>1811675465</v>
+        <v>730499631.8351073</v>
       </c>
       <c r="G43">
-        <v>1060339068.7589843</v>
-      </c>
-      <c r="J43">
-        <v>2359993577.6579094</v>
+        <v>-723339392.9564781</v>
+      </c>
+      <c r="H43">
+        <v>2133427319.9883466</v>
+      </c>
+      <c r="I43">
+        <v>1248654287.947438</v>
       </c>
       <c r="L43">
-        <v>-3227589.802110714</v>
-      </c>
-      <c r="M43">
-        <v>68498014.3785825</v>
+        <v>2779126212.6367774</v>
+      </c>
+      <c r="N43">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O43">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="44">
@@ -4067,31 +4570,37 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>1635465449</v>
+        <v>439319899.23358893</v>
       </c>
       <c r="C46">
-        <v>1283050519.152259</v>
+        <v>2295833353.233589</v>
       </c>
       <c r="D46">
-        <v>620333494.9113841</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E46">
-        <v>-614254256.4235625</v>
+        <v>1510919082.0137649</v>
       </c>
       <c r="F46">
-        <v>1811675465</v>
+        <v>730499631.8351073</v>
       </c>
       <c r="G46">
-        <v>1060339068.7589843</v>
-      </c>
-      <c r="J46">
-        <v>2359993577.6579094</v>
+        <v>-723339392.9564781</v>
+      </c>
+      <c r="H46">
+        <v>2133427319.9883466</v>
+      </c>
+      <c r="I46">
+        <v>1248654287.947438</v>
       </c>
       <c r="L46">
-        <v>-3227589.802110714</v>
-      </c>
-      <c r="M46">
-        <v>68498014.3785825</v>
+        <v>2779126212.6367774</v>
+      </c>
+      <c r="N46">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O46">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="47">
@@ -4113,7 +4622,13 @@
       <c r="F47">
         <v>0</v>
       </c>
-      <c r="J47">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="L47">
         <v>0</v>
       </c>
     </row>
@@ -4122,31 +4637,37 @@
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>1635465449</v>
+        <v>439319899.23358893</v>
       </c>
       <c r="C48">
-        <v>1283050519.152259</v>
+        <v>2295833353.233589</v>
       </c>
       <c r="D48">
-        <v>620333494.9113841</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E48">
-        <v>-614254256.4235625</v>
+        <v>1510919082.0137649</v>
       </c>
       <c r="F48">
-        <v>1811675465</v>
+        <v>730499631.8351073</v>
       </c>
       <c r="G48">
-        <v>1060339068.7589843</v>
-      </c>
-      <c r="J48">
-        <v>2359993577.6579094</v>
+        <v>-723339392.9564781</v>
+      </c>
+      <c r="H48">
+        <v>2133427319.9883466</v>
+      </c>
+      <c r="I48">
+        <v>1248654287.947438</v>
       </c>
       <c r="L48">
-        <v>-3227589.802110714</v>
-      </c>
-      <c r="M48">
-        <v>68498014.3785825</v>
+        <v>2779126212.6367774</v>
+      </c>
+      <c r="N48">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O48">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="49"/>
@@ -4155,43 +4676,49 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>7224205</v>
+        <v>12380531.998821812</v>
       </c>
       <c r="C50">
-        <v>5257949.556539223</v>
+        <v>10577755.095823422</v>
       </c>
       <c r="D50">
-        <v>2282785.1128961705</v>
+        <v>8507216.998821812</v>
       </c>
       <c r="E50">
-        <v>10947924.015693694</v>
+        <v>6191756.441897497</v>
       </c>
       <c r="F50">
-        <v>11145184</v>
+        <v>2688149.4139317684</v>
       </c>
       <c r="G50">
-        <v>15628712.054185</v>
-      </c>
-      <c r="J50">
-        <v>6224411.895535565</v>
+        <v>12892221.380177265</v>
+      </c>
+      <c r="H50">
+        <v>13124558.173501015</v>
+      </c>
+      <c r="I50">
+        <v>18404356.584157564</v>
       </c>
       <c r="L50">
-        <v>1718194.4636246322</v>
-      </c>
-      <c r="M50">
-        <v>135966.74983373977</v>
+        <v>7329861.581360006</v>
+      </c>
+      <c r="N50">
+        <v>2023344.18087928</v>
+      </c>
+      <c r="O50">
+        <v>160114.31644868103</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:O129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -4206,6 +4733,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4213,39 +4742,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -4259,40 +4794,46 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>479436490</v>
+        <v>-614058418</v>
       </c>
       <c r="C3">
-        <v>-142947507.72792688</v>
+        <v>50009385.060205765</v>
       </c>
       <c r="D3">
-        <v>-517559363.65596694</v>
+        <v>564583958.7308866</v>
       </c>
       <c r="E3">
-        <v>-797565263.7900287</v>
+        <v>-168334850.3651588</v>
       </c>
       <c r="F3">
-        <v>2011037307</v>
+        <v>-639053250</v>
       </c>
       <c r="G3">
-        <v>1310713514.5754213</v>
+        <v>-951736128.4213861</v>
       </c>
       <c r="H3">
-        <v>1335116463.685269</v>
+        <v>2368195637.2189384</v>
       </c>
       <c r="I3">
-        <v>1745544382.0476024</v>
+        <v>1543494999.35031</v>
       </c>
       <c r="J3">
-        <v>2495631447.921071</v>
+        <v>1572231889.2210543</v>
       </c>
       <c r="K3">
-        <v>3065343092.0717688</v>
+        <v>2055551419.0354898</v>
       </c>
       <c r="L3">
-        <v>1447512.8573447445</v>
+        <v>2938853240.8131313</v>
       </c>
       <c r="M3">
-        <v>43327016.1109233</v>
+        <v>3609745135.9829865</v>
+      </c>
+      <c r="N3">
+        <v>1704589.7764551733</v>
+      </c>
+      <c r="O3">
+        <v>51021853.33432166</v>
       </c>
     </row>
     <row r="4">
@@ -4300,40 +4841,46 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>1635465449</v>
+        <v>-1116765170</v>
       </c>
       <c r="C4">
-        <v>937736548.7345228</v>
+        <v>-191056267.16074526</v>
       </c>
       <c r="D4">
-        <v>314064457.45456666</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E4">
-        <v>-407343436.2154676</v>
+        <v>1104277675.9257014</v>
       </c>
       <c r="F4">
-        <v>1811675465</v>
+        <v>369837502</v>
       </c>
       <c r="G4">
-        <v>1466361494.5822637</v>
+        <v>-479678374.28729373</v>
       </c>
       <c r="H4">
-        <v>1505406427.5431826</v>
+        <v>2133427319.9883466</v>
       </c>
       <c r="I4">
-        <v>2018586285.4694808</v>
+        <v>1726785913.900283</v>
       </c>
       <c r="J4">
-        <v>2359993577.6579094</v>
+        <v>1772765190.1532393</v>
       </c>
       <c r="K4">
-        <v>2766016003.481189</v>
+        <v>2377085307.1493053</v>
       </c>
       <c r="L4">
-        <v>-3227589.802110714</v>
+        <v>2779126212.6367774</v>
       </c>
       <c r="M4">
-        <v>68498014.3785825</v>
+        <v>3257257838.5896225</v>
+      </c>
+      <c r="N4">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O4">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="5">
@@ -4341,40 +4888,46 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>41595964</v>
+        <v>61352382</v>
       </c>
       <c r="C5">
-        <v>86814622.56216107</v>
+        <v>3131859.558090278</v>
       </c>
       <c r="D5">
-        <v>57150784.453254454</v>
+        <v>48983368.00010245</v>
       </c>
       <c r="E5">
-        <v>18042519.93817964</v>
+        <v>102232817.70203315</v>
       </c>
       <c r="F5">
-        <v>201794946</v>
+        <v>37716634</v>
       </c>
       <c r="G5">
-        <v>-153754627.68279472</v>
+        <v>8705063.999945693</v>
       </c>
       <c r="H5">
-        <v>-173158531.84897053</v>
+        <v>237633538.20766848</v>
       </c>
       <c r="I5">
-        <v>-239973204.1654996</v>
+        <v>-181061304.63775462</v>
       </c>
       <c r="J5">
-        <v>113492080.73998995</v>
+        <v>-203911323.89468327</v>
       </c>
       <c r="K5">
-        <v>5142890.706633786</v>
+        <v>-282592219.0384237</v>
       </c>
       <c r="L5">
-        <v>7964572.160722205</v>
+        <v>133648167.30739233</v>
       </c>
       <c r="M5">
-        <v>2217317.4022943918</v>
+        <v>6056263.24869763</v>
+      </c>
+      <c r="N5">
+        <v>9379072.669454828</v>
+      </c>
+      <c r="O5">
+        <v>2611110.883008203</v>
       </c>
     </row>
     <row r="6">
@@ -4382,40 +4935,46 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>7224205</v>
+        <v>8464364</v>
       </c>
       <c r="C6">
-        <v>5566465.266412649</v>
+        <v>4471336.673083787</v>
       </c>
       <c r="D6">
-        <v>3898699.777595086</v>
+        <v>8507216.998821812</v>
       </c>
       <c r="E6">
-        <v>2038760.2916515777</v>
+        <v>6555064.251052799</v>
       </c>
       <c r="F6">
-        <v>11145184</v>
+        <v>4591049</v>
       </c>
       <c r="G6">
-        <v>11453699.709873427</v>
+        <v>2400798.576082178</v>
       </c>
       <c r="H6">
-        <v>12761098.664698916</v>
+        <v>13124558.173501015</v>
       </c>
       <c r="I6">
-        <v>2236020.275957884</v>
+        <v>13487865.982656317</v>
       </c>
       <c r="J6">
-        <v>6224411.895535565</v>
+        <v>15027457.759569246</v>
       </c>
       <c r="K6">
-        <v>2049399.5512239924</v>
+        <v>2633135.3694059276</v>
       </c>
       <c r="L6">
-        <v>1718194.4636246322</v>
+        <v>7329861.581360006</v>
       </c>
       <c r="M6">
-        <v>135966.74983373977</v>
+        <v>2413370.979858759</v>
+      </c>
+      <c r="N6">
+        <v>2023344.18087928</v>
+      </c>
+      <c r="O6">
+        <v>160114.31644868103</v>
       </c>
     </row>
     <row r="7">
@@ -4428,37 +4987,43 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1319640</v>
+        <v>1600060</v>
       </c>
       <c r="C8">
-        <v>234167.90665593575</v>
+        <v>557641.4843899513</v>
       </c>
       <c r="D8">
-        <v>271061.5093657113</v>
+        <v>1554006.8201726305</v>
       </c>
       <c r="E8">
-        <v>229489.89366058705</v>
+        <v>275755.9061629475</v>
+      </c>
+      <c r="F8">
+        <v>319198</v>
       </c>
       <c r="G8">
-        <v>76522.64278247337</v>
-      </c>
-      <c r="H8">
-        <v>83347.79331262351</v>
+        <v>270242.01286613534</v>
       </c>
       <c r="I8">
-        <v>215654.13979808372</v>
+        <v>90112.99201418381</v>
       </c>
       <c r="J8">
-        <v>246482.03454210205</v>
+        <v>98150.28284543945</v>
       </c>
       <c r="K8">
-        <v>2979177.98820344</v>
+        <v>253954.11176130158</v>
       </c>
       <c r="L8">
-        <v>6075076.951895368</v>
+        <v>290257.0115550093</v>
       </c>
       <c r="M8">
-        <v>1929924.4102828011</v>
+        <v>3508277.1908826055</v>
+      </c>
+      <c r="N8">
+        <v>7154004.892485039</v>
+      </c>
+      <c r="O8">
+        <v>2272677.166497768</v>
       </c>
     </row>
     <row r="9">
@@ -4481,28 +5046,34 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>1727000</v>
+        <v>1378762</v>
       </c>
       <c r="C12">
-        <v>1419256.102327736</v>
+        <v>529273.3017942763</v>
       </c>
       <c r="D12">
-        <v>1064153.4461603297</v>
+        <v>2033713.57221525</v>
       </c>
       <c r="E12">
-        <v>588187.2236410588</v>
+        <v>1671314.6483805631</v>
       </c>
       <c r="F12">
-        <v>5080779</v>
+        <v>1253131</v>
       </c>
       <c r="G12">
-        <v>5399343.504576475</v>
+        <v>692635.679942277</v>
       </c>
       <c r="H12">
-        <v>5880939.925773505</v>
+        <v>5983120.561509106</v>
+      </c>
+      <c r="I12">
+        <v>6358261.821835224</v>
       </c>
       <c r="J12">
-        <v>1175231.168005811</v>
+        <v>6925389.3135078885</v>
+      </c>
+      <c r="L12">
+        <v>1383951.1157288933</v>
       </c>
     </row>
     <row r="13">
@@ -4585,40 +5156,46 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-1197624923</v>
+        <v>441466654</v>
       </c>
       <c r="C28">
-        <v>-1167449733.29353</v>
+        <v>238053951.5905673</v>
       </c>
       <c r="D28">
-        <v>-888740103.7462047</v>
+        <v>-1410321980.5028048</v>
       </c>
       <c r="E28">
-        <v>-408242275.0018513</v>
+        <v>-1374787705.5461063</v>
       </c>
       <c r="F28">
-        <v>-2395028</v>
+        <v>-1046566757</v>
       </c>
       <c r="G28">
-        <v>-1853618.0286586562</v>
+        <v>-480736825.648955</v>
       </c>
       <c r="H28">
-        <v>2911284.0997359655</v>
+        <v>-2820382.715365111</v>
       </c>
       <c r="I28">
-        <v>-33006163.64686312</v>
+        <v>-2182818.8434197945</v>
       </c>
       <c r="J28">
-        <v>22145789.52317148</v>
+        <v>3428325.411816728</v>
       </c>
       <c r="K28">
-        <v>294184196.4929538</v>
+        <v>-38868027.200569265</v>
       </c>
       <c r="L28">
-        <v>-3289469.5012667454</v>
+        <v>26078860.868961282</v>
       </c>
       <c r="M28">
-        <v>-27388315.66995361</v>
+        <v>346431032.50663465</v>
+      </c>
+      <c r="N28">
+        <v>-3873676.1842005267</v>
+      </c>
+      <c r="O28">
+        <v>-32252454.718066167</v>
       </c>
     </row>
     <row r="29">
@@ -4626,31 +5203,37 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>-1182143764</v>
+        <v>419513147</v>
       </c>
       <c r="C29">
-        <v>-1151174659.4044464</v>
+        <v>242521708.6653719</v>
       </c>
       <c r="D29">
-        <v>-875334631.9762816</v>
+        <v>-1392091382.256179</v>
       </c>
       <c r="E29">
-        <v>-404345565.86308545</v>
+        <v>-1355622193.874401</v>
       </c>
       <c r="F29">
-        <v>86124</v>
+        <v>-1030780677</v>
       </c>
       <c r="G29">
-        <v>86124.36701492626</v>
+        <v>-476148149.8512934</v>
       </c>
       <c r="H29">
-        <v>86124.40768859928</v>
+        <v>101419.54122377893</v>
       </c>
       <c r="I29">
-        <v>-30722189.17604554</v>
+        <v>101419.97342021017</v>
       </c>
       <c r="J29">
-        <v>22175080.60840364</v>
+        <v>101420.02131748917</v>
+      </c>
+      <c r="K29">
+        <v>-36178421.01649581</v>
+      </c>
+      <c r="L29">
+        <v>26113354.023322344</v>
       </c>
     </row>
     <row r="30">
@@ -4663,24 +5246,30 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-25197</v>
-      </c>
-      <c r="I31">
-        <v>-597177.966223191</v>
+        <v>29672</v>
+      </c>
+      <c r="C31">
+        <v>29671.605825579176</v>
+      </c>
+      <c r="D31">
+        <v>-29671.963450554522</v>
+      </c>
+      <c r="K31">
+        <v>-703236.2101540265</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="K32">
-        <v>-31840308.67185768</v>
-      </c>
-      <c r="L32">
-        <v>-642624.6957041519</v>
-      </c>
       <c r="M32">
-        <v>-5878837.099419674</v>
+        <v>-37495117.480880074</v>
+      </c>
+      <c r="N32">
+        <v>-756754.2359549676</v>
+      </c>
+      <c r="O32">
+        <v>-6922913.027175637</v>
       </c>
     </row>
     <row r="33">
@@ -4688,40 +5277,46 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1396549</v>
+        <v>-21513468</v>
       </c>
       <c r="C33">
-        <v>-1707843.171604469</v>
+        <v>-23205415.2135494</v>
       </c>
       <c r="D33">
-        <v>-2353966.5496476884</v>
+        <v>-1644574.7860820123</v>
       </c>
       <c r="E33">
-        <v>-2544650.110871191</v>
+        <v>-2011154.5091529514</v>
       </c>
       <c r="F33">
-        <v>-641844</v>
+        <v>-2771995</v>
       </c>
       <c r="G33">
-        <v>-693290.197171554</v>
+        <v>-2996521.8495192337</v>
       </c>
       <c r="H33">
-        <v>-771069.738733849</v>
+        <v>-755834.8894296034</v>
       </c>
       <c r="I33">
-        <v>-850900.0517956198</v>
+        <v>-816417.8827281854</v>
       </c>
       <c r="J33">
-        <v>94033.04866737442</v>
+        <v>-908010.9975607967</v>
       </c>
       <c r="K33">
-        <v>-13098.977812173418</v>
+        <v>-1002019.0989782347</v>
       </c>
       <c r="L33">
-        <v>-268894.18072093616</v>
+        <v>110733.2294798011</v>
       </c>
       <c r="M33">
-        <v>-1040.4625043544354</v>
+        <v>-15425.343925167055</v>
+      </c>
+      <c r="N33">
+        <v>-316649.53377062426</v>
+      </c>
+      <c r="O33">
+        <v>-1225.2476644393075</v>
       </c>
     </row>
     <row r="34">
@@ -4754,40 +5349,46 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>4121</v>
+        <v>-167250</v>
       </c>
       <c r="C39">
-        <v>-102732.50103943312</v>
+        <v>-991136.7217345879</v>
       </c>
       <c r="D39">
-        <v>-74954.00391421921</v>
+        <v>4852.885715749303</v>
       </c>
       <c r="E39">
-        <v>-67174.88025816582</v>
+        <v>-120977.69639346405</v>
       </c>
       <c r="F39">
-        <v>-35073</v>
+        <v>-88265</v>
       </c>
       <c r="G39">
-        <v>-65684.30913632017</v>
+        <v>-79103.23623258871</v>
       </c>
       <c r="H39">
-        <v>-852880.5778262356</v>
+        <v>-41301.931741925575</v>
       </c>
       <c r="I39">
-        <v>-1215239.1916715459</v>
+        <v>-77349.78052815082</v>
       </c>
       <c r="J39">
-        <v>-45338.484684584</v>
+        <v>-1004351.364565142</v>
       </c>
       <c r="K39">
-        <v>-52021.73422506888</v>
+        <v>-1431064.526688079</v>
       </c>
       <c r="L39">
-        <v>1181045.958803085</v>
+        <v>-53390.55683075376</v>
       </c>
       <c r="M39">
-        <v>-326161.3482400165</v>
+        <v>-61260.745190328416</v>
+      </c>
+      <c r="N39">
+        <v>1390798.607891029</v>
+      </c>
+      <c r="O39">
+        <v>-384087.2962638947</v>
       </c>
     </row>
     <row r="40">
@@ -4795,40 +5396,46 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>25110</v>
+        <v>377069</v>
       </c>
       <c r="C40">
-        <v>133497.464858251</v>
+        <v>-20044.68022934048</v>
       </c>
       <c r="D40">
-        <v>73621.22901375084</v>
+        <v>29569.512332556416</v>
       </c>
       <c r="E40">
-        <v>-16260.638006017552</v>
+        <v>157206.48878897133</v>
       </c>
       <c r="F40">
-        <v>-488335</v>
+        <v>86695</v>
       </c>
       <c r="G40">
-        <v>-53964.173840735086</v>
+        <v>-19147.907925022115</v>
       </c>
       <c r="H40">
-        <v>4157270.4487942867</v>
+        <v>-575062.8357195914</v>
       </c>
       <c r="I40">
-        <v>-312870.70634821255</v>
+        <v>-63548.160250889465</v>
       </c>
       <c r="J40">
-        <v>473020.0050176008</v>
+        <v>4895597.762062724</v>
       </c>
       <c r="K40">
-        <v>52228.992130348044</v>
+        <v>-368436.2488992078</v>
       </c>
       <c r="L40">
-        <v>16949.24547534598</v>
+        <v>557027.9120634744</v>
       </c>
       <c r="M40">
-        <v>13933.573403901575</v>
+        <v>61504.81190423411</v>
+      </c>
+      <c r="N40">
+        <v>19959.41549624727</v>
+      </c>
+      <c r="O40">
+        <v>16408.162907337624</v>
       </c>
     </row>
     <row r="41">
@@ -4841,40 +5448,46 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>83899</v>
+        <v>9330</v>
       </c>
       <c r="C42">
-        <v>-17684.036392038535</v>
+        <v>256230.7482116719</v>
       </c>
       <c r="D42">
-        <v>-59415.060188303956</v>
+        <v>98799.38332095384</v>
       </c>
       <c r="E42">
-        <v>38974.15554254423</v>
+        <v>-20824.704587166863</v>
       </c>
       <c r="F42">
-        <v>-126198</v>
+        <v>-69966</v>
       </c>
       <c r="G42">
-        <v>-42149.0752905958</v>
+        <v>45894.83748842695</v>
       </c>
       <c r="H42">
-        <v>26902.30817612071</v>
+        <v>-148610.64585200933</v>
       </c>
       <c r="I42">
-        <v>-281047.52106312336</v>
+        <v>-49634.711334572734</v>
       </c>
       <c r="J42">
-        <v>261576.5378443315</v>
+        <v>31680.13275141516</v>
       </c>
       <c r="K42">
-        <v>-63809.005965576216</v>
+        <v>-330961.29590244667</v>
       </c>
       <c r="L42">
-        <v>38860.161743515855</v>
+        <v>308032.2844163827</v>
       </c>
       <c r="M42">
-        <v>45951.44228789942</v>
+        <v>-75141.42528185072</v>
+      </c>
+      <c r="N42">
+        <v>45761.68984149857</v>
+      </c>
+      <c r="O42">
+        <v>54112.375126674495</v>
       </c>
     </row>
     <row r="43">
@@ -4887,34 +5500,40 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>136141</v>
+        <v>24734913</v>
       </c>
       <c r="C44">
-        <v>-255992.75836743665</v>
+        <v>169338.0064860839</v>
       </c>
       <c r="D44">
-        <v>-317155.5517356976</v>
+        <v>160319.5132802295</v>
       </c>
       <c r="E44">
-        <v>415603.0221173795</v>
+        <v>-301456.83096738555</v>
       </c>
       <c r="F44">
-        <v>724253</v>
+        <v>-373478</v>
+      </c>
+      <c r="G44">
+        <v>489404.38894262357</v>
       </c>
       <c r="H44">
+        <v>852879.6501549575</v>
+      </c>
+      <c r="J44">
         <v>0</v>
       </c>
-      <c r="I44">
-        <v>238455.6619577688</v>
-      </c>
       <c r="K44">
-        <v>374175499.0968427</v>
-      </c>
-      <c r="L44">
-        <v>-436134.6183693828</v>
+        <v>280805.16276496014</v>
       </c>
       <c r="M44">
-        <v>118600.20656252968</v>
+        <v>440628715.0571303</v>
+      </c>
+      <c r="N44">
+        <v>-513591.7155128734</v>
+      </c>
+      <c r="O44">
+        <v>139663.49146134846</v>
       </c>
     </row>
     <row r="45">
@@ -4937,40 +5556,46 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-14308684</v>
+        <v>18483241</v>
       </c>
       <c r="C48">
-        <v>-14324318.88653845</v>
+        <v>19293599.180185378</v>
       </c>
       <c r="D48">
-        <v>-10673601.83345093</v>
+        <v>-16849892.79174244</v>
       </c>
       <c r="E48">
-        <v>-1723200.6872903758</v>
+        <v>-16868304.41939345</v>
       </c>
       <c r="F48">
-        <v>-1913955</v>
+        <v>-12569071</v>
       </c>
       <c r="G48">
-        <v>-1084654.6402343772</v>
+        <v>-2029202.0304158027</v>
       </c>
       <c r="H48">
-        <v>264937.25163704396</v>
+        <v>-2253871.6040007174</v>
       </c>
       <c r="I48">
-        <v>734805.3043263423</v>
+        <v>-1277288.2819982062</v>
       </c>
       <c r="J48">
-        <v>-812582.1920768844</v>
+        <v>311989.8578110384</v>
       </c>
       <c r="K48">
-        <v>-679867.132992368</v>
+        <v>865306.0337835782</v>
       </c>
       <c r="L48">
-        <v>283697.1245328879</v>
+        <v>-956896.0234899706</v>
       </c>
       <c r="M48">
-        <v>-119761.68542768472</v>
+        <v>-800610.8950026921</v>
+      </c>
+      <c r="N48">
+        <v>334081.46645105624</v>
+      </c>
+      <c r="O48">
+        <v>-141031.24787820253</v>
       </c>
     </row>
     <row r="49">
@@ -4978,31 +5603,37 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>479436490</v>
+        <v>-613946134</v>
       </c>
       <c r="C49">
-        <v>-142898561.99684605</v>
+        <v>50129543.987912305</v>
       </c>
       <c r="D49">
-        <v>-517524861.8383836</v>
+        <v>564583958.7308866</v>
       </c>
       <c r="E49">
-        <v>-797543191.2791394</v>
+        <v>-168277211.91837186</v>
       </c>
       <c r="F49">
-        <v>2011075383</v>
+        <v>-639012621</v>
       </c>
       <c r="G49">
-        <v>1310753248.8708103</v>
+        <v>-951710135.936303</v>
       </c>
       <c r="H49">
-        <v>1335159179.7939482</v>
+        <v>2368240475.4806495</v>
       </c>
       <c r="I49">
-        <v>1745606917.6571178</v>
+        <v>1543541790.4191084</v>
       </c>
       <c r="J49">
-        <v>2495631447.921071</v>
+        <v>1572282191.6703727</v>
+      </c>
+      <c r="K49">
+        <v>2055625060.9103122</v>
+      </c>
+      <c r="L49">
+        <v>2938853240.8131313</v>
       </c>
     </row>
     <row r="50">
@@ -5069,35 +5700,41 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
+      <c r="B62">
+        <v>-112284</v>
+      </c>
       <c r="C62">
-        <v>-48945.73108083226</v>
-      </c>
-      <c r="D62">
-        <v>-34501.81758333679</v>
+        <v>-120158.92770654352</v>
       </c>
       <c r="E62">
-        <v>-22072.510889467252</v>
+        <v>-57638.44678696373</v>
       </c>
       <c r="F62">
-        <v>-38076</v>
+        <v>-40629</v>
       </c>
       <c r="G62">
-        <v>-39734.295389074665</v>
+        <v>-25992.48508304153</v>
       </c>
       <c r="H62">
-        <v>-42716.10867864771</v>
+        <v>-44838.261711446365</v>
       </c>
       <c r="I62">
-        <v>-62535.60951571907</v>
+        <v>-46791.0687985935</v>
+      </c>
+      <c r="J62">
+        <v>-50302.449317885046</v>
       </c>
       <c r="K62">
-        <v>-63809.005965576216</v>
-      </c>
-      <c r="L62">
-        <v>38860.161743515855</v>
+        <v>-73641.87482273945</v>
       </c>
       <c r="M62">
-        <v>45951.44228789942</v>
+        <v>-75141.42528185072</v>
+      </c>
+      <c r="N62">
+        <v>45761.68984149857</v>
+      </c>
+      <c r="O62">
+        <v>54112.375126674495</v>
       </c>
     </row>
     <row r="63">
@@ -5121,40 +5758,46 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-1483714794</v>
+        <v>676879067</v>
       </c>
       <c r="C67">
-        <v>-783567118.4251786</v>
+        <v>-25421940.992836345</v>
       </c>
       <c r="D67">
-        <v>-345978836.1672866</v>
+        <v>-1747221142.938248</v>
       </c>
       <c r="E67">
-        <v>306552100.46611327</v>
+        <v>-922727900.1058946</v>
       </c>
       <c r="F67">
-        <v>-1805521617</v>
+        <v>-407419387</v>
       </c>
       <c r="G67">
-        <v>-1451281198.2714732</v>
+        <v>360988786.5986956</v>
       </c>
       <c r="H67">
-        <v>-1497771157.5865326</v>
+        <v>-2126180554.383859</v>
       </c>
       <c r="I67">
-        <v>-1965501844.4532387</v>
+        <v>-1709027371.1786373</v>
       </c>
       <c r="J67">
-        <v>-2768566947.6739235</v>
+        <v>-1763773903.4489157</v>
       </c>
       <c r="K67">
-        <v>-3227220055.3986883</v>
+        <v>-2314573119.443346</v>
       </c>
       <c r="L67">
-        <v>-19328581.528869905</v>
+        <v>-3260261828.066593</v>
       </c>
       <c r="M67">
-        <v>-56066903.60578507</v>
+        <v>-3800371295.4195504</v>
+      </c>
+      <c r="N67">
+        <v>-22761319.390232608</v>
+      </c>
+      <c r="O67">
+        <v>-66024332.8402833</v>
       </c>
     </row>
     <row r="68">
@@ -5181,31 +5824,43 @@
       <c r="A72" t="str">
         <v xml:space="preserve">    İştiraklerin ve/veya İş Ortaklıklarının Pay Satışı veya Sermaye Azaltımı Sebebiyle Oluşan Nakit Girişleri</v>
       </c>
+      <c r="B72">
+        <v>682075627</v>
+      </c>
+      <c r="F72">
+        <v>-401134500</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
         <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
-      <c r="B73">
-        <v>-1474955288</v>
-      </c>
       <c r="C73">
-        <v>-775118744.8338838</v>
-      </c>
-      <c r="F73">
-        <v>-1799392782</v>
+        <v>-23162187.150025606</v>
+      </c>
+      <c r="D73">
+        <v>-1736905956.9289248</v>
+      </c>
+      <c r="E73">
+        <v>-912779103.3278047</v>
       </c>
       <c r="G73">
-        <v>-1445191666.0070057</v>
-      </c>
-      <c r="K73">
-        <v>-3226982796.5638714</v>
-      </c>
-      <c r="L73">
-        <v>-18727209.50227223</v>
+        <v>361155174.24570316</v>
+      </c>
+      <c r="H73">
+        <v>-2118963244.0645957</v>
+      </c>
+      <c r="I73">
+        <v>-1701856343.7236922</v>
       </c>
       <c r="M73">
-        <v>-55246596.2905873</v>
+        <v>-3800091899.639299</v>
+      </c>
+      <c r="N73">
+        <v>-22053144.258534703</v>
+      </c>
+      <c r="O73">
+        <v>-65058339.71908748</v>
       </c>
     </row>
     <row r="74">
@@ -5227,46 +5882,52 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="C77">
+        <v>-2259753.84281074</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-8759506</v>
-      </c>
-      <c r="C78">
-        <v>-8448373.591294896</v>
+        <v>-5196560</v>
       </c>
       <c r="D78">
-        <v>-5337099.332654358</v>
+        <v>-10315186.009323055</v>
       </c>
       <c r="E78">
-        <v>-141296.17948752662</v>
+        <v>-9948796.778089939</v>
       </c>
       <c r="F78">
-        <v>-6128835</v>
+        <v>-6284887</v>
       </c>
       <c r="G78">
-        <v>-6089532.264467424</v>
+        <v>-166387.64700755678</v>
       </c>
       <c r="H78">
-        <v>-6128834.935396226</v>
+        <v>-7217310.319263377</v>
       </c>
       <c r="I78">
-        <v>-2487483.9726198013</v>
+        <v>-7171027.454945029</v>
       </c>
       <c r="J78">
-        <v>-832455.5742861931</v>
+        <v>-7217310.243186034</v>
       </c>
       <c r="K78">
-        <v>-237258.83481648038</v>
+        <v>-2929258.781577763</v>
       </c>
       <c r="L78">
-        <v>-601372.0265976819</v>
+        <v>-980298.8996479857</v>
       </c>
       <c r="M78">
-        <v>-820308.7061904233</v>
+        <v>-279395.7802514489</v>
+      </c>
+      <c r="N78">
+        <v>-708175.1316979132</v>
+      </c>
+      <c r="O78">
+        <v>-965994.7592274441</v>
       </c>
     </row>
     <row r="79">
@@ -5303,25 +5964,19 @@
       <c r="A85" t="str">
         <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="E85">
-        <v>306693396.64560074</v>
-      </c>
-      <c r="I85">
-        <v>-1963014360.480619</v>
-      </c>
-      <c r="J85">
-        <v>-2767734492.0996375</v>
+      <c r="K85">
+        <v>-2311643860.6617684</v>
+      </c>
+      <c r="L85">
+        <v>-3259281529.1669455</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
         <v xml:space="preserve">    Diğer Uzun Vadeli Varlık Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="D86">
-        <v>-340641736.8346322</v>
-      </c>
-      <c r="H86">
-        <v>-1491642322.6511364</v>
+      <c r="J86">
+        <v>-1756556593.2057297</v>
       </c>
     </row>
     <row r="87">
@@ -5395,40 +6050,46 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>964078795</v>
+        <v>-3412566</v>
       </c>
       <c r="C101">
-        <v>968322147.8365328</v>
+        <v>-1374836.4831072171</v>
       </c>
       <c r="D101">
-        <v>974707803.8068814</v>
+        <v>1135298280.2990294</v>
       </c>
       <c r="E101">
-        <v>982478452.7778108</v>
+        <v>1140295248.599756</v>
       </c>
       <c r="F101">
-        <v>-162060449</v>
+        <v>1125966861</v>
       </c>
       <c r="G101">
-        <v>178813054.39118025</v>
+        <v>1156944300.4592087</v>
       </c>
       <c r="H101">
-        <v>186356132.24340314</v>
+        <v>-190842231.99223936</v>
       </c>
       <c r="I101">
-        <v>261050475.52867475</v>
+        <v>210570084.31071627</v>
       </c>
       <c r="J101">
-        <v>246190221.87641504</v>
+        <v>219452805.67976198</v>
       </c>
       <c r="K101">
-        <v>45543828.5828847</v>
+        <v>307412793.9293057</v>
       </c>
       <c r="L101">
-        <v>101481342.05209883</v>
+        <v>289913373.23494446</v>
       </c>
       <c r="M101">
-        <v>45494097.81355893</v>
+        <v>53632369.61184566</v>
+      </c>
+      <c r="N101">
+        <v>119504332.74925976</v>
+      </c>
+      <c r="O101">
+        <v>53573806.70476139</v>
       </c>
     </row>
     <row r="102">
@@ -5445,20 +6106,20 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B104">
-        <v>901528763</v>
-      </c>
-      <c r="C104">
-        <v>901528762.8502741</v>
-      </c>
       <c r="D104">
-        <v>901528763.2534791</v>
+        <v>1061639421.5723947</v>
       </c>
       <c r="E104">
-        <v>903273776.9892476</v>
-      </c>
-      <c r="J104">
-        <v>237760272.93971056</v>
+        <v>1061639421.3960775</v>
+      </c>
+      <c r="F104">
+        <v>1061626484</v>
+      </c>
+      <c r="G104">
+        <v>1063674674.0155197</v>
+      </c>
+      <c r="L104">
+        <v>279986273.312734</v>
       </c>
     </row>
     <row r="105">
@@ -5470,11 +6131,11 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="K106">
-        <v>-13596.953181904553</v>
-      </c>
-      <c r="L106">
-        <v>47181.079793045574</v>
+      <c r="M106">
+        <v>-16011.759251195495</v>
+      </c>
+      <c r="N106">
+        <v>55560.39509373912</v>
       </c>
     </row>
     <row r="107">
@@ -5491,8 +6152,8 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="J109">
-        <v>52116.08944515841</v>
+      <c r="L109">
+        <v>61371.85780857128</v>
       </c>
     </row>
     <row r="110">
@@ -5500,37 +6161,43 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>11861</v>
+        <v>46330</v>
       </c>
       <c r="C110">
-        <v>106612.42829693337</v>
+        <v>86394.0592747379</v>
       </c>
       <c r="D110">
-        <v>-44016.3495116804</v>
+        <v>13967.50242040827</v>
       </c>
       <c r="E110">
-        <v>-40555.86025606746</v>
+        <v>125546.6950748689</v>
       </c>
       <c r="F110">
-        <v>-4745</v>
+        <v>-51831</v>
       </c>
       <c r="G110">
-        <v>-36336.48927008036</v>
+        <v>-47757.940808019164</v>
       </c>
       <c r="H110">
-        <v>-55912.59954919433</v>
+        <v>-5587.707527597778</v>
       </c>
       <c r="I110">
-        <v>-4409.745171236238</v>
+        <v>-42789.81551546974</v>
+      </c>
+      <c r="J110">
+        <v>-65842.62452868141</v>
       </c>
       <c r="K110">
-        <v>31647499.007263992</v>
-      </c>
-      <c r="L110">
-        <v>-6364283.798326314</v>
+        <v>-5192.911757240186</v>
       </c>
       <c r="M110">
-        <v>3764318.227151091</v>
+        <v>37268065.0015874</v>
+      </c>
+      <c r="N110">
+        <v>-7494574.602250057</v>
+      </c>
+      <c r="O110">
+        <v>4432857.596233019</v>
       </c>
     </row>
     <row r="111">
@@ -5548,31 +6215,37 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-5461829</v>
+        <v>-3458896</v>
       </c>
       <c r="C113">
-        <v>-4274780.295727633</v>
+        <v>-1461230.542381955</v>
       </c>
       <c r="D113">
-        <v>-3063721.9117736267</v>
+        <v>-6431844.6823502295</v>
       </c>
       <c r="E113">
-        <v>-1623881.5237977586</v>
+        <v>-5033977.247052466</v>
       </c>
       <c r="F113">
-        <v>10413780</v>
+        <v>-3607792</v>
       </c>
       <c r="G113">
-        <v>11881031.224710591</v>
+        <v>-1912246.0138152556</v>
       </c>
       <c r="H113">
-        <v>6913741.749569788</v>
+        <v>12263257.512486236</v>
       </c>
       <c r="I113">
-        <v>-1729449.0155346245</v>
+        <v>13991091.17174702</v>
       </c>
       <c r="J113">
-        <v>8377832.8472593175</v>
+        <v>8141615.767742493</v>
+      </c>
+      <c r="K113">
+        <v>-2036597.530600503</v>
+      </c>
+      <c r="L113">
+        <v>9865728.064401856</v>
       </c>
     </row>
     <row r="114">
@@ -5624,38 +6297,38 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B123">
+      <c r="D123">
+        <v>80076735.90656456</v>
+      </c>
+      <c r="E123">
+        <v>83564257.755656</v>
+      </c>
+      <c r="F123">
         <v>68000000</v>
       </c>
-      <c r="C123">
-        <v>70961552.85368939</v>
-      </c>
-      <c r="D123">
-        <v>76286778.81468758</v>
-      </c>
-      <c r="E123">
-        <v>80869113.1726171</v>
-      </c>
-      <c r="F123">
-        <v>-172469484</v>
-      </c>
       <c r="G123">
-        <v>166968359.65573975</v>
+        <v>95229630.39831229</v>
       </c>
       <c r="H123">
-        <v>179498303.09338254</v>
+        <v>-203099901.797198</v>
       </c>
       <c r="I123">
-        <v>262784334.28938058</v>
+        <v>196621782.95448473</v>
+      </c>
+      <c r="J123">
+        <v>211377032.53654817</v>
       </c>
       <c r="K123">
-        <v>13909926.52880261</v>
-      </c>
-      <c r="L123">
-        <v>107798444.77063212</v>
+        <v>309454584.3716634</v>
       </c>
       <c r="M123">
-        <v>41729779.58640783</v>
+        <v>16380316.369509455</v>
+      </c>
+      <c r="N123">
+        <v>126943346.9564161</v>
+      </c>
+      <c r="O123">
+        <v>49140949.108528376</v>
       </c>
     </row>
     <row r="124">
@@ -5668,31 +6341,37 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-40199509</v>
+        <v>59408083</v>
       </c>
       <c r="C125">
-        <v>41807521.683427274</v>
+        <v>23212607.5842622</v>
       </c>
       <c r="D125">
-        <v>111169603.98362796</v>
+        <v>-47338903.90833184</v>
       </c>
       <c r="E125">
-        <v>491465289.45389533</v>
+        <v>49232498.12870261</v>
       </c>
       <c r="F125">
-        <v>43455241</v>
+        <v>79494224</v>
       </c>
       <c r="G125">
-        <v>38245370.69512832</v>
+        <v>566196958.6365181</v>
       </c>
       <c r="H125">
-        <v>23701438.34213979</v>
+        <v>51172850.84283995</v>
       </c>
       <c r="I125">
-        <v>41093013.12303829</v>
+        <v>45037712.48238903</v>
       </c>
       <c r="J125">
-        <v>-26745277.876437392</v>
+        <v>27910791.451900758</v>
+      </c>
+      <c r="K125">
+        <v>48391093.52144896</v>
+      </c>
+      <c r="L125">
+        <v>-31495214.018517073</v>
       </c>
     </row>
     <row r="126">
@@ -5705,40 +6384,46 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-40199509</v>
+        <v>59408083</v>
       </c>
       <c r="C127">
-        <v>41807521.683427274</v>
+        <v>23212607.5842622</v>
       </c>
       <c r="D127">
-        <v>111169603.98362796</v>
+        <v>-47338903.90833184</v>
       </c>
       <c r="E127">
-        <v>491465289.45389533</v>
+        <v>49232498.12870261</v>
       </c>
       <c r="F127">
-        <v>43455241</v>
+        <v>79494224</v>
       </c>
       <c r="G127">
-        <v>38245370.69512832</v>
+        <v>566196958.6365181</v>
       </c>
       <c r="H127">
-        <v>23701438.34213979</v>
+        <v>51172850.84283995</v>
       </c>
       <c r="I127">
-        <v>41093013.12303829</v>
+        <v>45037712.48238903</v>
       </c>
       <c r="J127">
-        <v>-26745277.876437392</v>
+        <v>27910791.451900758</v>
       </c>
       <c r="K127">
-        <v>-116333134.74403445</v>
+        <v>48391093.52144896</v>
       </c>
       <c r="L127">
-        <v>83600273.3805737</v>
+        <v>-31495214.018517073</v>
       </c>
       <c r="M127">
-        <v>32754210.318697162</v>
+        <v>-136993789.8247182</v>
+      </c>
+      <c r="N127">
+        <v>98447603.13548237</v>
+      </c>
+      <c r="O127">
+        <v>38571327.198799774</v>
       </c>
     </row>
     <row r="128">
@@ -5746,31 +6431,37 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>76446285</v>
+        <v>10884798</v>
       </c>
       <c r="C128">
-        <v>76446285.02094606</v>
+        <v>10884729.013096305</v>
       </c>
       <c r="D128">
-        <v>76446284.37240955</v>
+        <v>90023073.16151424</v>
       </c>
       <c r="E128">
-        <v>76446285.04382186</v>
+        <v>90023073.18618031</v>
       </c>
       <c r="F128">
-        <v>61300127</v>
+        <v>90021975</v>
       </c>
       <c r="G128">
-        <v>61300126.9971371</v>
+        <v>90021408.00377838</v>
       </c>
       <c r="H128">
-        <v>61300126.68637398</v>
+        <v>72186971.77673335</v>
       </c>
       <c r="I128">
-        <v>61298196.726766594</v>
+        <v>72186971.773362</v>
       </c>
       <c r="J128">
-        <v>116354487.84161593</v>
+        <v>72186971.40740766</v>
+      </c>
+      <c r="K128">
+        <v>72184698.68879308</v>
+      </c>
+      <c r="L128">
+        <v>137018935.2123038</v>
       </c>
     </row>
     <row r="129">
@@ -5778,43 +6469,49 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>9243325</v>
+        <v>20502322</v>
       </c>
       <c r="C129">
-        <v>42989111.89196429</v>
+        <v>33711111.319711186</v>
       </c>
       <c r="D129">
-        <v>131757633.0399691</v>
+        <v>10884930.807699205</v>
       </c>
       <c r="E129">
-        <v>544211238.5259334</v>
+        <v>50623937.644567326</v>
       </c>
       <c r="F129">
-        <v>76446285</v>
+        <v>155155774</v>
       </c>
       <c r="G129">
-        <v>84222011.96563634</v>
+        <v>640850787.3822523</v>
       </c>
       <c r="H129">
-        <v>78252790.07253757</v>
+        <v>90023073.16151424</v>
       </c>
       <c r="I129">
-        <v>85313050.51845372</v>
+        <v>99179761.90723209</v>
       </c>
       <c r="J129">
-        <v>61300127.410258695</v>
+        <v>92150411.83221218</v>
+      </c>
+      <c r="K129">
+        <v>100464567.87867087</v>
+      </c>
+      <c r="L129">
+        <v>72186972.2598536</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:O129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -5829,6 +6526,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5836,39 +6535,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -5882,31 +6587,37 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>622383997.7279269</v>
+        <v>-664067803.0602058</v>
       </c>
       <c r="C3">
-        <v>374611855.92804</v>
+        <v>50009385.060205765</v>
       </c>
       <c r="D3">
-        <v>280005900.13406175</v>
+        <v>732918809.0960454</v>
       </c>
       <c r="E3">
-        <v>-797565263.7900287</v>
+        <v>470718399.6348412</v>
       </c>
       <c r="F3">
-        <v>700323792.4245787</v>
+        <v>312682878.4213861</v>
       </c>
       <c r="G3">
-        <v>-24402949.109847784</v>
+        <v>-951736128.4213861</v>
       </c>
       <c r="H3">
-        <v>-410427918.3623333</v>
+        <v>824700637.8686283</v>
       </c>
       <c r="I3">
-        <v>1745544382.0476024</v>
+        <v>-28736889.87074423</v>
       </c>
       <c r="J3">
-        <v>-569711644.1506977</v>
+        <v>-483319529.8144355</v>
+      </c>
+      <c r="K3">
+        <v>2055551419.0354898</v>
+      </c>
+      <c r="L3">
+        <v>-670891895.1698551</v>
       </c>
     </row>
     <row r="4">
@@ -5914,31 +6625,37 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>697728900.2654772</v>
+        <v>-925708902.8392547</v>
       </c>
       <c r="C4">
-        <v>623672091.2799561</v>
+        <v>-191056267.16074526</v>
       </c>
       <c r="D4">
-        <v>721407893.6700342</v>
+        <v>821644895.3078876</v>
       </c>
       <c r="E4">
-        <v>-407343436.2154676</v>
+        <v>734440173.9257014</v>
       </c>
       <c r="F4">
-        <v>345313970.4177363</v>
+        <v>849515876.2872937</v>
       </c>
       <c r="G4">
-        <v>-39044932.9609189</v>
+        <v>-479678374.28729373</v>
       </c>
       <c r="H4">
-        <v>-513179857.92629814</v>
+        <v>406641406.0880635</v>
       </c>
       <c r="I4">
-        <v>2018586285.4694808</v>
+        <v>-45979276.25295615</v>
       </c>
       <c r="J4">
-        <v>-406022425.8232794</v>
+        <v>-604320116.9960661</v>
+      </c>
+      <c r="K4">
+        <v>2377085307.1493053</v>
+      </c>
+      <c r="L4">
+        <v>-478131625.9528451</v>
       </c>
     </row>
     <row r="5">
@@ -5946,31 +6663,37 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>-45218658.56216107</v>
+        <v>58220522.44190972</v>
       </c>
       <c r="C5">
-        <v>29663838.10890662</v>
+        <v>3131859.558090278</v>
       </c>
       <c r="D5">
-        <v>39108264.51507482</v>
+        <v>-53249449.701930694</v>
       </c>
       <c r="E5">
-        <v>18042519.93817964</v>
+        <v>64516183.70203315</v>
       </c>
       <c r="F5">
-        <v>355549573.6827947</v>
+        <v>29011570.000054307</v>
       </c>
       <c r="G5">
-        <v>19403904.166175812</v>
+        <v>8705063.999945693</v>
       </c>
       <c r="H5">
-        <v>66814672.316529065</v>
+        <v>418694842.8454231</v>
       </c>
       <c r="I5">
-        <v>-239973204.1654996</v>
+        <v>22850019.256928653</v>
       </c>
       <c r="J5">
-        <v>108349190.03335616</v>
+        <v>78680895.14374045</v>
+      </c>
+      <c r="K5">
+        <v>-282592219.0384237</v>
+      </c>
+      <c r="L5">
+        <v>127591904.0586947</v>
       </c>
     </row>
     <row r="6">
@@ -5978,31 +6701,37 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>1657739.7335873507</v>
+        <v>3993027.326916213</v>
       </c>
       <c r="C6">
-        <v>1667765.4888175633</v>
+        <v>4471336.673083787</v>
       </c>
       <c r="D6">
-        <v>1859939.4859435083</v>
+        <v>1952152.747769013</v>
       </c>
       <c r="E6">
-        <v>2038760.2916515777</v>
+        <v>1964015.2510527987</v>
       </c>
       <c r="F6">
-        <v>-308515.7098734267</v>
+        <v>2190250.423917822</v>
       </c>
       <c r="G6">
-        <v>-1307398.9548254889</v>
+        <v>2400798.576082178</v>
       </c>
       <c r="H6">
-        <v>10525078.388741031</v>
+        <v>-363307.8091553021</v>
       </c>
       <c r="I6">
-        <v>2236020.275957884</v>
+        <v>-1539591.7769129295</v>
       </c>
       <c r="J6">
-        <v>4175012.3443115726</v>
+        <v>12394322.39016332</v>
+      </c>
+      <c r="K6">
+        <v>2633135.3694059276</v>
+      </c>
+      <c r="L6">
+        <v>4916490.601501247</v>
       </c>
     </row>
     <row r="7">
@@ -6015,28 +6744,34 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1085472.0933440642</v>
+        <v>1042418.5156100487</v>
       </c>
       <c r="C8">
-        <v>-36893.60270977556</v>
+        <v>557641.4843899513</v>
       </c>
       <c r="D8">
-        <v>41571.61570512425</v>
+        <v>1278250.914009683</v>
       </c>
       <c r="E8">
-        <v>229489.89366058705</v>
+        <v>-43442.093837052525</v>
+      </c>
+      <c r="F8">
+        <v>48955.98713386466</v>
       </c>
       <c r="G8">
-        <v>-6825.150530150146</v>
-      </c>
-      <c r="H8">
-        <v>-132306.3464854602</v>
+        <v>270242.01286613534</v>
       </c>
       <c r="I8">
-        <v>215654.13979808372</v>
+        <v>-8037.290831255639</v>
       </c>
       <c r="J8">
-        <v>-2732695.953661338</v>
+        <v>-155803.82891586213</v>
+      </c>
+      <c r="K8">
+        <v>253954.11176130158</v>
+      </c>
+      <c r="L8">
+        <v>-3218020.179327596</v>
       </c>
     </row>
     <row r="9">
@@ -6059,22 +6794,28 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>307743.8976722639</v>
+        <v>849488.6982057237</v>
       </c>
       <c r="C12">
-        <v>355102.65616740636</v>
+        <v>529273.3017942763</v>
       </c>
       <c r="D12">
-        <v>475966.22251927096</v>
+        <v>362398.92383468687</v>
       </c>
       <c r="E12">
-        <v>588187.2236410588</v>
+        <v>418183.6483805631</v>
       </c>
       <c r="F12">
-        <v>-318564.50457647536</v>
+        <v>560495.320057723</v>
       </c>
       <c r="G12">
-        <v>-481596.42119702976</v>
+        <v>692635.679942277</v>
+      </c>
+      <c r="H12">
+        <v>-375141.2603261173</v>
+      </c>
+      <c r="I12">
+        <v>-567127.4916726649</v>
       </c>
     </row>
     <row r="13">
@@ -6157,31 +6898,37 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-30175189.706470013</v>
+        <v>203412702.4094327</v>
       </c>
       <c r="C28">
-        <v>-278709629.54732525</v>
+        <v>238053951.5905673</v>
       </c>
       <c r="D28">
-        <v>-480497828.7443534</v>
+        <v>-35534274.95669842</v>
       </c>
       <c r="E28">
-        <v>-408242275.0018513</v>
+        <v>-328220948.54610634</v>
       </c>
       <c r="F28">
-        <v>-541409.9713413438</v>
+        <v>-565829931.351045</v>
       </c>
       <c r="G28">
-        <v>-4764902.128394621</v>
+        <v>-480736825.648955</v>
       </c>
       <c r="H28">
-        <v>35917447.746599086</v>
+        <v>-637563.8719453164</v>
       </c>
       <c r="I28">
-        <v>-33006163.64686312</v>
+        <v>-5611144.255236522</v>
       </c>
       <c r="J28">
-        <v>-272038406.9697823</v>
+        <v>42296352.612385996</v>
+      </c>
+      <c r="K28">
+        <v>-38868027.200569265</v>
+      </c>
+      <c r="L28">
+        <v>-320352171.6376734</v>
       </c>
     </row>
     <row r="29">
@@ -6189,28 +6936,34 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>-30969104.595553637</v>
+        <v>176991438.3346281</v>
       </c>
       <c r="C29">
-        <v>-275840027.4281647</v>
+        <v>242521708.6653719</v>
       </c>
       <c r="D29">
-        <v>-470989066.1131962</v>
+        <v>-36469188.381778</v>
       </c>
       <c r="E29">
-        <v>-404345565.86308545</v>
+        <v>-324841516.8744011</v>
       </c>
       <c r="F29">
-        <v>-0.3670149262616178</v>
+        <v>-554632527.1487067</v>
       </c>
       <c r="G29">
-        <v>-0.04067367302195635</v>
+        <v>-476148149.8512934</v>
       </c>
       <c r="H29">
-        <v>30808313.58373414</v>
+        <v>-0.4321964312402997</v>
       </c>
       <c r="I29">
-        <v>-30722189.17604554</v>
+        <v>-0.04789727900060825</v>
+      </c>
+      <c r="J29">
+        <v>36279841.0378133</v>
+      </c>
+      <c r="K29">
+        <v>-36178421.01649581</v>
       </c>
     </row>
     <row r="30">
@@ -6222,8 +6975,14 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="I31">
-        <v>-597177.966223191</v>
+      <c r="B31">
+        <v>0.3941744208241289</v>
+      </c>
+      <c r="C31">
+        <v>29671.605825579176</v>
+      </c>
+      <c r="K31">
+        <v>-703236.2101540265</v>
       </c>
     </row>
     <row r="32">
@@ -6236,31 +6995,37 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>311294.17160446895</v>
+        <v>1691947.2135494016</v>
       </c>
       <c r="C33">
-        <v>646123.3780432194</v>
+        <v>-23205415.2135494</v>
       </c>
       <c r="D33">
-        <v>190683.56122350274</v>
+        <v>366579.7230709391</v>
       </c>
       <c r="E33">
-        <v>-2544650.110871191</v>
+        <v>760840.4908470486</v>
       </c>
       <c r="F33">
-        <v>51446.19717155397</v>
+        <v>224526.84951923368</v>
       </c>
       <c r="G33">
-        <v>77779.54156229505</v>
+        <v>-2996521.8495192337</v>
       </c>
       <c r="H33">
-        <v>79830.31306177075</v>
+        <v>60582.993298582034</v>
       </c>
       <c r="I33">
-        <v>-850900.0517956198</v>
+        <v>91593.11483261129</v>
       </c>
       <c r="J33">
-        <v>107132.02647954783</v>
+        <v>94008.10141743801</v>
+      </c>
+      <c r="K33">
+        <v>-1002019.0989782347</v>
+      </c>
+      <c r="L33">
+        <v>126158.57340496815</v>
       </c>
     </row>
     <row r="34">
@@ -6293,31 +7058,37 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>106853.50103943312</v>
+        <v>823886.7217345879</v>
       </c>
       <c r="C39">
-        <v>-27778.497125213908</v>
+        <v>-991136.7217345879</v>
       </c>
       <c r="D39">
-        <v>-7779.123656053387</v>
+        <v>125830.58210921336</v>
       </c>
       <c r="E39">
-        <v>-67174.88025816582</v>
+        <v>-32712.69639346405</v>
       </c>
       <c r="F39">
-        <v>30611.309136320167</v>
+        <v>-9161.763767411292</v>
       </c>
       <c r="G39">
-        <v>787196.2686899154</v>
+        <v>-79103.23623258871</v>
       </c>
       <c r="H39">
-        <v>362358.6138453103</v>
+        <v>36047.848786225244</v>
       </c>
       <c r="I39">
-        <v>-1215239.1916715459</v>
+        <v>927001.5840369911</v>
       </c>
       <c r="J39">
-        <v>6683.249540484881</v>
+        <v>426713.1621229369</v>
+      </c>
+      <c r="K39">
+        <v>-1431064.526688079</v>
+      </c>
+      <c r="L39">
+        <v>7870.188359574655</v>
       </c>
     </row>
     <row r="40">
@@ -6325,31 +7096,37 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>-108387.46485825101</v>
+        <v>397113.6802293405</v>
       </c>
       <c r="C40">
-        <v>59876.235844500174</v>
+        <v>-20044.68022934048</v>
       </c>
       <c r="D40">
-        <v>89881.8670197684</v>
+        <v>-127636.97645641491</v>
       </c>
       <c r="E40">
-        <v>-16260.638006017552</v>
+        <v>70511.48878897133</v>
       </c>
       <c r="F40">
-        <v>-434370.8261592649</v>
+        <v>105842.90792502211</v>
       </c>
       <c r="G40">
-        <v>-4211234.622635022</v>
+        <v>-19147.907925022115</v>
       </c>
       <c r="H40">
-        <v>4470141.155142499</v>
+        <v>-511514.67546870187</v>
       </c>
       <c r="I40">
-        <v>-312870.70634821255</v>
+        <v>-4959145.922313613</v>
       </c>
       <c r="J40">
-        <v>420791.0128872527</v>
+        <v>5264034.010961931</v>
+      </c>
+      <c r="K40">
+        <v>-368436.2488992078</v>
+      </c>
+      <c r="L40">
+        <v>495523.1001592403</v>
       </c>
     </row>
     <row r="41">
@@ -6362,31 +7139,37 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>101583.03639203854</v>
+        <v>-246900.7482116719</v>
       </c>
       <c r="C42">
-        <v>41731.02379626542</v>
+        <v>256230.7482116719</v>
       </c>
       <c r="D42">
-        <v>-98389.21573084818</v>
+        <v>119624.08790812071</v>
       </c>
       <c r="E42">
-        <v>38974.15554254423</v>
+        <v>49141.29541283313</v>
       </c>
       <c r="F42">
-        <v>-84048.92470940421</v>
+        <v>-115860.83748842694</v>
       </c>
       <c r="G42">
-        <v>-69051.3834667165</v>
+        <v>45894.83748842695</v>
       </c>
       <c r="H42">
-        <v>307949.82923924405</v>
+        <v>-98975.9345174366</v>
       </c>
       <c r="I42">
-        <v>-281047.52106312336</v>
+        <v>-81314.84408598789</v>
       </c>
       <c r="J42">
-        <v>325385.54380990774</v>
+        <v>362641.4286538618</v>
+      </c>
+      <c r="K42">
+        <v>-330961.29590244667</v>
+      </c>
+      <c r="L42">
+        <v>383173.70969823346</v>
       </c>
     </row>
     <row r="43">
@@ -6399,22 +7182,28 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>392133.75836743665</v>
+        <v>24565574.993513916</v>
       </c>
       <c r="C44">
-        <v>61162.79336826096</v>
+        <v>169338.0064860839</v>
       </c>
       <c r="D44">
-        <v>-732758.5738530771</v>
+        <v>461776.3442476151</v>
       </c>
       <c r="E44">
-        <v>415603.0221173795</v>
-      </c>
-      <c r="H44">
-        <v>-238455.6619577688</v>
-      </c>
-      <c r="I44">
-        <v>238455.6619577688</v>
+        <v>72021.16903261445</v>
+      </c>
+      <c r="F44">
+        <v>-862882.3889426235</v>
+      </c>
+      <c r="G44">
+        <v>489404.38894262357</v>
+      </c>
+      <c r="J44">
+        <v>-280805.16276496014</v>
+      </c>
+      <c r="K44">
+        <v>280805.16276496014</v>
       </c>
     </row>
     <row r="45">
@@ -6437,31 +7226,37 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>15634.886538449675</v>
+        <v>-810358.1801853776</v>
       </c>
       <c r="C48">
-        <v>-3650717.0530875195</v>
+        <v>19293599.180185378</v>
       </c>
       <c r="D48">
-        <v>-8950401.146160554</v>
+        <v>18411.62765100971</v>
       </c>
       <c r="E48">
-        <v>-1723200.6872903758</v>
+        <v>-4299233.41939345</v>
       </c>
       <c r="F48">
-        <v>-829300.3597656228</v>
+        <v>-10539868.969584197</v>
       </c>
       <c r="G48">
-        <v>-1349591.8918714211</v>
+        <v>-2029202.0304158027</v>
       </c>
       <c r="H48">
-        <v>-469868.05268929835</v>
+        <v>-976583.3220025112</v>
       </c>
       <c r="I48">
-        <v>734805.3043263423</v>
+        <v>-1589278.1398092445</v>
       </c>
       <c r="J48">
-        <v>-132715.05908451648</v>
+        <v>-553316.1759725398</v>
+      </c>
+      <c r="K48">
+        <v>865306.0337835782</v>
+      </c>
+      <c r="L48">
+        <v>-156285.12848727847</v>
       </c>
     </row>
     <row r="49">
@@ -6469,28 +7264,34 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>622335051.9968461</v>
+        <v>-664075677.9879123</v>
       </c>
       <c r="C49">
-        <v>374626299.8415376</v>
+        <v>50129543.987912305</v>
       </c>
       <c r="D49">
-        <v>280018329.4407558</v>
+        <v>732861170.6492584</v>
       </c>
       <c r="E49">
-        <v>-797543191.2791394</v>
+        <v>470735409.08162814</v>
       </c>
       <c r="F49">
-        <v>700322134.1291897</v>
+        <v>312697514.936303</v>
       </c>
       <c r="G49">
-        <v>-24405930.923137903</v>
+        <v>-951710135.936303</v>
       </c>
       <c r="H49">
-        <v>-410447737.86316967</v>
+        <v>824698685.0615411</v>
       </c>
       <c r="I49">
-        <v>1745606917.6571178</v>
+        <v>-28740401.251264334</v>
+      </c>
+      <c r="J49">
+        <v>-483342869.23993945</v>
+      </c>
+      <c r="K49">
+        <v>2055625060.9103122</v>
       </c>
     </row>
     <row r="50">
@@ -6557,26 +7358,32 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
+      <c r="B62">
+        <v>7874.927706543516</v>
+      </c>
       <c r="C62">
-        <v>-14443.913497495465</v>
-      </c>
-      <c r="D62">
-        <v>-12429.306693869541</v>
+        <v>-120158.92770654352</v>
       </c>
       <c r="E62">
-        <v>-22072.510889467252</v>
+        <v>-17009.44678696373</v>
       </c>
       <c r="F62">
-        <v>1658.2953890746649</v>
+        <v>-14636.51491695847</v>
       </c>
       <c r="G62">
-        <v>2981.813289573045</v>
+        <v>-25992.48508304153</v>
       </c>
       <c r="H62">
-        <v>19819.500837071362</v>
+        <v>1952.8070871471355</v>
       </c>
       <c r="I62">
-        <v>-62535.60951571907</v>
+        <v>3511.380519291546</v>
+      </c>
+      <c r="J62">
+        <v>23339.425504854407</v>
+      </c>
+      <c r="K62">
+        <v>-73641.87482273945</v>
       </c>
     </row>
     <row r="63">
@@ -6600,31 +7407,37 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-700147675.5748214</v>
+        <v>702301007.9928364</v>
       </c>
       <c r="C67">
-        <v>-437588282.2578921</v>
+        <v>-25421940.992836345</v>
       </c>
       <c r="D67">
-        <v>-652530936.6333998</v>
+        <v>-824493242.8323534</v>
       </c>
       <c r="E67">
-        <v>306552100.46611327</v>
+        <v>-515308513.10589457</v>
       </c>
       <c r="F67">
-        <v>-354240418.72852683</v>
+        <v>-768408173.5986955</v>
       </c>
       <c r="G67">
-        <v>46489959.31505942</v>
+        <v>360988786.5986956</v>
       </c>
       <c r="H67">
-        <v>467730686.86670613</v>
+        <v>-417153183.20522165</v>
       </c>
       <c r="I67">
-        <v>-1965501844.4532387</v>
+        <v>54746532.270278454</v>
       </c>
       <c r="J67">
-        <v>458653107.7247648</v>
+        <v>550799215.9944303</v>
+      </c>
+      <c r="K67">
+        <v>-2314573119.443346</v>
+      </c>
+      <c r="L67">
+        <v>540109467.3529572</v>
       </c>
     </row>
     <row r="68">
@@ -6656,11 +7469,17 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
-      <c r="B73">
-        <v>-699836543.1661162</v>
-      </c>
-      <c r="F73">
-        <v>-354201115.9929943</v>
+      <c r="C73">
+        <v>-23162187.150025606</v>
+      </c>
+      <c r="D73">
+        <v>-824126853.6011201</v>
+      </c>
+      <c r="G73">
+        <v>361155174.24570316</v>
+      </c>
+      <c r="H73">
+        <v>-417106900.3409035</v>
       </c>
     </row>
     <row r="74">
@@ -6682,37 +7501,40 @@
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="C77">
+        <v>-2259753.84281074</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
-      <c r="B78">
-        <v>-311132.40870510414</v>
-      </c>
-      <c r="C78">
-        <v>-3111274.258640538</v>
-      </c>
       <c r="D78">
-        <v>-5195803.1531668315</v>
+        <v>-366389.23123311624</v>
       </c>
       <c r="E78">
-        <v>-141296.17948752662</v>
+        <v>-3663909.7780899387</v>
       </c>
       <c r="F78">
-        <v>-39302.73553257622</v>
+        <v>-6118499.352992443</v>
       </c>
       <c r="G78">
-        <v>39302.67092880234</v>
+        <v>-166387.64700755678</v>
       </c>
       <c r="H78">
-        <v>-3641350.962776425</v>
+        <v>-46282.86431834847</v>
       </c>
       <c r="I78">
-        <v>-2487483.9726198013</v>
+        <v>46282.7882410055</v>
       </c>
       <c r="J78">
-        <v>-595196.7394697127</v>
+        <v>-4288051.461608271</v>
+      </c>
+      <c r="K78">
+        <v>-2929258.781577763</v>
+      </c>
+      <c r="L78">
+        <v>-700903.1193965368</v>
       </c>
     </row>
     <row r="79">
@@ -6749,11 +7571,8 @@
       <c r="A85" t="str">
         <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="E85">
-        <v>306693396.64560074</v>
-      </c>
-      <c r="I85">
-        <v>-1963014360.480619</v>
+      <c r="K85">
+        <v>-2311643860.6617684</v>
       </c>
     </row>
     <row r="86">
@@ -6832,31 +7651,37 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>-4243352.836532831</v>
+        <v>-2037729.5168927829</v>
       </c>
       <c r="C101">
-        <v>-6385655.970348597</v>
+        <v>-1374836.4831072171</v>
       </c>
       <c r="D101">
-        <v>-7770648.970929384</v>
+        <v>-4996968.300726652</v>
       </c>
       <c r="E101">
-        <v>982478452.7778108</v>
+        <v>14328387.599756002</v>
       </c>
       <c r="F101">
-        <v>-340873503.3911803</v>
+        <v>-30977439.459208727</v>
       </c>
       <c r="G101">
-        <v>-7543077.85222289</v>
+        <v>1156944300.4592087</v>
       </c>
       <c r="H101">
-        <v>-74694343.28527161</v>
+        <v>-401412316.3029556</v>
       </c>
       <c r="I101">
-        <v>261050475.52867475</v>
+        <v>-8882721.369045705</v>
       </c>
       <c r="J101">
-        <v>200646393.29353034</v>
+        <v>-87959988.2495437</v>
+      </c>
+      <c r="K101">
+        <v>307412793.9293057</v>
+      </c>
+      <c r="L101">
+        <v>236281003.6230988</v>
       </c>
     </row>
     <row r="102">
@@ -6873,17 +7698,17 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B104">
-        <v>0.14972591400146484</v>
-      </c>
-      <c r="C104">
-        <v>-0.4032050371170044</v>
-      </c>
       <c r="D104">
-        <v>-1745013.7357684374</v>
+        <v>0.1763172149658203</v>
       </c>
       <c r="E104">
-        <v>903273776.9892476</v>
+        <v>12937.396077513695</v>
+      </c>
+      <c r="F104">
+        <v>-2048190.0155197382</v>
+      </c>
+      <c r="G104">
+        <v>1063674674.0155197</v>
       </c>
     </row>
     <row r="105">
@@ -6916,28 +7741,34 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-94751.42829693337</v>
+        <v>-40064.0592747379</v>
       </c>
       <c r="C110">
-        <v>150628.77780861378</v>
+        <v>86394.0592747379</v>
       </c>
       <c r="D110">
-        <v>-3460.4892556129344</v>
+        <v>-111579.19265446062</v>
       </c>
       <c r="E110">
-        <v>-40555.86025606746</v>
+        <v>177377.6950748689</v>
       </c>
       <c r="F110">
-        <v>31591.48927008036</v>
+        <v>-4073.0591919808357</v>
       </c>
       <c r="G110">
-        <v>19576.11027911397</v>
+        <v>-47757.940808019164</v>
       </c>
       <c r="H110">
-        <v>-51502.854377958094</v>
+        <v>37202.10798787196</v>
       </c>
       <c r="I110">
-        <v>-4409.745171236238</v>
+        <v>23052.80901321167</v>
+      </c>
+      <c r="J110">
+        <v>-60649.71277144122</v>
+      </c>
+      <c r="K110">
+        <v>-5192.911757240186</v>
       </c>
     </row>
     <row r="111">
@@ -6955,28 +7786,34 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-1187048.704272367</v>
+        <v>-1997665.457618045</v>
       </c>
       <c r="C113">
-        <v>-1211058.3839540062</v>
+        <v>-1461230.542381955</v>
       </c>
       <c r="D113">
-        <v>-1439840.387975868</v>
+        <v>-1397867.435297764</v>
       </c>
       <c r="E113">
-        <v>-1623881.5237977586</v>
+        <v>-1426185.2470524656</v>
       </c>
       <c r="F113">
-        <v>-1467251.2247105911</v>
+        <v>-1695545.9861847444</v>
       </c>
       <c r="G113">
-        <v>4967289.4751408035</v>
+        <v>-1912246.0138152556</v>
       </c>
       <c r="H113">
-        <v>8643190.765104413</v>
+        <v>-1727833.6592607833</v>
       </c>
       <c r="I113">
-        <v>-1729449.0155346245</v>
+        <v>5849475.404004526</v>
+      </c>
+      <c r="J113">
+        <v>10178213.298342995</v>
+      </c>
+      <c r="K113">
+        <v>-2036597.530600503</v>
       </c>
     </row>
     <row r="114">
@@ -7028,29 +7865,29 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B123">
-        <v>-2961552.8536893874</v>
-      </c>
-      <c r="C123">
-        <v>-5325225.960998192</v>
-      </c>
       <c r="D123">
-        <v>-4582334.357929513</v>
+        <v>-3487521.8490914404</v>
       </c>
       <c r="E123">
-        <v>80869113.1726171</v>
+        <v>15564257.755656004</v>
       </c>
       <c r="F123">
-        <v>-339437843.6557398</v>
+        <v>-27229630.398312286</v>
       </c>
       <c r="G123">
-        <v>-12529943.437642783</v>
+        <v>95229630.39831229</v>
       </c>
       <c r="H123">
-        <v>-83286031.19599804</v>
+        <v>-399721684.75168276</v>
       </c>
       <c r="I123">
-        <v>262784334.28938058</v>
+        <v>-14755249.582063437</v>
+      </c>
+      <c r="J123">
+        <v>-98077551.83511522</v>
+      </c>
+      <c r="K123">
+        <v>309454584.3716634</v>
       </c>
     </row>
     <row r="124">
@@ -7063,28 +7900,34 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-82007030.68342727</v>
+        <v>36195475.4157378</v>
       </c>
       <c r="C125">
-        <v>-69362082.30020069</v>
+        <v>23212607.5842622</v>
       </c>
       <c r="D125">
-        <v>-380295685.47026736</v>
+        <v>-96571402.03703445</v>
       </c>
       <c r="E125">
-        <v>491465289.45389533</v>
+        <v>-30261725.87129739</v>
       </c>
       <c r="F125">
-        <v>5209870.304871678</v>
+        <v>-486702734.6365181</v>
       </c>
       <c r="G125">
-        <v>14543932.35298853</v>
+        <v>566196958.6365181</v>
       </c>
       <c r="H125">
-        <v>-17391574.7808985</v>
+        <v>6135138.360450916</v>
       </c>
       <c r="I125">
-        <v>41093013.12303829</v>
+        <v>17126921.030488275</v>
+      </c>
+      <c r="J125">
+        <v>-20480302.069548205</v>
+      </c>
+      <c r="K125">
+        <v>48391093.52144896</v>
       </c>
     </row>
     <row r="126">
@@ -7097,31 +7940,37 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-82007030.68342727</v>
+        <v>36195475.4157378</v>
       </c>
       <c r="C127">
-        <v>-69362082.30020069</v>
+        <v>23212607.5842622</v>
       </c>
       <c r="D127">
-        <v>-380295685.47026736</v>
+        <v>-96571402.03703445</v>
       </c>
       <c r="E127">
-        <v>491465289.45389533</v>
+        <v>-30261725.87129739</v>
       </c>
       <c r="F127">
-        <v>5209870.304871678</v>
+        <v>-486702734.6365181</v>
       </c>
       <c r="G127">
-        <v>14543932.35298853</v>
+        <v>566196958.6365181</v>
       </c>
       <c r="H127">
-        <v>-17391574.7808985</v>
+        <v>6135138.360450916</v>
       </c>
       <c r="I127">
-        <v>41093013.12303829</v>
+        <v>17126921.030488275</v>
       </c>
       <c r="J127">
-        <v>89587856.86759706</v>
+        <v>-20480302.069548205</v>
+      </c>
+      <c r="K127">
+        <v>48391093.52144896</v>
+      </c>
+      <c r="L127">
+        <v>105498575.80620113</v>
       </c>
     </row>
     <row r="128">
@@ -7129,28 +7978,34 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>-0.02094605565071106</v>
+        <v>68.98690369538963</v>
       </c>
       <c r="C128">
-        <v>0.6485365033149719</v>
+        <v>10884729.013096305</v>
       </c>
       <c r="D128">
-        <v>-0.6714123040437698</v>
+        <v>-0.02466607093811035</v>
       </c>
       <c r="E128">
-        <v>76446285.04382186</v>
+        <v>1098.1861803084612</v>
       </c>
       <c r="F128">
-        <v>0.002862900495529175</v>
+        <v>566.9962216168642</v>
       </c>
       <c r="G128">
-        <v>0.3107631206512451</v>
+        <v>90021408.00377838</v>
       </c>
       <c r="H128">
-        <v>1929.959607385099</v>
+        <v>0.0033713579177856445</v>
       </c>
       <c r="I128">
-        <v>61298196.726766594</v>
+        <v>0.36595433950424194</v>
+      </c>
+      <c r="J128">
+        <v>2272.718614578247</v>
+      </c>
+      <c r="K128">
+        <v>72184698.68879308</v>
       </c>
     </row>
     <row r="129">
@@ -7158,40 +8013,46 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>-33745786.89196429</v>
+        <v>-13208789.319711186</v>
       </c>
       <c r="C129">
-        <v>-88768521.14800481</v>
+        <v>33711111.319711186</v>
       </c>
       <c r="D129">
-        <v>-412453605.4859643</v>
+        <v>-39739006.83686812</v>
       </c>
       <c r="E129">
-        <v>544211238.5259334</v>
+        <v>-104531836.35543267</v>
       </c>
       <c r="F129">
-        <v>-7775726.965636343</v>
+        <v>-485695013.38225234</v>
       </c>
       <c r="G129">
-        <v>5969221.893098772</v>
+        <v>640850787.3822523</v>
       </c>
       <c r="H129">
-        <v>-7060260.445916146</v>
+        <v>-9156688.745717853</v>
       </c>
       <c r="I129">
-        <v>85313050.51845372</v>
+        <v>7029350.075019911</v>
+      </c>
+      <c r="J129">
+        <v>-8314156.046458691</v>
+      </c>
+      <c r="K129">
+        <v>100464567.87867087</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M129"/>
+  <dimension ref="A1:O129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
@@ -7206,6 +8067,8 @@
     <col min="11" max="11" customWidth="1" width="20"/>
     <col min="12" max="12" customWidth="1" width="20"/>
     <col min="13" max="13" customWidth="1" width="20"/>
+    <col min="14" max="14" customWidth="1" width="20"/>
+    <col min="15" max="15" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7213,39 +8076,45 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
         <v>2025/12</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>2025/6</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>2025/3</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>2024/6</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>2024/3</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>2023/12</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>2023/9</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>2022/12</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>2021/12</v>
       </c>
     </row>
@@ -7259,31 +8128,37 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>479436490</v>
+        <v>589578790.7308865</v>
       </c>
       <c r="C3">
-        <v>557376284.6966518</v>
+        <v>1566329472.2124784</v>
       </c>
       <c r="D3">
-        <v>158361479.65876395</v>
+        <v>564583958.7308866</v>
       </c>
       <c r="E3">
-        <v>-532072338.8376311</v>
+        <v>656365787.5034695</v>
       </c>
       <c r="F3">
-        <v>2011037307</v>
+        <v>156910497.99788404</v>
       </c>
       <c r="G3">
-        <v>741001870.4247236</v>
-      </c>
-      <c r="J3">
-        <v>2495631447.921071</v>
+        <v>-639091910.2379376</v>
+      </c>
+      <c r="H3">
+        <v>2368195637.2189384</v>
+      </c>
+      <c r="I3">
+        <v>872603104.180455</v>
       </c>
       <c r="L3">
-        <v>1447512.8573447445</v>
-      </c>
-      <c r="M3">
-        <v>43327016.1109233</v>
+        <v>2938853240.8131313</v>
+      </c>
+      <c r="N3">
+        <v>1704589.7764551733</v>
+      </c>
+      <c r="O3">
+        <v>51021853.33432166</v>
       </c>
     </row>
     <row r="4">
@@ -7291,31 +8166,37 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>1635465449</v>
+        <v>439319899.23358893</v>
       </c>
       <c r="C4">
-        <v>1283050519.152259</v>
+        <v>2214544678.3601375</v>
       </c>
       <c r="D4">
-        <v>620333494.9113841</v>
+        <v>1925922571.233589</v>
       </c>
       <c r="E4">
-        <v>-614254256.6849483</v>
+        <v>1510919082.0137649</v>
       </c>
       <c r="F4">
-        <v>1811675465</v>
+        <v>730499631.8351073</v>
       </c>
       <c r="G4">
-        <v>1060339068.7589843</v>
-      </c>
-      <c r="J4">
-        <v>2359993577.6579094</v>
+        <v>-723336361.4482524</v>
+      </c>
+      <c r="H4">
+        <v>2133427319.9883466</v>
+      </c>
+      <c r="I4">
+        <v>1248654287.947438</v>
       </c>
       <c r="L4">
-        <v>-3227589.802110714</v>
-      </c>
-      <c r="M4">
-        <v>68498014.3785825</v>
+        <v>2779126212.6367774</v>
+      </c>
+      <c r="N4">
+        <v>-3800806.708799127</v>
+      </c>
+      <c r="O4">
+        <v>80663197.16937962</v>
       </c>
     </row>
     <row r="5">
@@ -7323,31 +8204,37 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>41595964</v>
+        <v>72619116.00010246</v>
       </c>
       <c r="C5">
-        <v>442364196.2449558</v>
+        <v>43410163.55824704</v>
       </c>
       <c r="D5">
-        <v>432104262.302225</v>
+        <v>48983368.00010245</v>
       </c>
       <c r="E5">
-        <v>459810670.1036792</v>
+        <v>520927660.54745626</v>
       </c>
       <c r="F5">
-        <v>201794946</v>
+        <v>479261496.1023518</v>
       </c>
       <c r="G5">
-        <v>-45405437.64943856</v>
-      </c>
-      <c r="J5">
-        <v>113492080.73998995</v>
+        <v>528930821.2460379</v>
+      </c>
+      <c r="H5">
+        <v>237633538.20766848</v>
+      </c>
+      <c r="I5">
+        <v>-53469400.579059914</v>
       </c>
       <c r="L5">
-        <v>7964572.160722205</v>
-      </c>
-      <c r="M5">
-        <v>2217317.4022943918</v>
+        <v>133648167.30739233</v>
+      </c>
+      <c r="N5">
+        <v>9379072.669454828</v>
+      </c>
+      <c r="O5">
+        <v>2611110.883008203</v>
       </c>
     </row>
     <row r="6">
@@ -7355,31 +8242,37 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>7224205</v>
+        <v>12380531.998821812</v>
       </c>
       <c r="C6">
-        <v>5257949.556539223</v>
+        <v>10577755.095823422</v>
       </c>
       <c r="D6">
-        <v>2282785.1128961705</v>
+        <v>8507216.998821812</v>
       </c>
       <c r="E6">
-        <v>10947924.015693694</v>
+        <v>6191756.441897497</v>
       </c>
       <c r="F6">
-        <v>11145184</v>
+        <v>2688149.4139317684</v>
       </c>
       <c r="G6">
-        <v>15628712.054185</v>
-      </c>
-      <c r="J6">
-        <v>6224411.895535565</v>
+        <v>12892221.380177265</v>
+      </c>
+      <c r="H6">
+        <v>13124558.173501015</v>
+      </c>
+      <c r="I6">
+        <v>18404356.584157564</v>
       </c>
       <c r="L6">
-        <v>1718194.4636246322</v>
-      </c>
-      <c r="M6">
-        <v>135966.74983373977</v>
+        <v>7329861.581360006</v>
+      </c>
+      <c r="N6">
+        <v>2023344.18087928</v>
+      </c>
+      <c r="O6">
+        <v>160114.31644868103</v>
       </c>
     </row>
     <row r="7">
@@ -7392,19 +8285,25 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>1319640</v>
-      </c>
-      <c r="G8">
-        <v>-2656173.3108788645</v>
-      </c>
-      <c r="J8">
-        <v>246482.03454210205</v>
+        <v>2834868.8201726303</v>
+      </c>
+      <c r="C8">
+        <v>1841406.2916964465</v>
+      </c>
+      <c r="D8">
+        <v>1554006.8201726305</v>
+      </c>
+      <c r="I8">
+        <v>-3127907.1873134123</v>
       </c>
       <c r="L8">
-        <v>6075076.951895368</v>
-      </c>
-      <c r="M8">
-        <v>1929924.4102828011</v>
+        <v>290257.0115550093</v>
+      </c>
+      <c r="N8">
+        <v>7154004.892485039</v>
+      </c>
+      <c r="O8">
+        <v>2272677.166497768</v>
       </c>
     </row>
     <row r="9">
@@ -7427,19 +8326,25 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>1727000</v>
+        <v>2159344.5722152498</v>
       </c>
       <c r="C12">
-        <v>1100691.5977512607</v>
+        <v>1870351.1940672493</v>
       </c>
       <c r="D12">
-        <v>263992.5203868246</v>
+        <v>2033713.57221525</v>
+      </c>
+      <c r="E12">
+        <v>1296173.3880544459</v>
       </c>
       <c r="F12">
-        <v>5080779</v>
-      </c>
-      <c r="J12">
-        <v>1175231.168005811</v>
+        <v>310862.24800121784</v>
+      </c>
+      <c r="H12">
+        <v>5983120.561509106</v>
+      </c>
+      <c r="L12">
+        <v>1383951.1157288933</v>
       </c>
     </row>
     <row r="13">
@@ -7522,31 +8427,37 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
       <c r="B28">
-        <v>-1197624923</v>
+        <v>77711430.49719524</v>
       </c>
       <c r="C28">
-        <v>-1167991143.2648714</v>
+        <v>-691531203.2632825</v>
       </c>
       <c r="D28">
-        <v>-894046415.8459407</v>
+        <v>-1410321980.5028048</v>
       </c>
       <c r="E28">
-        <v>-377631139.3549882</v>
+        <v>-1375425269.4180517</v>
       </c>
       <c r="F28">
-        <v>-2395028</v>
+        <v>-1052815465.1271819</v>
       </c>
       <c r="G28">
-        <v>-273892024.9984409</v>
-      </c>
-      <c r="J28">
-        <v>22145789.52317148</v>
+        <v>-444689181.1637508</v>
+      </c>
+      <c r="H28">
+        <v>-2820382.715365111</v>
+      </c>
+      <c r="I28">
+        <v>-322534990.48109317</v>
       </c>
       <c r="L28">
-        <v>-3289469.5012667454</v>
-      </c>
-      <c r="M28">
-        <v>-27388315.66995361</v>
+        <v>26078860.868961282</v>
+      </c>
+      <c r="N28">
+        <v>-3873676.1842005267</v>
+      </c>
+      <c r="O28">
+        <v>-32252454.718066167</v>
       </c>
     </row>
     <row r="29">
@@ -7554,22 +8465,28 @@
         <v xml:space="preserve">    Finansal Yatırımlardaki Azalış (Artış)</v>
       </c>
       <c r="B29">
-        <v>-1182143764</v>
+        <v>58202441.743820906</v>
       </c>
       <c r="C29">
-        <v>-1151174659.7714612</v>
+        <v>-673421523.7395139</v>
       </c>
       <c r="D29">
-        <v>-875334632.3839703</v>
+        <v>-1392091382.256179</v>
       </c>
       <c r="E29">
-        <v>-373537252.6870399</v>
+        <v>-1355622194.3065975</v>
       </c>
       <c r="F29">
-        <v>86124</v>
-      </c>
-      <c r="J29">
-        <v>22175080.60840364</v>
+        <v>-1030780677.4800937</v>
+      </c>
+      <c r="G29">
+        <v>-439868309.2935738</v>
+      </c>
+      <c r="H29">
+        <v>101419.54122377893</v>
+      </c>
+      <c r="L29">
+        <v>26113354.023322344</v>
       </c>
     </row>
     <row r="30">
@@ -7581,19 +8498,19 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
-      <c r="B31">
-        <v>-25197</v>
+      <c r="D31">
+        <v>-29671.963450554522</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v xml:space="preserve">    Finans Sektörü Faaliyetlerinden Alacaklarda Azalış (Artış)</v>
       </c>
-      <c r="L32">
-        <v>-642624.6957041519</v>
-      </c>
-      <c r="M32">
-        <v>-5878837.099419674</v>
+      <c r="N32">
+        <v>-756754.2359549676</v>
+      </c>
+      <c r="O32">
+        <v>-6922913.027175637</v>
       </c>
     </row>
     <row r="33">
@@ -7601,31 +8518,37 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>-1396549</v>
+        <v>-20386047.78608201</v>
       </c>
       <c r="C33">
-        <v>-1656396.974432915</v>
+        <v>-21853468.150112182</v>
       </c>
       <c r="D33">
-        <v>-2224740.8109138394</v>
+        <v>-1644574.7860820123</v>
       </c>
       <c r="E33">
-        <v>-2335594.0590755716</v>
+        <v>-1950571.5158543694</v>
       </c>
       <c r="F33">
-        <v>-641844</v>
+        <v>-2619818.8918688064</v>
       </c>
       <c r="G33">
-        <v>-586158.1706920061</v>
-      </c>
-      <c r="J33">
-        <v>94033.04866737442</v>
+        <v>-2750337.6399706025</v>
+      </c>
+      <c r="H33">
+        <v>-755834.8894296034</v>
+      </c>
+      <c r="I33">
+        <v>-690259.3093232173</v>
       </c>
       <c r="L33">
-        <v>-268894.18072093616</v>
-      </c>
-      <c r="M33">
-        <v>-1040.4625043544354</v>
+        <v>110733.2294798011</v>
+      </c>
+      <c r="N33">
+        <v>-316649.53377062426</v>
+      </c>
+      <c r="O33">
+        <v>-1225.2476644393075</v>
       </c>
     </row>
     <row r="34">
@@ -7658,31 +8581,37 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>4121</v>
+        <v>-74132.1142842507</v>
       </c>
       <c r="C39">
-        <v>-72121.19190311295</v>
+        <v>-907180.5997862499</v>
       </c>
       <c r="D39">
-        <v>742853.5739120163</v>
+        <v>4852.885715749303</v>
       </c>
       <c r="E39">
-        <v>1112991.31141338</v>
+        <v>-84929.8476072388</v>
       </c>
       <c r="F39">
-        <v>-35073</v>
+        <v>874784.4328232164</v>
       </c>
       <c r="G39">
-        <v>-59001.059595835286</v>
-      </c>
-      <c r="J39">
-        <v>-45338.484684584</v>
+        <v>1310659.3587135645</v>
+      </c>
+      <c r="H39">
+        <v>-41301.931741925575</v>
+      </c>
+      <c r="I39">
+        <v>-69479.59216857617</v>
       </c>
       <c r="L39">
-        <v>1181045.958803085</v>
-      </c>
-      <c r="M39">
-        <v>-326161.3482400165</v>
+        <v>-53390.55683075376</v>
+      </c>
+      <c r="N39">
+        <v>1390798.607891029</v>
+      </c>
+      <c r="O39">
+        <v>-384087.2962638947</v>
       </c>
     </row>
     <row r="40">
@@ -7690,31 +8619,37 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>25110</v>
+        <v>319943.5123325564</v>
       </c>
       <c r="C40">
-        <v>-300873.36130101385</v>
+        <v>28672.74002823805</v>
       </c>
       <c r="D40">
-        <v>-4571984.219780535</v>
+        <v>29569.512332556416</v>
       </c>
       <c r="E40">
-        <v>-191724.931657805</v>
+        <v>-354308.18667973054</v>
       </c>
       <c r="F40">
-        <v>-488335</v>
+        <v>-5383965.597782315</v>
       </c>
       <c r="G40">
-        <v>366826.8390465176</v>
-      </c>
-      <c r="J40">
-        <v>473020.0050176008</v>
+        <v>-225774.49474540568</v>
+      </c>
+      <c r="H40">
+        <v>-575062.8357195914</v>
+      </c>
+      <c r="I40">
+        <v>431974.9399083508</v>
       </c>
       <c r="L40">
-        <v>16949.24547534598</v>
-      </c>
-      <c r="M40">
-        <v>13933.573403901575</v>
+        <v>557027.9120634744</v>
+      </c>
+      <c r="N40">
+        <v>19959.41549624727</v>
+      </c>
+      <c r="O40">
+        <v>16408.162907337624</v>
       </c>
     </row>
     <row r="41">
@@ -7727,31 +8662,37 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>83899</v>
+        <v>178095.38332095384</v>
       </c>
       <c r="C42">
-        <v>-101732.96110144275</v>
+        <v>309135.29404419876</v>
       </c>
       <c r="D42">
-        <v>-212515.36836442468</v>
+        <v>98799.38332095384</v>
       </c>
       <c r="E42">
-        <v>193823.6766056676</v>
+        <v>-119800.63910460347</v>
       </c>
       <c r="F42">
-        <v>-126198</v>
+        <v>-250256.7786034245</v>
       </c>
       <c r="G42">
-        <v>283236.4685193119</v>
-      </c>
-      <c r="J42">
-        <v>261576.5378443315</v>
+        <v>228245.48753886428</v>
+      </c>
+      <c r="H42">
+        <v>-148610.64585200933</v>
+      </c>
+      <c r="I42">
+        <v>333538.9983636607</v>
       </c>
       <c r="L42">
-        <v>38860.161743515855</v>
-      </c>
-      <c r="M42">
-        <v>45951.44228789942</v>
+        <v>308032.2844163827</v>
+      </c>
+      <c r="N42">
+        <v>45761.68984149857</v>
+      </c>
+      <c r="O42">
+        <v>54112.375126674495</v>
       </c>
     </row>
     <row r="43">
@@ -7764,22 +8705,28 @@
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B44">
-        <v>136141</v>
+        <v>25268710.513280228</v>
+      </c>
+      <c r="C44">
+        <v>-159746.8691763102</v>
       </c>
       <c r="D44">
-        <v>407097.4482643024</v>
-      </c>
-      <c r="E44">
-        <v>901400.3601596106</v>
+        <v>160319.5132802295</v>
       </c>
       <c r="F44">
-        <v>724253</v>
-      </c>
-      <c r="L44">
-        <v>-436134.6183693828</v>
-      </c>
-      <c r="M44">
-        <v>118600.20656252968</v>
+        <v>479401.65015495755</v>
+      </c>
+      <c r="G44">
+        <v>1061478.8763326209</v>
+      </c>
+      <c r="H44">
+        <v>852879.6501549575</v>
+      </c>
+      <c r="N44">
+        <v>-513591.7155128734</v>
+      </c>
+      <c r="O44">
+        <v>139663.49146134846</v>
       </c>
     </row>
     <row r="45">
@@ -7802,31 +8749,37 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-14308684</v>
+        <v>14202419.20825756</v>
       </c>
       <c r="C48">
-        <v>-15153619.246304072</v>
+        <v>4472908.4188587405</v>
       </c>
       <c r="D48">
-        <v>-12852494.085087974</v>
+        <v>-16849892.79174244</v>
       </c>
       <c r="E48">
-        <v>-4371960.9916167185</v>
+        <v>-17844887.74139596</v>
       </c>
       <c r="F48">
-        <v>-1913955</v>
+        <v>-15134932.461811755</v>
       </c>
       <c r="G48">
-        <v>-1217369.6993188937</v>
-      </c>
-      <c r="J48">
-        <v>-812582.1920768844</v>
+        <v>-5148379.668200098</v>
+      </c>
+      <c r="H48">
+        <v>-2253871.6040007174</v>
+      </c>
+      <c r="I48">
+        <v>-1433573.4104854846</v>
       </c>
       <c r="L48">
-        <v>283697.1245328879</v>
-      </c>
-      <c r="M48">
-        <v>-119761.68542768472</v>
+        <v>-956896.0234899706</v>
+      </c>
+      <c r="N48">
+        <v>334081.46645105624</v>
+      </c>
+      <c r="O48">
+        <v>-141031.24787820253</v>
       </c>
     </row>
     <row r="49">
@@ -7834,22 +8787,28 @@
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
       <c r="B49">
-        <v>479436490</v>
+        <v>589650445.7308865</v>
       </c>
       <c r="C49">
-        <v>557423572.1323436</v>
+        <v>1566423638.655102</v>
       </c>
       <c r="D49">
-        <v>158391341.3676682</v>
+        <v>564583958.7308866</v>
       </c>
       <c r="E49">
-        <v>-532074725.93625724</v>
+        <v>656421473.1431692</v>
       </c>
       <c r="F49">
-        <v>2011075383</v>
-      </c>
-      <c r="J49">
-        <v>2495631447.921071</v>
+        <v>156945662.81027675</v>
+      </c>
+      <c r="G49">
+        <v>-639094721.3659657</v>
+      </c>
+      <c r="H49">
+        <v>2368240475.4806495</v>
+      </c>
+      <c r="L49">
+        <v>2938853240.8131313</v>
       </c>
     </row>
     <row r="50">
@@ -7916,23 +8875,23 @@
       <c r="A62" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalara İlişkin Karşılıklar Kapsamında Yapılan Ödemeler</v>
       </c>
-      <c r="C62">
-        <v>-47287.43569175759</v>
-      </c>
-      <c r="D62">
-        <v>-29861.708904689083</v>
-      </c>
       <c r="E62">
-        <v>2387.09862625182</v>
+        <v>-55685.639699816595</v>
       </c>
       <c r="F62">
-        <v>-38076</v>
-      </c>
-      <c r="L62">
-        <v>38860.161743515855</v>
-      </c>
-      <c r="M62">
-        <v>45951.44228789942</v>
+        <v>-35164.81239356132</v>
+      </c>
+      <c r="G62">
+        <v>2811.128028251558</v>
+      </c>
+      <c r="H62">
+        <v>-44838.261711446365</v>
+      </c>
+      <c r="N62">
+        <v>45761.68984149857</v>
+      </c>
+      <c r="O62">
+        <v>54112.375126674495</v>
       </c>
     </row>
     <row r="63">
@@ -7956,31 +8915,37 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
       <c r="B67">
-        <v>-1483714794</v>
+        <v>-662922688.9382479</v>
       </c>
       <c r="C67">
-        <v>-1137807537.1537056</v>
+        <v>-2133631870.5297797</v>
       </c>
       <c r="D67">
-        <v>-653729295.580754</v>
+        <v>-1747221142.938248</v>
       </c>
       <c r="E67">
-        <v>466532327.919352</v>
+        <v>-1339881083.3111162</v>
       </c>
       <c r="F67">
-        <v>-1805521617</v>
+        <v>-769826037.9349432</v>
       </c>
       <c r="G67">
-        <v>-992628090.5467083</v>
-      </c>
-      <c r="J67">
-        <v>-2768566947.6739235</v>
+        <v>549381351.6581826</v>
+      </c>
+      <c r="H67">
+        <v>-2126180554.383859</v>
+      </c>
+      <c r="I67">
+        <v>-1168917903.82568</v>
       </c>
       <c r="L67">
-        <v>-19328581.528869905</v>
-      </c>
-      <c r="M67">
-        <v>-56066903.60578507</v>
+        <v>-3260261828.066593</v>
+      </c>
+      <c r="N67">
+        <v>-22761319.390232608</v>
+      </c>
+      <c r="O67">
+        <v>-66024332.8402833</v>
       </c>
     </row>
     <row r="68">
@@ -8012,20 +8977,23 @@
       <c r="A73" t="str">
         <v xml:space="preserve">    İştiraklar ve/veya İş Ortaklıkları Pay Alımı veya Sermaye Artırımı Sebebiyle Oluşan Nakit Çıkışları</v>
       </c>
-      <c r="B73">
-        <v>-1474955288</v>
-      </c>
       <c r="C73">
-        <v>-1129319860.826878</v>
-      </c>
-      <c r="F73">
-        <v>-1799392782</v>
-      </c>
-      <c r="L73">
-        <v>-18727209.50227223</v>
-      </c>
-      <c r="M73">
-        <v>-55246596.2905873</v>
+        <v>-2121223318.3246536</v>
+      </c>
+      <c r="D73">
+        <v>-1736905956.9289248</v>
+      </c>
+      <c r="E73">
+        <v>-1329886003.6687083</v>
+      </c>
+      <c r="H73">
+        <v>-2118963244.0645957</v>
+      </c>
+      <c r="N73">
+        <v>-22053144.258534703</v>
+      </c>
+      <c r="O73">
+        <v>-65058339.71908748</v>
       </c>
     </row>
     <row r="74">
@@ -8053,31 +9021,34 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-8759506</v>
-      </c>
-      <c r="C78">
-        <v>-8487676.326827472</v>
+        <v>-9226859.009323055</v>
       </c>
       <c r="D78">
-        <v>-5337099.397258132</v>
+        <v>-10315186.009323055</v>
       </c>
       <c r="E78">
-        <v>-3782647.206867725</v>
+        <v>-9995079.642408287</v>
       </c>
       <c r="F78">
-        <v>-6128835</v>
+        <v>-6284887.076077343</v>
       </c>
       <c r="G78">
-        <v>-6684729.003937136</v>
-      </c>
-      <c r="J78">
-        <v>-832455.5742861931</v>
+        <v>-4454439.184693171</v>
+      </c>
+      <c r="H78">
+        <v>-7217310.319263377</v>
+      </c>
+      <c r="I78">
+        <v>-7871930.574341565</v>
       </c>
       <c r="L78">
-        <v>-601372.0265976819</v>
-      </c>
-      <c r="M78">
-        <v>-820308.7061904233</v>
+        <v>-980298.8996479857</v>
+      </c>
+      <c r="N78">
+        <v>-708175.1316979132</v>
+      </c>
+      <c r="O78">
+        <v>-965994.7592274441</v>
       </c>
     </row>
     <row r="79">
@@ -8114,8 +9085,8 @@
       <c r="A85" t="str">
         <v xml:space="preserve">    Diğer Uzun Vadeli Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="J85">
-        <v>-2767734492.0996375</v>
+      <c r="L85">
+        <v>-3259281529.1669455</v>
       </c>
     </row>
     <row r="86">
@@ -8194,31 +9165,37 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>964078795</v>
+        <v>5918853.29902935</v>
       </c>
       <c r="C101">
-        <v>627448644.4453526</v>
+        <v>-23020856.643286593</v>
       </c>
       <c r="D101">
-        <v>626291222.5634782</v>
+        <v>1135298280.2990294</v>
       </c>
       <c r="E101">
-        <v>559367528.2491361</v>
+        <v>738882932.2968004</v>
       </c>
       <c r="F101">
-        <v>-162060449</v>
+        <v>715671823.3279986</v>
       </c>
       <c r="G101">
-        <v>379459447.6847106</v>
-      </c>
-      <c r="J101">
-        <v>246190221.87641504</v>
+        <v>658689274.5376637</v>
+      </c>
+      <c r="H101">
+        <v>-190842231.99223936</v>
+      </c>
+      <c r="I101">
+        <v>446851087.93381506</v>
       </c>
       <c r="L101">
-        <v>101481342.05209883</v>
-      </c>
-      <c r="M101">
-        <v>45494097.81355893</v>
+        <v>289913373.23494446</v>
+      </c>
+      <c r="N101">
+        <v>119504332.74925976</v>
+      </c>
+      <c r="O101">
+        <v>53573806.70476139</v>
       </c>
     </row>
     <row r="102">
@@ -8235,11 +9212,11 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="B104">
-        <v>901528763</v>
-      </c>
-      <c r="J104">
-        <v>237760272.93971056</v>
+      <c r="D104">
+        <v>1061639421.5723947</v>
+      </c>
+      <c r="L104">
+        <v>279986273.312734</v>
       </c>
     </row>
     <row r="105">
@@ -8251,8 +9228,8 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
-      <c r="L106">
-        <v>47181.079793045574</v>
+      <c r="N106">
+        <v>55560.39509373912</v>
       </c>
     </row>
     <row r="107">
@@ -8269,8 +9246,8 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="J109">
-        <v>52116.08944515841</v>
+      <c r="L109">
+        <v>61371.85780857128</v>
       </c>
     </row>
     <row r="110">
@@ -8278,25 +9255,31 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>11861</v>
+        <v>112128.50242040827</v>
       </c>
       <c r="C110">
-        <v>138203.91756701373</v>
+        <v>148119.50250316533</v>
       </c>
       <c r="D110">
-        <v>7151.250037513935</v>
+        <v>13967.50242040827</v>
       </c>
       <c r="E110">
-        <v>-40891.115084831225</v>
+        <v>162748.80306274086</v>
       </c>
       <c r="F110">
-        <v>-4745</v>
-      </c>
-      <c r="L110">
-        <v>-6364283.798326314</v>
-      </c>
-      <c r="M110">
-        <v>3764318.227151091</v>
+        <v>8423.917001083631</v>
+      </c>
+      <c r="G110">
+        <v>-48152.73657837676</v>
+      </c>
+      <c r="H110">
+        <v>-5587.707527597778</v>
+      </c>
+      <c r="N110">
+        <v>-7494574.602250057</v>
+      </c>
+      <c r="O110">
+        <v>4432857.596233019</v>
       </c>
     </row>
     <row r="111">
@@ -8314,22 +9297,28 @@
         <v xml:space="preserve">    Kira Sözleşmelerinden Kaynaklanan Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B113">
-        <v>-5461829</v>
+        <v>-6282948.6823502295</v>
       </c>
       <c r="C113">
-        <v>-5742031.520438224</v>
+        <v>-5980829.210916929</v>
       </c>
       <c r="D113">
-        <v>436316.33865658566</v>
+        <v>-6431844.6823502295</v>
       </c>
       <c r="E113">
-        <v>10519347.491736867</v>
+        <v>-6761810.906313249</v>
       </c>
       <c r="F113">
-        <v>10413780</v>
-      </c>
-      <c r="J113">
-        <v>8377832.8472593175</v>
+        <v>513849.744743743</v>
+      </c>
+      <c r="G113">
+        <v>12387609.029271483</v>
+      </c>
+      <c r="H113">
+        <v>12263257.512486236</v>
+      </c>
+      <c r="L113">
+        <v>9865728.064401856</v>
       </c>
     </row>
     <row r="114">
@@ -8381,26 +9370,26 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B123">
-        <v>68000000</v>
-      </c>
-      <c r="C123">
-        <v>-268476290.8020504</v>
-      </c>
       <c r="D123">
-        <v>-275681008.278695</v>
+        <v>80076735.90656456</v>
       </c>
       <c r="E123">
-        <v>-354384705.1167635</v>
+        <v>-316157426.99602675</v>
       </c>
       <c r="F123">
-        <v>-172469484</v>
-      </c>
-      <c r="L123">
-        <v>107798444.77063212</v>
-      </c>
-      <c r="M123">
-        <v>41729779.58640783</v>
+        <v>-346476934.3337462</v>
+      </c>
+      <c r="G123">
+        <v>-417324855.7705491</v>
+      </c>
+      <c r="H123">
+        <v>-203099901.797198</v>
+      </c>
+      <c r="N123">
+        <v>126943346.9564161</v>
+      </c>
+      <c r="O123">
+        <v>49140949.108528376</v>
       </c>
     </row>
     <row r="124">
@@ -8413,22 +9402,28 @@
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B125">
-        <v>-40199509</v>
+        <v>-67425044.90833184</v>
       </c>
       <c r="C125">
-        <v>47017391.98829895</v>
+        <v>-590323254.9605877</v>
       </c>
       <c r="D125">
-        <v>130923406.64148816</v>
+        <v>-47338903.90833184</v>
       </c>
       <c r="E125">
-        <v>493827517.33085704</v>
+        <v>55367636.48915353</v>
       </c>
       <c r="F125">
-        <v>43455241</v>
-      </c>
-      <c r="J125">
-        <v>-26745277.876437392</v>
+        <v>102756283.39093919</v>
+      </c>
+      <c r="G125">
+        <v>568978715.9579091</v>
+      </c>
+      <c r="H125">
+        <v>51172850.84283995</v>
+      </c>
+      <c r="L125">
+        <v>-31495214.018517073</v>
       </c>
     </row>
     <row r="126">
@@ -8441,31 +9436,37 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>-40199509</v>
+        <v>-67425044.90833184</v>
       </c>
       <c r="C127">
-        <v>47017391.98829895</v>
+        <v>-590323254.9605877</v>
       </c>
       <c r="D127">
-        <v>130923406.64148816</v>
+        <v>-47338903.90833184</v>
       </c>
       <c r="E127">
-        <v>493827517.33085704</v>
+        <v>55367636.48915353</v>
       </c>
       <c r="F127">
-        <v>43455241</v>
+        <v>102756283.39093919</v>
       </c>
       <c r="G127">
-        <v>127833227.56272538</v>
-      </c>
-      <c r="J127">
-        <v>-26745277.876437392</v>
+        <v>568978715.9579091</v>
+      </c>
+      <c r="H127">
+        <v>51172850.84283995</v>
+      </c>
+      <c r="I127">
+        <v>150536288.28859016</v>
       </c>
       <c r="L127">
-        <v>83600273.3805737</v>
-      </c>
-      <c r="M127">
-        <v>32754210.318697162</v>
+        <v>-31495214.018517073</v>
+      </c>
+      <c r="N127">
+        <v>98447603.13548237</v>
+      </c>
+      <c r="O127">
+        <v>38571327.198799774</v>
       </c>
     </row>
     <row r="128">
@@ -8473,22 +9474,28 @@
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B128">
-        <v>76446285</v>
+        <v>10885896.161514238</v>
       </c>
       <c r="C128">
-        <v>76446285.02380896</v>
+        <v>10886394.170832159</v>
       </c>
       <c r="D128">
-        <v>76446284.68603557</v>
+        <v>90023073.16151424</v>
       </c>
       <c r="E128">
-        <v>76448215.31705526</v>
+        <v>90023073.18955167</v>
       </c>
       <c r="F128">
-        <v>61300127</v>
-      </c>
-      <c r="J128">
-        <v>116354487.84161593</v>
+        <v>90021975.3693257</v>
+      </c>
+      <c r="G128">
+        <v>90023681.09171866</v>
+      </c>
+      <c r="H128">
+        <v>72186971.77673335</v>
+      </c>
+      <c r="L128">
+        <v>137018935.2123038</v>
       </c>
     </row>
     <row r="129">
@@ -8496,27 +9503,33 @@
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B129">
-        <v>9243325</v>
+        <v>-123768521.1923008</v>
       </c>
       <c r="C129">
-        <v>35213384.926327944</v>
+        <v>-596254745.2548419</v>
       </c>
       <c r="D129">
-        <v>129951127.96743153</v>
+        <v>10884930.807699205</v>
       </c>
       <c r="E129">
-        <v>535344473.00747967</v>
+        <v>41467248.89884947</v>
       </c>
       <c r="F129">
-        <v>76446285</v>
-      </c>
-      <c r="J129">
-        <v>61300127.410258695</v>
+        <v>153028435.32930207</v>
+      </c>
+      <c r="G129">
+        <v>630409292.6650957</v>
+      </c>
+      <c r="H129">
+        <v>90023073.16151424</v>
+      </c>
+      <c r="L129">
+        <v>72186972.2598536</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O129"/>
   </ignoredErrors>
 </worksheet>
 </file>